--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132406871</v>
+        <v>132406796</v>
       </c>
       <c r="B11" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,34 +1567,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394156</v>
+        <v>394255</v>
       </c>
       <c r="R11" t="n">
-        <v>6728616</v>
+        <v>6728707</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1653,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132406859</v>
+        <v>132406829</v>
       </c>
       <c r="B12" t="n">
-        <v>79317</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394095</v>
+        <v>394324</v>
       </c>
       <c r="R12" t="n">
-        <v>6728614</v>
+        <v>6728712</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1750,7 +1758,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132406869</v>
+        <v>132406871</v>
       </c>
       <c r="B13" t="n">
         <v>79317</v>
@@ -1785,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394106</v>
+        <v>394156</v>
       </c>
       <c r="R13" t="n">
-        <v>6728622</v>
+        <v>6728616</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1847,10 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132406896</v>
+        <v>132406859</v>
       </c>
       <c r="B14" t="n">
-        <v>78983</v>
+        <v>79317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1858,21 +1866,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1882,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394194</v>
+        <v>394095</v>
       </c>
       <c r="R14" t="n">
-        <v>6728673</v>
+        <v>6728614</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1944,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132406796</v>
+        <v>132406869</v>
       </c>
       <c r="B15" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1955,42 +1963,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394255</v>
+        <v>394106</v>
       </c>
       <c r="R15" t="n">
-        <v>6728707</v>
+        <v>6728622</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132406829</v>
+        <v>132406896</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>78983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,21 +2060,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394324</v>
+        <v>394194</v>
       </c>
       <c r="R16" t="n">
-        <v>6728712</v>
+        <v>6728673</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132406821</v>
+        <v>132406857</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79317</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394200</v>
+        <v>394275</v>
       </c>
       <c r="R29" t="n">
-        <v>6728673</v>
+        <v>6728588</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132406790</v>
+        <v>132406880</v>
       </c>
       <c r="B30" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394508</v>
+        <v>394331</v>
       </c>
       <c r="R30" t="n">
-        <v>6728780</v>
+        <v>6728694</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132406857</v>
+        <v>132406867</v>
       </c>
       <c r="B31" t="n">
         <v>79317</v>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394275</v>
+        <v>394208</v>
       </c>
       <c r="R31" t="n">
-        <v>6728588</v>
+        <v>6728528</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132406880</v>
+        <v>132406913</v>
       </c>
       <c r="B32" t="n">
-        <v>79317</v>
+        <v>78324</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394331</v>
+        <v>394300</v>
       </c>
       <c r="R32" t="n">
-        <v>6728694</v>
+        <v>6728717</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132406867</v>
+        <v>132406879</v>
       </c>
       <c r="B33" t="n">
         <v>79317</v>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394208</v>
+        <v>394255</v>
       </c>
       <c r="R33" t="n">
-        <v>6728528</v>
+        <v>6728727</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3795,10 +3795,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132406913</v>
+        <v>132406821</v>
       </c>
       <c r="B34" t="n">
-        <v>78324</v>
+        <v>79075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3806,21 +3806,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394300</v>
+        <v>394200</v>
       </c>
       <c r="R34" t="n">
-        <v>6728717</v>
+        <v>6728673</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132406879</v>
+        <v>132406790</v>
       </c>
       <c r="B35" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3903,21 +3903,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394255</v>
+        <v>394508</v>
       </c>
       <c r="R35" t="n">
-        <v>6728727</v>
+        <v>6728780</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132406847</v>
+        <v>132406811</v>
       </c>
       <c r="B36" t="n">
-        <v>80382</v>
+        <v>97963</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4000,21 +4000,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394223</v>
+        <v>394327</v>
       </c>
       <c r="R36" t="n">
-        <v>6728619</v>
+        <v>6728676</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132406811</v>
+        <v>132406847</v>
       </c>
       <c r="B37" t="n">
-        <v>97963</v>
+        <v>80382</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394327</v>
+        <v>394223</v>
       </c>
       <c r="R37" t="n">
-        <v>6728676</v>
+        <v>6728619</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132406810</v>
+        <v>132406907</v>
       </c>
       <c r="B2" t="n">
-        <v>80326</v>
+        <v>83289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394222</v>
+        <v>394350</v>
       </c>
       <c r="R2" t="n">
-        <v>6728619</v>
+        <v>6728689</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132406907</v>
+        <v>132406810</v>
       </c>
       <c r="B3" t="n">
-        <v>83289</v>
+        <v>80326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394350</v>
+        <v>394222</v>
       </c>
       <c r="R3" t="n">
-        <v>6728689</v>
+        <v>6728619</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132406822</v>
+        <v>132406789</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79936</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394220</v>
+        <v>394312</v>
       </c>
       <c r="R4" t="n">
-        <v>6728660</v>
+        <v>6728711</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132406794</v>
+        <v>132406822</v>
       </c>
       <c r="B5" t="n">
-        <v>57948</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394686</v>
+        <v>394220</v>
       </c>
       <c r="R5" t="n">
-        <v>6728607</v>
+        <v>6728660</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1071,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132406789</v>
+        <v>132406876</v>
       </c>
       <c r="B6" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394312</v>
+        <v>394234</v>
       </c>
       <c r="R6" t="n">
-        <v>6728711</v>
+        <v>6728610</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1265,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132406876</v>
+        <v>132406794</v>
       </c>
       <c r="B8" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,34 +1268,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394234</v>
+        <v>394686</v>
       </c>
       <c r="R8" t="n">
-        <v>6728610</v>
+        <v>6728607</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1362,32 +1362,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132406812</v>
+        <v>132406870</v>
       </c>
       <c r="B9" t="n">
-        <v>79341</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394226</v>
+        <v>394127</v>
       </c>
       <c r="R9" t="n">
-        <v>6728553</v>
+        <v>6728621</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132406870</v>
+        <v>132406812</v>
       </c>
       <c r="B10" t="n">
-        <v>79317</v>
+        <v>79341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>394127</v>
+        <v>394226</v>
       </c>
       <c r="R10" t="n">
-        <v>6728621</v>
+        <v>6728553</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132406796</v>
+        <v>132406869</v>
       </c>
       <c r="B11" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,42 +1567,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394255</v>
+        <v>394106</v>
       </c>
       <c r="R11" t="n">
-        <v>6728707</v>
+        <v>6728622</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1661,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132406829</v>
+        <v>132406859</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>79317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394324</v>
+        <v>394095</v>
       </c>
       <c r="R12" t="n">
-        <v>6728712</v>
+        <v>6728614</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1758,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132406871</v>
+        <v>132406796</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,34 +1761,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394156</v>
+        <v>394255</v>
       </c>
       <c r="R13" t="n">
-        <v>6728616</v>
+        <v>6728707</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132406859</v>
+        <v>132406896</v>
       </c>
       <c r="B14" t="n">
-        <v>79317</v>
+        <v>78983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394095</v>
+        <v>394194</v>
       </c>
       <c r="R14" t="n">
-        <v>6728614</v>
+        <v>6728673</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132406869</v>
+        <v>132406829</v>
       </c>
       <c r="B15" t="n">
-        <v>79317</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394106</v>
+        <v>394324</v>
       </c>
       <c r="R15" t="n">
-        <v>6728622</v>
+        <v>6728712</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132406896</v>
+        <v>132406871</v>
       </c>
       <c r="B16" t="n">
-        <v>78983</v>
+        <v>79317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,21 +2060,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394194</v>
+        <v>394156</v>
       </c>
       <c r="R16" t="n">
-        <v>6728673</v>
+        <v>6728616</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2146,10 +2146,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132406866</v>
+        <v>132406899</v>
       </c>
       <c r="B17" t="n">
-        <v>79317</v>
+        <v>83289</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2157,21 +2157,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394232</v>
+        <v>394326</v>
       </c>
       <c r="R17" t="n">
-        <v>6728586</v>
+        <v>6728675</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132406864</v>
+        <v>132406881</v>
       </c>
       <c r="B18" t="n">
         <v>79317</v>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394530</v>
+        <v>394330</v>
       </c>
       <c r="R18" t="n">
-        <v>6728402</v>
+        <v>6728612</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132406899</v>
+        <v>132406866</v>
       </c>
       <c r="B19" t="n">
-        <v>83289</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2351,21 +2351,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394326</v>
+        <v>394232</v>
       </c>
       <c r="R19" t="n">
-        <v>6728675</v>
+        <v>6728586</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132406881</v>
+        <v>132406864</v>
       </c>
       <c r="B20" t="n">
         <v>79317</v>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394330</v>
+        <v>394530</v>
       </c>
       <c r="R20" t="n">
-        <v>6728612</v>
+        <v>6728402</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2534,32 +2534,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132406804</v>
+        <v>132406863</v>
       </c>
       <c r="B21" t="n">
-        <v>79403</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394251</v>
+        <v>394633</v>
       </c>
       <c r="R21" t="n">
-        <v>6728702</v>
+        <v>6728442</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2631,7 +2631,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132406863</v>
+        <v>132406861</v>
       </c>
       <c r="B22" t="n">
         <v>79317</v>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394633</v>
+        <v>394220</v>
       </c>
       <c r="R22" t="n">
-        <v>6728442</v>
+        <v>6728637</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2728,32 +2728,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132406861</v>
+        <v>132406804</v>
       </c>
       <c r="B23" t="n">
-        <v>79317</v>
+        <v>79403</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394220</v>
+        <v>394251</v>
       </c>
       <c r="R23" t="n">
-        <v>6728637</v>
+        <v>6728702</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132406825</v>
+        <v>132406784</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79936</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3030,21 +3030,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394291</v>
+        <v>394200</v>
       </c>
       <c r="R26" t="n">
-        <v>6728707</v>
+        <v>6728673</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132406784</v>
+        <v>132406825</v>
       </c>
       <c r="B28" t="n">
-        <v>79936</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3224,21 +3224,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394200</v>
+        <v>394291</v>
       </c>
       <c r="R28" t="n">
-        <v>6728673</v>
+        <v>6728707</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132406857</v>
+        <v>132406867</v>
       </c>
       <c r="B29" t="n">
         <v>79317</v>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394275</v>
+        <v>394208</v>
       </c>
       <c r="R29" t="n">
-        <v>6728588</v>
+        <v>6728528</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3407,7 +3407,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132406880</v>
+        <v>132406857</v>
       </c>
       <c r="B30" t="n">
         <v>79317</v>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394331</v>
+        <v>394275</v>
       </c>
       <c r="R30" t="n">
-        <v>6728694</v>
+        <v>6728588</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132406867</v>
+        <v>132406879</v>
       </c>
       <c r="B31" t="n">
         <v>79317</v>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394208</v>
+        <v>394255</v>
       </c>
       <c r="R31" t="n">
-        <v>6728528</v>
+        <v>6728727</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132406913</v>
+        <v>132406821</v>
       </c>
       <c r="B32" t="n">
-        <v>78324</v>
+        <v>79075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394300</v>
+        <v>394200</v>
       </c>
       <c r="R32" t="n">
-        <v>6728717</v>
+        <v>6728673</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132406879</v>
+        <v>132406880</v>
       </c>
       <c r="B33" t="n">
         <v>79317</v>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394255</v>
+        <v>394331</v>
       </c>
       <c r="R33" t="n">
-        <v>6728727</v>
+        <v>6728694</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3795,10 +3795,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132406821</v>
+        <v>132406913</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>78324</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3806,21 +3806,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394200</v>
+        <v>394300</v>
       </c>
       <c r="R34" t="n">
-        <v>6728673</v>
+        <v>6728717</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132406811</v>
+        <v>132406847</v>
       </c>
       <c r="B36" t="n">
-        <v>97963</v>
+        <v>80382</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4000,21 +4000,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394327</v>
+        <v>394223</v>
       </c>
       <c r="R36" t="n">
-        <v>6728676</v>
+        <v>6728619</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132406847</v>
+        <v>132406811</v>
       </c>
       <c r="B37" t="n">
-        <v>80382</v>
+        <v>97963</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394223</v>
+        <v>394327</v>
       </c>
       <c r="R37" t="n">
-        <v>6728619</v>
+        <v>6728676</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132406875</v>
+        <v>132406889</v>
       </c>
       <c r="B39" t="n">
         <v>79317</v>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394228</v>
+        <v>394500</v>
       </c>
       <c r="R39" t="n">
-        <v>6728628</v>
+        <v>6728810</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4377,7 +4377,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132406889</v>
+        <v>132406875</v>
       </c>
       <c r="B40" t="n">
         <v>79317</v>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394500</v>
+        <v>394228</v>
       </c>
       <c r="R40" t="n">
-        <v>6728810</v>
+        <v>6728628</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4571,32 +4571,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132406845</v>
+        <v>132406893</v>
       </c>
       <c r="B42" t="n">
-        <v>80382</v>
+        <v>79317</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394182</v>
+        <v>394568</v>
       </c>
       <c r="R42" t="n">
-        <v>6728645</v>
+        <v>6728820</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132406842</v>
+        <v>132406817</v>
       </c>
       <c r="B43" t="n">
-        <v>81302</v>
+        <v>79075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4679,21 +4679,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394087</v>
+        <v>394230</v>
       </c>
       <c r="R43" t="n">
-        <v>6728600</v>
+        <v>6728542</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4765,32 +4765,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132406893</v>
+        <v>132406803</v>
       </c>
       <c r="B44" t="n">
-        <v>79317</v>
+        <v>79403</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394568</v>
+        <v>394101</v>
       </c>
       <c r="R44" t="n">
-        <v>6728820</v>
+        <v>6728595</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4862,7 +4862,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132406803</v>
+        <v>132406806</v>
       </c>
       <c r="B45" t="n">
         <v>79403</v>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394101</v>
+        <v>394329</v>
       </c>
       <c r="R45" t="n">
-        <v>6728595</v>
+        <v>6728656</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4959,32 +4959,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132406806</v>
+        <v>132406842</v>
       </c>
       <c r="B46" t="n">
-        <v>79403</v>
+        <v>81302</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6450</v>
+        <v>1049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394329</v>
+        <v>394087</v>
       </c>
       <c r="R46" t="n">
-        <v>6728656</v>
+        <v>6728600</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5056,32 +5056,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132406817</v>
+        <v>132406845</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>80382</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394230</v>
+        <v>394182</v>
       </c>
       <c r="R47" t="n">
-        <v>6728542</v>
+        <v>6728645</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5153,10 +5153,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132406878</v>
+        <v>132406824</v>
       </c>
       <c r="B48" t="n">
-        <v>79317</v>
+        <v>79075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5164,21 +5164,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394267</v>
+        <v>394268</v>
       </c>
       <c r="R48" t="n">
-        <v>6728664</v>
+        <v>6728667</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5250,10 +5250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132406890</v>
+        <v>132406785</v>
       </c>
       <c r="B49" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5261,21 +5261,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>394513</v>
+        <v>394219</v>
       </c>
       <c r="R49" t="n">
-        <v>6728800</v>
+        <v>6728660</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5347,32 +5347,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132406850</v>
+        <v>132406791</v>
       </c>
       <c r="B50" t="n">
-        <v>78328</v>
+        <v>79907</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6000248</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>394578</v>
+        <v>394101</v>
       </c>
       <c r="R50" t="n">
-        <v>6728822</v>
+        <v>6728590</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132406791</v>
+        <v>132406878</v>
       </c>
       <c r="B51" t="n">
-        <v>79907</v>
+        <v>79317</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5455,21 +5455,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>394101</v>
+        <v>394267</v>
       </c>
       <c r="R51" t="n">
-        <v>6728590</v>
+        <v>6728664</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132406831</v>
+        <v>132406890</v>
       </c>
       <c r="B52" t="n">
-        <v>79075</v>
+        <v>79317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>394313</v>
+        <v>394513</v>
       </c>
       <c r="R52" t="n">
-        <v>6728712</v>
+        <v>6728800</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5638,10 +5638,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132406785</v>
+        <v>132406816</v>
       </c>
       <c r="B53" t="n">
-        <v>79936</v>
+        <v>79075</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5649,21 +5649,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>394219</v>
+        <v>394266</v>
       </c>
       <c r="R53" t="n">
-        <v>6728660</v>
+        <v>6728588</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5735,7 +5735,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132406816</v>
+        <v>132406815</v>
       </c>
       <c r="B54" t="n">
         <v>79075</v>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>394266</v>
+        <v>394482</v>
       </c>
       <c r="R54" t="n">
-        <v>6728588</v>
+        <v>6728440</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5832,7 +5832,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132406815</v>
+        <v>132406831</v>
       </c>
       <c r="B55" t="n">
         <v>79075</v>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>394482</v>
+        <v>394313</v>
       </c>
       <c r="R55" t="n">
-        <v>6728440</v>
+        <v>6728712</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5929,32 +5929,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132406824</v>
+        <v>132406850</v>
       </c>
       <c r="B56" t="n">
-        <v>79075</v>
+        <v>78328</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6000248</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>394268</v>
+        <v>394578</v>
       </c>
       <c r="R56" t="n">
-        <v>6728667</v>
+        <v>6728822</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6123,32 +6123,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132406865</v>
+        <v>132406846</v>
       </c>
       <c r="B58" t="n">
-        <v>79317</v>
+        <v>80382</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>394504</v>
+        <v>394178</v>
       </c>
       <c r="R58" t="n">
-        <v>6728428</v>
+        <v>6728650</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132406846</v>
+        <v>132406788</v>
       </c>
       <c r="B59" t="n">
-        <v>80382</v>
+        <v>79936</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394178</v>
+        <v>394213</v>
       </c>
       <c r="R59" t="n">
-        <v>6728650</v>
+        <v>6728660</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,53 +6317,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406801</v>
+        <v>132406865</v>
       </c>
       <c r="B60" t="n">
-        <v>57136</v>
+        <v>79317</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394300</v>
+        <v>394504</v>
       </c>
       <c r="R60" t="n">
-        <v>6728604</v>
+        <v>6728428</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6422,45 +6414,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132406788</v>
+        <v>132406801</v>
       </c>
       <c r="B61" t="n">
-        <v>79936</v>
+        <v>57136</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>394213</v>
+        <v>394300</v>
       </c>
       <c r="R61" t="n">
-        <v>6728660</v>
+        <v>6728604</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6616,45 +6616,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132406832</v>
+        <v>132406802</v>
       </c>
       <c r="B63" t="n">
-        <v>79075</v>
+        <v>57136</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>394299</v>
+        <v>394104</v>
       </c>
       <c r="R63" t="n">
-        <v>6728725</v>
+        <v>6728596</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6713,53 +6721,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132406802</v>
+        <v>132406832</v>
       </c>
       <c r="B64" t="n">
-        <v>57136</v>
+        <v>79075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>394104</v>
+        <v>394299</v>
       </c>
       <c r="R64" t="n">
-        <v>6728596</v>
+        <v>6728725</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6915,10 +6915,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132406860</v>
+        <v>132406823</v>
       </c>
       <c r="B66" t="n">
-        <v>79317</v>
+        <v>79075</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6926,21 +6926,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>394205</v>
+        <v>394266</v>
       </c>
       <c r="R66" t="n">
-        <v>6728648</v>
+        <v>6728609</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7012,7 +7012,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132406891</v>
+        <v>132406887</v>
       </c>
       <c r="B67" t="n">
         <v>79317</v>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>394509</v>
+        <v>394304</v>
       </c>
       <c r="R67" t="n">
-        <v>6728838</v>
+        <v>6728722</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7109,32 +7109,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132406887</v>
+        <v>132406782</v>
       </c>
       <c r="B68" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>394304</v>
+        <v>394325</v>
       </c>
       <c r="R68" t="n">
-        <v>6728722</v>
+        <v>6728655</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7206,32 +7206,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132406782</v>
+        <v>132406891</v>
       </c>
       <c r="B69" t="n">
-        <v>91855</v>
+        <v>79317</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7241,10 +7241,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>394325</v>
+        <v>394509</v>
       </c>
       <c r="R69" t="n">
-        <v>6728655</v>
+        <v>6728838</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7303,10 +7303,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132406823</v>
+        <v>132406860</v>
       </c>
       <c r="B70" t="n">
-        <v>79075</v>
+        <v>79317</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>394266</v>
+        <v>394205</v>
       </c>
       <c r="R70" t="n">
-        <v>6728609</v>
+        <v>6728648</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132406895</v>
+        <v>132406873</v>
       </c>
       <c r="B72" t="n">
-        <v>78983</v>
+        <v>79317</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7508,21 +7508,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>394301</v>
+        <v>394217</v>
       </c>
       <c r="R72" t="n">
-        <v>6728610</v>
+        <v>6728660</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7594,10 +7594,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132406873</v>
+        <v>132406895</v>
       </c>
       <c r="B73" t="n">
-        <v>79317</v>
+        <v>78983</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7605,21 +7605,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>394217</v>
+        <v>394301</v>
       </c>
       <c r="R73" t="n">
-        <v>6728660</v>
+        <v>6728610</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -6915,10 +6915,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132406823</v>
+        <v>132406891</v>
       </c>
       <c r="B66" t="n">
-        <v>79075</v>
+        <v>79317</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6926,21 +6926,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>394266</v>
+        <v>394509</v>
       </c>
       <c r="R66" t="n">
-        <v>6728609</v>
+        <v>6728838</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7012,7 +7012,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132406887</v>
+        <v>132406860</v>
       </c>
       <c r="B67" t="n">
         <v>79317</v>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>394304</v>
+        <v>394205</v>
       </c>
       <c r="R67" t="n">
-        <v>6728722</v>
+        <v>6728648</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7109,32 +7109,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132406782</v>
+        <v>132406823</v>
       </c>
       <c r="B68" t="n">
-        <v>91855</v>
+        <v>79075</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>394325</v>
+        <v>394266</v>
       </c>
       <c r="R68" t="n">
-        <v>6728655</v>
+        <v>6728609</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132406891</v>
+        <v>132406887</v>
       </c>
       <c r="B69" t="n">
         <v>79317</v>
@@ -7241,10 +7241,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>394509</v>
+        <v>394304</v>
       </c>
       <c r="R69" t="n">
-        <v>6728838</v>
+        <v>6728722</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7303,32 +7303,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132406860</v>
+        <v>132406782</v>
       </c>
       <c r="B70" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>394205</v>
+        <v>394325</v>
       </c>
       <c r="R70" t="n">
-        <v>6728648</v>
+        <v>6728655</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132406907</v>
       </c>
       <c r="B2" t="n">
-        <v>83289</v>
+        <v>83291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132406810</v>
       </c>
       <c r="B3" t="n">
-        <v>80326</v>
+        <v>80328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132406789</v>
+        <v>132406858</v>
       </c>
       <c r="B4" t="n">
-        <v>79936</v>
+        <v>79319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394312</v>
+        <v>394105</v>
       </c>
       <c r="R4" t="n">
-        <v>6728711</v>
+        <v>6728596</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132406822</v>
+        <v>132406789</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394220</v>
+        <v>394312</v>
       </c>
       <c r="R5" t="n">
-        <v>6728660</v>
+        <v>6728711</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1066,7 @@
         <v>132406876</v>
       </c>
       <c r="B6" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132406858</v>
+        <v>132406794</v>
       </c>
       <c r="B7" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394105</v>
+        <v>394686</v>
       </c>
       <c r="R7" t="n">
-        <v>6728596</v>
+        <v>6728607</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132406794</v>
+        <v>132406822</v>
       </c>
       <c r="B8" t="n">
-        <v>57948</v>
+        <v>79077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,42 +1276,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394686</v>
+        <v>394220</v>
       </c>
       <c r="R8" t="n">
-        <v>6728607</v>
+        <v>6728660</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1365,7 +1365,7 @@
         <v>132406870</v>
       </c>
       <c r="B9" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>132406812</v>
       </c>
       <c r="B10" t="n">
-        <v>79341</v>
+        <v>79343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132406869</v>
+        <v>132406796</v>
       </c>
       <c r="B11" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,34 +1567,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394106</v>
+        <v>394255</v>
       </c>
       <c r="R11" t="n">
-        <v>6728622</v>
+        <v>6728707</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1656,7 +1664,7 @@
         <v>132406859</v>
       </c>
       <c r="B12" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132406796</v>
+        <v>132406869</v>
       </c>
       <c r="B13" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,42 +1769,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394255</v>
+        <v>394106</v>
       </c>
       <c r="R13" t="n">
-        <v>6728707</v>
+        <v>6728622</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132406896</v>
+        <v>132406871</v>
       </c>
       <c r="B14" t="n">
-        <v>78983</v>
+        <v>79319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394194</v>
+        <v>394156</v>
       </c>
       <c r="R14" t="n">
-        <v>6728673</v>
+        <v>6728616</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1955,7 +1955,7 @@
         <v>132406829</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132406871</v>
+        <v>132406896</v>
       </c>
       <c r="B16" t="n">
-        <v>79317</v>
+        <v>78985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,21 +2060,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394156</v>
+        <v>394194</v>
       </c>
       <c r="R16" t="n">
-        <v>6728616</v>
+        <v>6728673</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2146,10 +2146,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132406899</v>
+        <v>132406864</v>
       </c>
       <c r="B17" t="n">
-        <v>83289</v>
+        <v>79319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2157,21 +2157,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394326</v>
+        <v>394530</v>
       </c>
       <c r="R17" t="n">
-        <v>6728675</v>
+        <v>6728402</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2246,7 +2246,7 @@
         <v>132406881</v>
       </c>
       <c r="B18" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>132406866</v>
       </c>
       <c r="B19" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132406864</v>
+        <v>132406899</v>
       </c>
       <c r="B20" t="n">
-        <v>79317</v>
+        <v>83291</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2448,21 +2448,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394530</v>
+        <v>394326</v>
       </c>
       <c r="R20" t="n">
-        <v>6728402</v>
+        <v>6728675</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2537,7 +2537,7 @@
         <v>132406863</v>
       </c>
       <c r="B21" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>132406861</v>
       </c>
       <c r="B22" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>132406804</v>
       </c>
       <c r="B23" t="n">
-        <v>79403</v>
+        <v>79405</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>132406820</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>132406877</v>
       </c>
       <c r="B25" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>132406784</v>
       </c>
       <c r="B26" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>132406807</v>
       </c>
       <c r="B27" t="n">
-        <v>79403</v>
+        <v>79405</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>132406825</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132406867</v>
+        <v>132406880</v>
       </c>
       <c r="B29" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394208</v>
+        <v>394331</v>
       </c>
       <c r="R29" t="n">
-        <v>6728528</v>
+        <v>6728694</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132406857</v>
+        <v>132406879</v>
       </c>
       <c r="B30" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394275</v>
+        <v>394255</v>
       </c>
       <c r="R30" t="n">
-        <v>6728588</v>
+        <v>6728727</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132406879</v>
+        <v>132406867</v>
       </c>
       <c r="B31" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394255</v>
+        <v>394208</v>
       </c>
       <c r="R31" t="n">
-        <v>6728727</v>
+        <v>6728528</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132406821</v>
+        <v>132406857</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79319</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394200</v>
+        <v>394275</v>
       </c>
       <c r="R32" t="n">
-        <v>6728673</v>
+        <v>6728588</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132406880</v>
+        <v>132406913</v>
       </c>
       <c r="B33" t="n">
-        <v>79317</v>
+        <v>78326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394331</v>
+        <v>394300</v>
       </c>
       <c r="R33" t="n">
-        <v>6728694</v>
+        <v>6728717</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3795,10 +3795,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132406913</v>
+        <v>132406790</v>
       </c>
       <c r="B34" t="n">
-        <v>78324</v>
+        <v>79938</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3806,21 +3806,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394300</v>
+        <v>394508</v>
       </c>
       <c r="R34" t="n">
-        <v>6728717</v>
+        <v>6728780</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132406790</v>
+        <v>132406821</v>
       </c>
       <c r="B35" t="n">
-        <v>79936</v>
+        <v>79077</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3903,21 +3903,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394508</v>
+        <v>394200</v>
       </c>
       <c r="R35" t="n">
-        <v>6728780</v>
+        <v>6728673</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132406847</v>
+        <v>132406811</v>
       </c>
       <c r="B36" t="n">
-        <v>80382</v>
+        <v>97971</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4000,21 +4000,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394223</v>
+        <v>394327</v>
       </c>
       <c r="R36" t="n">
-        <v>6728619</v>
+        <v>6728676</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132406811</v>
+        <v>132406847</v>
       </c>
       <c r="B37" t="n">
-        <v>97963</v>
+        <v>80384</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394327</v>
+        <v>394223</v>
       </c>
       <c r="R37" t="n">
-        <v>6728676</v>
+        <v>6728619</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4186,7 +4186,7 @@
         <v>132406818</v>
       </c>
       <c r="B38" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132406889</v>
+        <v>132406875</v>
       </c>
       <c r="B39" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394500</v>
+        <v>394228</v>
       </c>
       <c r="R39" t="n">
-        <v>6728810</v>
+        <v>6728628</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4377,10 +4377,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132406875</v>
+        <v>132406889</v>
       </c>
       <c r="B40" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394228</v>
+        <v>394500</v>
       </c>
       <c r="R40" t="n">
-        <v>6728628</v>
+        <v>6728810</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4477,7 +4477,7 @@
         <v>132406844</v>
       </c>
       <c r="B41" t="n">
-        <v>81302</v>
+        <v>81304</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4571,10 +4571,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132406893</v>
+        <v>132406842</v>
       </c>
       <c r="B42" t="n">
-        <v>79317</v>
+        <v>81304</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4582,21 +4582,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394568</v>
+        <v>394087</v>
       </c>
       <c r="R42" t="n">
-        <v>6728820</v>
+        <v>6728600</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4671,7 +4671,7 @@
         <v>132406817</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132406803</v>
+        <v>132406845</v>
       </c>
       <c r="B44" t="n">
-        <v>79403</v>
+        <v>80384</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4776,21 +4776,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6450</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394101</v>
+        <v>394182</v>
       </c>
       <c r="R44" t="n">
-        <v>6728595</v>
+        <v>6728645</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4862,32 +4862,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132406806</v>
+        <v>132406893</v>
       </c>
       <c r="B45" t="n">
-        <v>79403</v>
+        <v>79319</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394329</v>
+        <v>394568</v>
       </c>
       <c r="R45" t="n">
-        <v>6728656</v>
+        <v>6728820</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4959,32 +4959,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132406842</v>
+        <v>132406803</v>
       </c>
       <c r="B46" t="n">
-        <v>81302</v>
+        <v>79405</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1049</v>
+        <v>6450</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394087</v>
+        <v>394101</v>
       </c>
       <c r="R46" t="n">
-        <v>6728600</v>
+        <v>6728595</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5056,10 +5056,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132406845</v>
+        <v>132406806</v>
       </c>
       <c r="B47" t="n">
-        <v>80382</v>
+        <v>79405</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5067,21 +5067,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>6450</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394182</v>
+        <v>394329</v>
       </c>
       <c r="R47" t="n">
-        <v>6728645</v>
+        <v>6728656</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5153,32 +5153,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132406824</v>
+        <v>132406850</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>78330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6000248</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394268</v>
+        <v>394578</v>
       </c>
       <c r="R48" t="n">
-        <v>6728667</v>
+        <v>6728822</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5250,10 +5250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132406785</v>
+        <v>132406824</v>
       </c>
       <c r="B49" t="n">
-        <v>79936</v>
+        <v>79077</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5261,21 +5261,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>394219</v>
+        <v>394268</v>
       </c>
       <c r="R49" t="n">
-        <v>6728660</v>
+        <v>6728667</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5350,7 +5350,7 @@
         <v>132406791</v>
       </c>
       <c r="B50" t="n">
-        <v>79907</v>
+        <v>79909</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132406878</v>
+        <v>132406816</v>
       </c>
       <c r="B51" t="n">
-        <v>79317</v>
+        <v>79077</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5455,21 +5455,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>394267</v>
+        <v>394266</v>
       </c>
       <c r="R51" t="n">
-        <v>6728664</v>
+        <v>6728588</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132406890</v>
+        <v>132406815</v>
       </c>
       <c r="B52" t="n">
-        <v>79317</v>
+        <v>79077</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>394513</v>
+        <v>394482</v>
       </c>
       <c r="R52" t="n">
-        <v>6728800</v>
+        <v>6728440</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5638,10 +5638,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132406816</v>
+        <v>132406831</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>394266</v>
+        <v>394313</v>
       </c>
       <c r="R53" t="n">
-        <v>6728588</v>
+        <v>6728712</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132406815</v>
+        <v>132406785</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>79938</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>394482</v>
+        <v>394219</v>
       </c>
       <c r="R54" t="n">
-        <v>6728440</v>
+        <v>6728660</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5832,10 +5832,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132406831</v>
+        <v>132406878</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>79319</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5843,21 +5843,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>394313</v>
+        <v>394267</v>
       </c>
       <c r="R55" t="n">
-        <v>6728712</v>
+        <v>6728664</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5929,32 +5929,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132406850</v>
+        <v>132406890</v>
       </c>
       <c r="B56" t="n">
-        <v>78328</v>
+        <v>79319</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6000248</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>394578</v>
+        <v>394513</v>
       </c>
       <c r="R56" t="n">
-        <v>6728822</v>
+        <v>6728800</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6026,45 +6026,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132406900</v>
+        <v>132406801</v>
       </c>
       <c r="B57" t="n">
-        <v>83289</v>
+        <v>57137</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>308</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>394335</v>
+        <v>394300</v>
       </c>
       <c r="R57" t="n">
-        <v>6728632</v>
+        <v>6728604</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,32 +6131,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132406846</v>
+        <v>132406865</v>
       </c>
       <c r="B58" t="n">
-        <v>80382</v>
+        <v>79319</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6166,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>394178</v>
+        <v>394504</v>
       </c>
       <c r="R58" t="n">
-        <v>6728650</v>
+        <v>6728428</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,10 +6228,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132406788</v>
+        <v>132406900</v>
       </c>
       <c r="B59" t="n">
-        <v>79936</v>
+        <v>83291</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6231,21 +6239,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6263,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394213</v>
+        <v>394335</v>
       </c>
       <c r="R59" t="n">
-        <v>6728660</v>
+        <v>6728632</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6325,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406865</v>
+        <v>132406788</v>
       </c>
       <c r="B60" t="n">
-        <v>79317</v>
+        <v>79938</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6336,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6360,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394504</v>
+        <v>394213</v>
       </c>
       <c r="R60" t="n">
-        <v>6728428</v>
+        <v>6728660</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6414,10 +6422,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132406801</v>
+        <v>132406846</v>
       </c>
       <c r="B61" t="n">
-        <v>57136</v>
+        <v>80384</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,42 +6433,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>394300</v>
+        <v>394178</v>
       </c>
       <c r="R61" t="n">
-        <v>6728604</v>
+        <v>6728650</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6522,7 +6522,7 @@
         <v>132406786</v>
       </c>
       <c r="B62" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6616,53 +6616,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132406802</v>
+        <v>132406832</v>
       </c>
       <c r="B63" t="n">
-        <v>57136</v>
+        <v>79077</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>394104</v>
+        <v>394299</v>
       </c>
       <c r="R63" t="n">
-        <v>6728596</v>
+        <v>6728725</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6721,10 +6713,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132406832</v>
+        <v>132406854</v>
       </c>
       <c r="B64" t="n">
-        <v>79075</v>
+        <v>79319</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6732,21 +6724,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6756,10 +6748,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>394299</v>
+        <v>394452</v>
       </c>
       <c r="R64" t="n">
-        <v>6728725</v>
+        <v>6728433</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6818,45 +6810,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132406854</v>
+        <v>132406802</v>
       </c>
       <c r="B65" t="n">
-        <v>79317</v>
+        <v>57137</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>394452</v>
+        <v>394104</v>
       </c>
       <c r="R65" t="n">
-        <v>6728433</v>
+        <v>6728596</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6915,32 +6915,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132406891</v>
+        <v>132406782</v>
       </c>
       <c r="B66" t="n">
-        <v>79317</v>
+        <v>91861</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>394509</v>
+        <v>394325</v>
       </c>
       <c r="R66" t="n">
-        <v>6728838</v>
+        <v>6728655</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7012,10 +7012,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132406860</v>
+        <v>132406891</v>
       </c>
       <c r="B67" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>394205</v>
+        <v>394509</v>
       </c>
       <c r="R67" t="n">
-        <v>6728648</v>
+        <v>6728838</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7109,10 +7109,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132406823</v>
+        <v>132406887</v>
       </c>
       <c r="B68" t="n">
-        <v>79075</v>
+        <v>79319</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7120,21 +7120,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>394266</v>
+        <v>394304</v>
       </c>
       <c r="R68" t="n">
-        <v>6728609</v>
+        <v>6728722</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7206,10 +7206,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132406887</v>
+        <v>132406860</v>
       </c>
       <c r="B69" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7241,10 +7241,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>394304</v>
+        <v>394205</v>
       </c>
       <c r="R69" t="n">
-        <v>6728722</v>
+        <v>6728648</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7303,32 +7303,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132406782</v>
+        <v>132406823</v>
       </c>
       <c r="B70" t="n">
-        <v>91855</v>
+        <v>79077</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>394325</v>
+        <v>394266</v>
       </c>
       <c r="R70" t="n">
-        <v>6728655</v>
+        <v>6728609</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7403,7 +7403,7 @@
         <v>132406872</v>
       </c>
       <c r="B71" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>132406873</v>
       </c>
       <c r="B72" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>132406895</v>
       </c>
       <c r="B73" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132406858</v>
+        <v>132406794</v>
       </c>
       <c r="B4" t="n">
-        <v>79319</v>
+        <v>57949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394105</v>
+        <v>394686</v>
       </c>
       <c r="R4" t="n">
-        <v>6728596</v>
+        <v>6728607</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132406789</v>
+        <v>132406858</v>
       </c>
       <c r="B5" t="n">
-        <v>79938</v>
+        <v>79319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394312</v>
+        <v>394105</v>
       </c>
       <c r="R5" t="n">
-        <v>6728711</v>
+        <v>6728596</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132406876</v>
+        <v>132406789</v>
       </c>
       <c r="B6" t="n">
-        <v>79319</v>
+        <v>79938</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394234</v>
+        <v>394312</v>
       </c>
       <c r="R6" t="n">
-        <v>6728610</v>
+        <v>6728711</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132406794</v>
+        <v>132406876</v>
       </c>
       <c r="B7" t="n">
-        <v>57949</v>
+        <v>79319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,42 +1179,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394686</v>
+        <v>394234</v>
       </c>
       <c r="R7" t="n">
-        <v>6728607</v>
+        <v>6728610</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132406796</v>
+        <v>132406859</v>
       </c>
       <c r="B11" t="n">
-        <v>57949</v>
+        <v>79319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,42 +1567,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394255</v>
+        <v>394095</v>
       </c>
       <c r="R11" t="n">
-        <v>6728707</v>
+        <v>6728614</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1661,7 +1653,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132406859</v>
+        <v>132406869</v>
       </c>
       <c r="B12" t="n">
         <v>79319</v>
@@ -1696,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394095</v>
+        <v>394106</v>
       </c>
       <c r="R12" t="n">
-        <v>6728614</v>
+        <v>6728622</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1758,7 +1750,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132406869</v>
+        <v>132406871</v>
       </c>
       <c r="B13" t="n">
         <v>79319</v>
@@ -1793,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394106</v>
+        <v>394156</v>
       </c>
       <c r="R13" t="n">
-        <v>6728622</v>
+        <v>6728616</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1855,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132406871</v>
+        <v>132406829</v>
       </c>
       <c r="B14" t="n">
-        <v>79319</v>
+        <v>79077</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1866,21 +1858,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394156</v>
+        <v>394324</v>
       </c>
       <c r="R14" t="n">
-        <v>6728616</v>
+        <v>6728712</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1952,10 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132406829</v>
+        <v>132406796</v>
       </c>
       <c r="B15" t="n">
-        <v>79077</v>
+        <v>57949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,34 +1955,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394324</v>
+        <v>394255</v>
       </c>
       <c r="R15" t="n">
-        <v>6728712</v>
+        <v>6728707</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -5153,32 +5153,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132406850</v>
+        <v>132406785</v>
       </c>
       <c r="B48" t="n">
-        <v>78330</v>
+        <v>79938</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6000248</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394578</v>
+        <v>394219</v>
       </c>
       <c r="R48" t="n">
-        <v>6728822</v>
+        <v>6728660</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5250,10 +5250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132406824</v>
+        <v>132406878</v>
       </c>
       <c r="B49" t="n">
-        <v>79077</v>
+        <v>79319</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5261,21 +5261,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>394268</v>
+        <v>394267</v>
       </c>
       <c r="R49" t="n">
-        <v>6728667</v>
+        <v>6728664</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5347,10 +5347,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132406791</v>
+        <v>132406890</v>
       </c>
       <c r="B50" t="n">
-        <v>79909</v>
+        <v>79319</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>394101</v>
+        <v>394513</v>
       </c>
       <c r="R50" t="n">
-        <v>6728590</v>
+        <v>6728800</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132406816</v>
+        <v>132406791</v>
       </c>
       <c r="B51" t="n">
-        <v>79077</v>
+        <v>79909</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5455,21 +5455,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>394266</v>
+        <v>394101</v>
       </c>
       <c r="R51" t="n">
-        <v>6728588</v>
+        <v>6728590</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5541,7 +5541,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132406815</v>
+        <v>132406816</v>
       </c>
       <c r="B52" t="n">
         <v>79077</v>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>394482</v>
+        <v>394266</v>
       </c>
       <c r="R52" t="n">
-        <v>6728440</v>
+        <v>6728588</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132406831</v>
+        <v>132406815</v>
       </c>
       <c r="B53" t="n">
         <v>79077</v>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>394313</v>
+        <v>394482</v>
       </c>
       <c r="R53" t="n">
-        <v>6728712</v>
+        <v>6728440</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132406785</v>
+        <v>132406831</v>
       </c>
       <c r="B54" t="n">
-        <v>79938</v>
+        <v>79077</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>394219</v>
+        <v>394313</v>
       </c>
       <c r="R54" t="n">
-        <v>6728660</v>
+        <v>6728712</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5832,32 +5832,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132406878</v>
+        <v>132406850</v>
       </c>
       <c r="B55" t="n">
-        <v>79319</v>
+        <v>78330</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6000248</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>394267</v>
+        <v>394578</v>
       </c>
       <c r="R55" t="n">
-        <v>6728664</v>
+        <v>6728822</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5929,10 +5929,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132406890</v>
+        <v>132406824</v>
       </c>
       <c r="B56" t="n">
-        <v>79319</v>
+        <v>79077</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5940,21 +5940,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>394513</v>
+        <v>394268</v>
       </c>
       <c r="R56" t="n">
-        <v>6728800</v>
+        <v>6728667</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6026,53 +6026,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132406801</v>
+        <v>132406865</v>
       </c>
       <c r="B57" t="n">
-        <v>57137</v>
+        <v>79319</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>394300</v>
+        <v>394504</v>
       </c>
       <c r="R57" t="n">
-        <v>6728604</v>
+        <v>6728428</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6131,10 +6123,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132406865</v>
+        <v>132406788</v>
       </c>
       <c r="B58" t="n">
-        <v>79319</v>
+        <v>79938</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6142,21 +6134,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6166,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>394504</v>
+        <v>394213</v>
       </c>
       <c r="R58" t="n">
-        <v>6728428</v>
+        <v>6728660</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6228,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132406900</v>
+        <v>132406846</v>
       </c>
       <c r="B59" t="n">
-        <v>83291</v>
+        <v>80384</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308</v>
+        <v>229497</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6263,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394335</v>
+        <v>394178</v>
       </c>
       <c r="R59" t="n">
-        <v>6728632</v>
+        <v>6728650</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6325,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406788</v>
+        <v>132406900</v>
       </c>
       <c r="B60" t="n">
-        <v>79938</v>
+        <v>83291</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,21 +6328,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6360,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394213</v>
+        <v>394335</v>
       </c>
       <c r="R60" t="n">
-        <v>6728660</v>
+        <v>6728632</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6422,10 +6414,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132406846</v>
+        <v>132406801</v>
       </c>
       <c r="B61" t="n">
-        <v>80384</v>
+        <v>57137</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6433,34 +6425,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>394178</v>
+        <v>394300</v>
       </c>
       <c r="R61" t="n">
-        <v>6728650</v>
+        <v>6728604</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6616,10 +6616,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132406832</v>
+        <v>132406854</v>
       </c>
       <c r="B63" t="n">
-        <v>79077</v>
+        <v>79319</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>394299</v>
+        <v>394452</v>
       </c>
       <c r="R63" t="n">
-        <v>6728725</v>
+        <v>6728433</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6713,45 +6713,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132406854</v>
+        <v>132406802</v>
       </c>
       <c r="B64" t="n">
-        <v>79319</v>
+        <v>57137</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>394452</v>
+        <v>394104</v>
       </c>
       <c r="R64" t="n">
-        <v>6728433</v>
+        <v>6728596</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6810,53 +6818,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132406802</v>
+        <v>132406832</v>
       </c>
       <c r="B65" t="n">
-        <v>57137</v>
+        <v>79077</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>394104</v>
+        <v>394299</v>
       </c>
       <c r="R65" t="n">
-        <v>6728596</v>
+        <v>6728725</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7206,10 +7206,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132406860</v>
+        <v>132406823</v>
       </c>
       <c r="B69" t="n">
-        <v>79319</v>
+        <v>79077</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7217,21 +7217,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7241,10 +7241,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>394205</v>
+        <v>394266</v>
       </c>
       <c r="R69" t="n">
-        <v>6728648</v>
+        <v>6728609</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7303,10 +7303,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132406823</v>
+        <v>132406860</v>
       </c>
       <c r="B70" t="n">
-        <v>79077</v>
+        <v>79319</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>394266</v>
+        <v>394205</v>
       </c>
       <c r="R70" t="n">
-        <v>6728609</v>
+        <v>6728648</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7689,6 +7689,104 @@
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>132406909</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79351</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>185</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>394279</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6728740</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132406907</v>
       </c>
       <c r="B2" t="n">
-        <v>83291</v>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132406810</v>
       </c>
       <c r="B3" t="n">
-        <v>80328</v>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132406794</v>
+        <v>132406789</v>
       </c>
       <c r="B4" t="n">
-        <v>57949</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394686</v>
+        <v>394312</v>
       </c>
       <c r="R4" t="n">
-        <v>6728607</v>
+        <v>6728711</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132406858</v>
+        <v>132406876</v>
       </c>
       <c r="B5" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394105</v>
+        <v>394234</v>
       </c>
       <c r="R5" t="n">
-        <v>6728596</v>
+        <v>6728610</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1071,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132406789</v>
+        <v>132406858</v>
       </c>
       <c r="B6" t="n">
-        <v>79938</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394312</v>
+        <v>394105</v>
       </c>
       <c r="R6" t="n">
-        <v>6728711</v>
+        <v>6728596</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1168,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132406876</v>
+        <v>132406822</v>
       </c>
       <c r="B7" t="n">
-        <v>79319</v>
+        <v>79085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1179,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394234</v>
+        <v>394220</v>
       </c>
       <c r="R7" t="n">
-        <v>6728610</v>
+        <v>6728660</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1265,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132406822</v>
+        <v>132406794</v>
       </c>
       <c r="B8" t="n">
-        <v>79077</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,34 +1268,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394220</v>
+        <v>394686</v>
       </c>
       <c r="R8" t="n">
-        <v>6728660</v>
+        <v>6728607</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1362,32 +1362,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132406870</v>
+        <v>132406812</v>
       </c>
       <c r="B9" t="n">
-        <v>79319</v>
+        <v>79351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394127</v>
+        <v>394226</v>
       </c>
       <c r="R9" t="n">
-        <v>6728621</v>
+        <v>6728553</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132406812</v>
+        <v>132406870</v>
       </c>
       <c r="B10" t="n">
-        <v>79343</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>394226</v>
+        <v>394127</v>
       </c>
       <c r="R10" t="n">
-        <v>6728553</v>
+        <v>6728621</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132406859</v>
+        <v>132406796</v>
       </c>
       <c r="B11" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,34 +1567,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394095</v>
+        <v>394255</v>
       </c>
       <c r="R11" t="n">
-        <v>6728614</v>
+        <v>6728707</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1653,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132406869</v>
+        <v>132406896</v>
       </c>
       <c r="B12" t="n">
-        <v>79319</v>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394106</v>
+        <v>394194</v>
       </c>
       <c r="R12" t="n">
-        <v>6728622</v>
+        <v>6728673</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1750,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132406871</v>
+        <v>132406869</v>
       </c>
       <c r="B13" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394156</v>
+        <v>394106</v>
       </c>
       <c r="R13" t="n">
-        <v>6728616</v>
+        <v>6728622</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1847,10 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132406829</v>
+        <v>132406859</v>
       </c>
       <c r="B14" t="n">
-        <v>79077</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1858,21 +1866,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1882,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394324</v>
+        <v>394095</v>
       </c>
       <c r="R14" t="n">
-        <v>6728712</v>
+        <v>6728614</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1944,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132406796</v>
+        <v>132406871</v>
       </c>
       <c r="B15" t="n">
-        <v>57949</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1955,42 +1963,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394255</v>
+        <v>394156</v>
       </c>
       <c r="R15" t="n">
-        <v>6728707</v>
+        <v>6728616</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132406896</v>
+        <v>132406829</v>
       </c>
       <c r="B16" t="n">
-        <v>78985</v>
+        <v>79085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,21 +2060,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394194</v>
+        <v>394324</v>
       </c>
       <c r="R16" t="n">
-        <v>6728673</v>
+        <v>6728712</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2146,10 +2146,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132406864</v>
+        <v>132406881</v>
       </c>
       <c r="B17" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394530</v>
+        <v>394330</v>
       </c>
       <c r="R17" t="n">
-        <v>6728402</v>
+        <v>6728612</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132406881</v>
+        <v>132406866</v>
       </c>
       <c r="B18" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394330</v>
+        <v>394232</v>
       </c>
       <c r="R18" t="n">
-        <v>6728612</v>
+        <v>6728586</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132406866</v>
+        <v>132406864</v>
       </c>
       <c r="B19" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394232</v>
+        <v>394530</v>
       </c>
       <c r="R19" t="n">
-        <v>6728586</v>
+        <v>6728402</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2440,7 +2440,7 @@
         <v>132406899</v>
       </c>
       <c r="B20" t="n">
-        <v>83291</v>
+        <v>83299</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>132406863</v>
       </c>
       <c r="B21" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>132406861</v>
       </c>
       <c r="B22" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>132406804</v>
       </c>
       <c r="B23" t="n">
-        <v>79405</v>
+        <v>79413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2825,10 +2825,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132406820</v>
+        <v>132406877</v>
       </c>
       <c r="B24" t="n">
-        <v>79077</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2836,21 +2836,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394100</v>
+        <v>394260</v>
       </c>
       <c r="R24" t="n">
-        <v>6728603</v>
+        <v>6728663</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132406877</v>
+        <v>132406820</v>
       </c>
       <c r="B25" t="n">
-        <v>79319</v>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2933,21 +2933,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394260</v>
+        <v>394100</v>
       </c>
       <c r="R25" t="n">
-        <v>6728663</v>
+        <v>6728603</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3022,7 +3022,7 @@
         <v>132406784</v>
       </c>
       <c r="B26" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>132406807</v>
       </c>
       <c r="B27" t="n">
-        <v>79405</v>
+        <v>79413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>132406825</v>
       </c>
       <c r="B28" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132406880</v>
+        <v>132406821</v>
       </c>
       <c r="B29" t="n">
-        <v>79319</v>
+        <v>79085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394331</v>
+        <v>394200</v>
       </c>
       <c r="R29" t="n">
-        <v>6728694</v>
+        <v>6728673</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132406879</v>
+        <v>132406867</v>
       </c>
       <c r="B30" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394255</v>
+        <v>394208</v>
       </c>
       <c r="R30" t="n">
-        <v>6728727</v>
+        <v>6728528</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132406867</v>
+        <v>132406857</v>
       </c>
       <c r="B31" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394208</v>
+        <v>394275</v>
       </c>
       <c r="R31" t="n">
-        <v>6728528</v>
+        <v>6728588</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132406857</v>
+        <v>132406879</v>
       </c>
       <c r="B32" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394275</v>
+        <v>394255</v>
       </c>
       <c r="R32" t="n">
-        <v>6728588</v>
+        <v>6728727</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132406913</v>
+        <v>132406880</v>
       </c>
       <c r="B33" t="n">
-        <v>78326</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394300</v>
+        <v>394331</v>
       </c>
       <c r="R33" t="n">
-        <v>6728717</v>
+        <v>6728694</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3795,10 +3795,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132406790</v>
+        <v>132406913</v>
       </c>
       <c r="B34" t="n">
-        <v>79938</v>
+        <v>78334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3806,21 +3806,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394508</v>
+        <v>394300</v>
       </c>
       <c r="R34" t="n">
-        <v>6728780</v>
+        <v>6728717</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132406821</v>
+        <v>132406790</v>
       </c>
       <c r="B35" t="n">
-        <v>79077</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3903,21 +3903,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394200</v>
+        <v>394508</v>
       </c>
       <c r="R35" t="n">
-        <v>6728673</v>
+        <v>6728780</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3992,7 +3992,7 @@
         <v>132406811</v>
       </c>
       <c r="B36" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>132406847</v>
       </c>
       <c r="B37" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>132406818</v>
       </c>
       <c r="B38" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132406875</v>
+        <v>132406889</v>
       </c>
       <c r="B39" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394228</v>
+        <v>394500</v>
       </c>
       <c r="R39" t="n">
-        <v>6728628</v>
+        <v>6728810</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4377,10 +4377,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132406889</v>
+        <v>132406875</v>
       </c>
       <c r="B40" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394500</v>
+        <v>394228</v>
       </c>
       <c r="R40" t="n">
-        <v>6728810</v>
+        <v>6728628</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4477,7 +4477,7 @@
         <v>132406844</v>
       </c>
       <c r="B41" t="n">
-        <v>81304</v>
+        <v>81312</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>132406842</v>
       </c>
       <c r="B42" t="n">
-        <v>81304</v>
+        <v>81312</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132406817</v>
+        <v>132406893</v>
       </c>
       <c r="B43" t="n">
-        <v>79077</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4679,21 +4679,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394230</v>
+        <v>394568</v>
       </c>
       <c r="R43" t="n">
-        <v>6728542</v>
+        <v>6728820</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132406845</v>
+        <v>132406803</v>
       </c>
       <c r="B44" t="n">
-        <v>80384</v>
+        <v>79413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4776,21 +4776,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>6450</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394182</v>
+        <v>394101</v>
       </c>
       <c r="R44" t="n">
-        <v>6728645</v>
+        <v>6728595</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4862,32 +4862,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132406893</v>
+        <v>132406806</v>
       </c>
       <c r="B45" t="n">
-        <v>79319</v>
+        <v>79413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394568</v>
+        <v>394329</v>
       </c>
       <c r="R45" t="n">
-        <v>6728820</v>
+        <v>6728656</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4959,32 +4959,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132406803</v>
+        <v>132406817</v>
       </c>
       <c r="B46" t="n">
-        <v>79405</v>
+        <v>79085</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394101</v>
+        <v>394230</v>
       </c>
       <c r="R46" t="n">
-        <v>6728595</v>
+        <v>6728542</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5056,10 +5056,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132406806</v>
+        <v>132406845</v>
       </c>
       <c r="B47" t="n">
-        <v>79405</v>
+        <v>80392</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5067,21 +5067,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6450</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394329</v>
+        <v>394182</v>
       </c>
       <c r="R47" t="n">
-        <v>6728656</v>
+        <v>6728645</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5156,7 +5156,7 @@
         <v>132406785</v>
       </c>
       <c r="B48" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>132406878</v>
       </c>
       <c r="B49" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>132406890</v>
       </c>
       <c r="B50" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5444,32 +5444,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132406791</v>
+        <v>132406850</v>
       </c>
       <c r="B51" t="n">
-        <v>79909</v>
+        <v>78338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6000248</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>394101</v>
+        <v>394578</v>
       </c>
       <c r="R51" t="n">
-        <v>6728590</v>
+        <v>6728822</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132406816</v>
+        <v>132406831</v>
       </c>
       <c r="B52" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>394266</v>
+        <v>394313</v>
       </c>
       <c r="R52" t="n">
-        <v>6728588</v>
+        <v>6728712</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5638,10 +5638,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132406815</v>
+        <v>132406824</v>
       </c>
       <c r="B53" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>394482</v>
+        <v>394268</v>
       </c>
       <c r="R53" t="n">
-        <v>6728440</v>
+        <v>6728667</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132406831</v>
+        <v>132406791</v>
       </c>
       <c r="B54" t="n">
-        <v>79077</v>
+        <v>79917</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>394313</v>
+        <v>394101</v>
       </c>
       <c r="R54" t="n">
-        <v>6728712</v>
+        <v>6728590</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5832,32 +5832,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132406850</v>
+        <v>132406815</v>
       </c>
       <c r="B55" t="n">
-        <v>78330</v>
+        <v>79085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6000248</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>394578</v>
+        <v>394482</v>
       </c>
       <c r="R55" t="n">
-        <v>6728822</v>
+        <v>6728440</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5929,10 +5929,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132406824</v>
+        <v>132406816</v>
       </c>
       <c r="B56" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>394268</v>
+        <v>394266</v>
       </c>
       <c r="R56" t="n">
-        <v>6728667</v>
+        <v>6728588</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6026,32 +6026,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132406865</v>
+        <v>132406846</v>
       </c>
       <c r="B57" t="n">
-        <v>79319</v>
+        <v>80392</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>394504</v>
+        <v>394178</v>
       </c>
       <c r="R57" t="n">
-        <v>6728428</v>
+        <v>6728650</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,10 +6123,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132406788</v>
+        <v>132406900</v>
       </c>
       <c r="B58" t="n">
-        <v>79938</v>
+        <v>83299</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>394213</v>
+        <v>394335</v>
       </c>
       <c r="R58" t="n">
-        <v>6728660</v>
+        <v>6728632</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132406846</v>
+        <v>132406788</v>
       </c>
       <c r="B59" t="n">
-        <v>80384</v>
+        <v>79946</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394178</v>
+        <v>394213</v>
       </c>
       <c r="R59" t="n">
-        <v>6728650</v>
+        <v>6728660</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406900</v>
+        <v>132406865</v>
       </c>
       <c r="B60" t="n">
-        <v>83291</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394335</v>
+        <v>394504</v>
       </c>
       <c r="R60" t="n">
-        <v>6728632</v>
+        <v>6728428</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6417,7 +6417,7 @@
         <v>132406801</v>
       </c>
       <c r="B61" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>132406786</v>
       </c>
       <c r="B62" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>132406854</v>
       </c>
       <c r="B63" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>132406802</v>
       </c>
       <c r="B64" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>132406832</v>
       </c>
       <c r="B65" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6915,32 +6915,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132406782</v>
+        <v>132406887</v>
       </c>
       <c r="B66" t="n">
-        <v>91861</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>394325</v>
+        <v>394304</v>
       </c>
       <c r="R66" t="n">
-        <v>6728655</v>
+        <v>6728722</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7012,32 +7012,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132406891</v>
+        <v>132406782</v>
       </c>
       <c r="B67" t="n">
-        <v>79319</v>
+        <v>91871</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>394509</v>
+        <v>394325</v>
       </c>
       <c r="R67" t="n">
-        <v>6728838</v>
+        <v>6728655</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7109,10 +7109,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132406887</v>
+        <v>132406891</v>
       </c>
       <c r="B68" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>394304</v>
+        <v>394509</v>
       </c>
       <c r="R68" t="n">
-        <v>6728722</v>
+        <v>6728838</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7206,10 +7206,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132406823</v>
+        <v>132406860</v>
       </c>
       <c r="B69" t="n">
-        <v>79077</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7217,21 +7217,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7241,10 +7241,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>394266</v>
+        <v>394205</v>
       </c>
       <c r="R69" t="n">
-        <v>6728609</v>
+        <v>6728648</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7303,10 +7303,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132406860</v>
+        <v>132406823</v>
       </c>
       <c r="B70" t="n">
-        <v>79319</v>
+        <v>79085</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>394205</v>
+        <v>394266</v>
       </c>
       <c r="R70" t="n">
-        <v>6728648</v>
+        <v>6728609</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7403,7 +7403,7 @@
         <v>132406872</v>
       </c>
       <c r="B71" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>132406873</v>
       </c>
       <c r="B72" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>132406895</v>
       </c>
       <c r="B73" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>132406909</v>
       </c>
       <c r="B74" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132406876</v>
+        <v>132406822</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394234</v>
+        <v>394220</v>
       </c>
       <c r="R5" t="n">
-        <v>6728610</v>
+        <v>6728660</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132406858</v>
+        <v>132406876</v>
       </c>
       <c r="B6" t="n">
         <v>79327</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394105</v>
+        <v>394234</v>
       </c>
       <c r="R6" t="n">
-        <v>6728596</v>
+        <v>6728610</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132406822</v>
+        <v>132406858</v>
       </c>
       <c r="B7" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394220</v>
+        <v>394105</v>
       </c>
       <c r="R7" t="n">
-        <v>6728660</v>
+        <v>6728596</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1362,32 +1362,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132406812</v>
+        <v>132406870</v>
       </c>
       <c r="B9" t="n">
-        <v>79351</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394226</v>
+        <v>394127</v>
       </c>
       <c r="R9" t="n">
-        <v>6728553</v>
+        <v>6728621</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132406870</v>
+        <v>132406812</v>
       </c>
       <c r="B10" t="n">
-        <v>79327</v>
+        <v>79351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>394127</v>
+        <v>394226</v>
       </c>
       <c r="R10" t="n">
-        <v>6728621</v>
+        <v>6728553</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132406796</v>
+        <v>132406896</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,42 +1567,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394255</v>
+        <v>394194</v>
       </c>
       <c r="R11" t="n">
-        <v>6728707</v>
+        <v>6728673</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1661,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132406896</v>
+        <v>132406796</v>
       </c>
       <c r="B12" t="n">
-        <v>78993</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,34 +1664,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394194</v>
+        <v>394255</v>
       </c>
       <c r="R12" t="n">
-        <v>6728673</v>
+        <v>6728707</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2146,10 +2146,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132406881</v>
+        <v>132406899</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>83299</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2157,21 +2157,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394330</v>
+        <v>394326</v>
       </c>
       <c r="R17" t="n">
-        <v>6728612</v>
+        <v>6728675</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132406866</v>
+        <v>132406881</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394232</v>
+        <v>394330</v>
       </c>
       <c r="R18" t="n">
-        <v>6728586</v>
+        <v>6728612</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132406864</v>
+        <v>132406866</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394530</v>
+        <v>394232</v>
       </c>
       <c r="R19" t="n">
-        <v>6728402</v>
+        <v>6728586</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132406899</v>
+        <v>132406864</v>
       </c>
       <c r="B20" t="n">
-        <v>83299</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2448,21 +2448,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394326</v>
+        <v>394530</v>
       </c>
       <c r="R20" t="n">
-        <v>6728675</v>
+        <v>6728402</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132406821</v>
+        <v>132406913</v>
       </c>
       <c r="B29" t="n">
-        <v>79085</v>
+        <v>78334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394200</v>
+        <v>394300</v>
       </c>
       <c r="R29" t="n">
-        <v>6728673</v>
+        <v>6728717</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132406867</v>
+        <v>132406790</v>
       </c>
       <c r="B30" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394208</v>
+        <v>394508</v>
       </c>
       <c r="R30" t="n">
-        <v>6728528</v>
+        <v>6728780</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132406857</v>
+        <v>132406867</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394275</v>
+        <v>394208</v>
       </c>
       <c r="R31" t="n">
-        <v>6728588</v>
+        <v>6728528</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3601,7 +3601,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132406879</v>
+        <v>132406857</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394255</v>
+        <v>394275</v>
       </c>
       <c r="R32" t="n">
-        <v>6728727</v>
+        <v>6728588</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132406880</v>
+        <v>132406879</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394331</v>
+        <v>394255</v>
       </c>
       <c r="R33" t="n">
-        <v>6728694</v>
+        <v>6728727</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3795,10 +3795,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132406913</v>
+        <v>132406880</v>
       </c>
       <c r="B34" t="n">
-        <v>78334</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3806,21 +3806,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394300</v>
+        <v>394331</v>
       </c>
       <c r="R34" t="n">
-        <v>6728717</v>
+        <v>6728694</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132406790</v>
+        <v>132406821</v>
       </c>
       <c r="B35" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3903,21 +3903,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394508</v>
+        <v>394200</v>
       </c>
       <c r="R35" t="n">
-        <v>6728780</v>
+        <v>6728673</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3992,7 +3992,7 @@
         <v>132406811</v>
       </c>
       <c r="B36" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132406844</v>
+        <v>132406893</v>
       </c>
       <c r="B41" t="n">
-        <v>81312</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4485,21 +4485,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394322</v>
+        <v>394568</v>
       </c>
       <c r="R41" t="n">
-        <v>6728714</v>
+        <v>6728820</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4571,32 +4571,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132406842</v>
+        <v>132406803</v>
       </c>
       <c r="B42" t="n">
-        <v>81312</v>
+        <v>79413</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1049</v>
+        <v>6450</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394087</v>
+        <v>394101</v>
       </c>
       <c r="R42" t="n">
-        <v>6728600</v>
+        <v>6728595</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4668,32 +4668,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132406893</v>
+        <v>132406806</v>
       </c>
       <c r="B43" t="n">
-        <v>79327</v>
+        <v>79413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394568</v>
+        <v>394329</v>
       </c>
       <c r="R43" t="n">
-        <v>6728820</v>
+        <v>6728656</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4765,32 +4765,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132406803</v>
+        <v>132406817</v>
       </c>
       <c r="B44" t="n">
-        <v>79413</v>
+        <v>79085</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394101</v>
+        <v>394230</v>
       </c>
       <c r="R44" t="n">
-        <v>6728595</v>
+        <v>6728542</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132406806</v>
+        <v>132406845</v>
       </c>
       <c r="B45" t="n">
-        <v>79413</v>
+        <v>80392</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6450</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394329</v>
+        <v>394182</v>
       </c>
       <c r="R45" t="n">
-        <v>6728656</v>
+        <v>6728645</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132406817</v>
+        <v>132406844</v>
       </c>
       <c r="B46" t="n">
-        <v>79085</v>
+        <v>81312</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4970,21 +4970,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394230</v>
+        <v>394322</v>
       </c>
       <c r="R46" t="n">
-        <v>6728542</v>
+        <v>6728714</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5056,32 +5056,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132406845</v>
+        <v>132406842</v>
       </c>
       <c r="B47" t="n">
-        <v>80392</v>
+        <v>81312</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394182</v>
+        <v>394087</v>
       </c>
       <c r="R47" t="n">
-        <v>6728645</v>
+        <v>6728600</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5153,10 +5153,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132406785</v>
+        <v>132406878</v>
       </c>
       <c r="B48" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5164,21 +5164,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394219</v>
+        <v>394267</v>
       </c>
       <c r="R48" t="n">
-        <v>6728660</v>
+        <v>6728664</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5250,7 +5250,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132406878</v>
+        <v>132406890</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>394267</v>
+        <v>394513</v>
       </c>
       <c r="R49" t="n">
-        <v>6728664</v>
+        <v>6728800</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5347,10 +5347,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132406890</v>
+        <v>132406824</v>
       </c>
       <c r="B50" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>394513</v>
+        <v>394268</v>
       </c>
       <c r="R50" t="n">
-        <v>6728800</v>
+        <v>6728667</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5444,32 +5444,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132406850</v>
+        <v>132406791</v>
       </c>
       <c r="B51" t="n">
-        <v>78338</v>
+        <v>79917</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6000248</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>394578</v>
+        <v>394101</v>
       </c>
       <c r="R51" t="n">
-        <v>6728822</v>
+        <v>6728590</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5541,7 +5541,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132406831</v>
+        <v>132406816</v>
       </c>
       <c r="B52" t="n">
         <v>79085</v>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>394313</v>
+        <v>394266</v>
       </c>
       <c r="R52" t="n">
-        <v>6728712</v>
+        <v>6728588</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132406824</v>
+        <v>132406815</v>
       </c>
       <c r="B53" t="n">
         <v>79085</v>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>394268</v>
+        <v>394482</v>
       </c>
       <c r="R53" t="n">
-        <v>6728667</v>
+        <v>6728440</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132406791</v>
+        <v>132406831</v>
       </c>
       <c r="B54" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>394101</v>
+        <v>394313</v>
       </c>
       <c r="R54" t="n">
-        <v>6728590</v>
+        <v>6728712</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5832,10 +5832,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132406815</v>
+        <v>132406785</v>
       </c>
       <c r="B55" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5843,21 +5843,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>394482</v>
+        <v>394219</v>
       </c>
       <c r="R55" t="n">
-        <v>6728440</v>
+        <v>6728660</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5929,32 +5929,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132406816</v>
+        <v>132406850</v>
       </c>
       <c r="B56" t="n">
-        <v>79085</v>
+        <v>78338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6000248</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>394266</v>
+        <v>394578</v>
       </c>
       <c r="R56" t="n">
-        <v>6728588</v>
+        <v>6728822</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6026,32 +6026,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132406846</v>
+        <v>132406900</v>
       </c>
       <c r="B57" t="n">
-        <v>80392</v>
+        <v>83299</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>394178</v>
+        <v>394335</v>
       </c>
       <c r="R57" t="n">
-        <v>6728650</v>
+        <v>6728632</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,10 +6123,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132406900</v>
+        <v>132406788</v>
       </c>
       <c r="B58" t="n">
-        <v>83299</v>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>394335</v>
+        <v>394213</v>
       </c>
       <c r="R58" t="n">
-        <v>6728632</v>
+        <v>6728660</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,10 +6220,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132406788</v>
+        <v>132406865</v>
       </c>
       <c r="B59" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6231,21 +6231,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394213</v>
+        <v>394504</v>
       </c>
       <c r="R59" t="n">
-        <v>6728660</v>
+        <v>6728428</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,45 +6317,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406865</v>
+        <v>132406801</v>
       </c>
       <c r="B60" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394504</v>
+        <v>394300</v>
       </c>
       <c r="R60" t="n">
-        <v>6728428</v>
+        <v>6728604</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6414,10 +6422,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132406801</v>
+        <v>132406846</v>
       </c>
       <c r="B61" t="n">
-        <v>57141</v>
+        <v>80392</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,42 +6433,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>394300</v>
+        <v>394178</v>
       </c>
       <c r="R61" t="n">
-        <v>6728604</v>
+        <v>6728650</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7015,7 +7015,7 @@
         <v>132406782</v>
       </c>
       <c r="B67" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132406873</v>
+        <v>132406895</v>
       </c>
       <c r="B72" t="n">
-        <v>79327</v>
+        <v>78993</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7508,21 +7508,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>394217</v>
+        <v>394301</v>
       </c>
       <c r="R72" t="n">
-        <v>6728660</v>
+        <v>6728610</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7594,10 +7594,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132406895</v>
+        <v>132406873</v>
       </c>
       <c r="B73" t="n">
-        <v>78993</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7605,21 +7605,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>394301</v>
+        <v>394217</v>
       </c>
       <c r="R73" t="n">
-        <v>6728610</v>
+        <v>6728660</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132406789</v>
+        <v>132406822</v>
       </c>
       <c r="B4" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394312</v>
+        <v>394220</v>
       </c>
       <c r="R4" t="n">
-        <v>6728711</v>
+        <v>6728660</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132406822</v>
+        <v>132406789</v>
       </c>
       <c r="B5" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394220</v>
+        <v>394312</v>
       </c>
       <c r="R5" t="n">
-        <v>6728660</v>
+        <v>6728711</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132406869</v>
+        <v>132406829</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394106</v>
+        <v>394324</v>
       </c>
       <c r="R13" t="n">
-        <v>6728622</v>
+        <v>6728712</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132406859</v>
+        <v>132406869</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394095</v>
+        <v>394106</v>
       </c>
       <c r="R14" t="n">
-        <v>6728614</v>
+        <v>6728622</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1952,7 +1952,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132406871</v>
+        <v>132406859</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394156</v>
+        <v>394095</v>
       </c>
       <c r="R15" t="n">
-        <v>6728616</v>
+        <v>6728614</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132406829</v>
+        <v>132406871</v>
       </c>
       <c r="B16" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,21 +2060,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394324</v>
+        <v>394156</v>
       </c>
       <c r="R16" t="n">
-        <v>6728712</v>
+        <v>6728616</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132406913</v>
+        <v>132406857</v>
       </c>
       <c r="B29" t="n">
-        <v>78334</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394300</v>
+        <v>394275</v>
       </c>
       <c r="R29" t="n">
-        <v>6728717</v>
+        <v>6728588</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132406790</v>
+        <v>132406879</v>
       </c>
       <c r="B30" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394508</v>
+        <v>394255</v>
       </c>
       <c r="R30" t="n">
-        <v>6728780</v>
+        <v>6728727</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132406867</v>
+        <v>132406880</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394208</v>
+        <v>394331</v>
       </c>
       <c r="R31" t="n">
-        <v>6728528</v>
+        <v>6728694</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132406857</v>
+        <v>132406913</v>
       </c>
       <c r="B32" t="n">
-        <v>79327</v>
+        <v>78334</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394275</v>
+        <v>394300</v>
       </c>
       <c r="R32" t="n">
-        <v>6728588</v>
+        <v>6728717</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132406879</v>
+        <v>132406790</v>
       </c>
       <c r="B33" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394255</v>
+        <v>394508</v>
       </c>
       <c r="R33" t="n">
-        <v>6728727</v>
+        <v>6728780</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3795,7 +3795,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132406880</v>
+        <v>132406867</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394331</v>
+        <v>394208</v>
       </c>
       <c r="R34" t="n">
-        <v>6728694</v>
+        <v>6728528</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132406811</v>
+        <v>132406847</v>
       </c>
       <c r="B36" t="n">
-        <v>97982</v>
+        <v>80392</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4000,21 +4000,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394327</v>
+        <v>394223</v>
       </c>
       <c r="R36" t="n">
-        <v>6728676</v>
+        <v>6728619</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132406847</v>
+        <v>132406811</v>
       </c>
       <c r="B37" t="n">
-        <v>80392</v>
+        <v>97983</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394223</v>
+        <v>394327</v>
       </c>
       <c r="R37" t="n">
-        <v>6728619</v>
+        <v>6728676</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132406817</v>
+        <v>132406844</v>
       </c>
       <c r="B44" t="n">
-        <v>79085</v>
+        <v>81312</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4776,21 +4776,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394230</v>
+        <v>394322</v>
       </c>
       <c r="R44" t="n">
-        <v>6728542</v>
+        <v>6728714</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4862,32 +4862,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132406845</v>
+        <v>132406842</v>
       </c>
       <c r="B45" t="n">
-        <v>80392</v>
+        <v>81312</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>1049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394182</v>
+        <v>394087</v>
       </c>
       <c r="R45" t="n">
-        <v>6728645</v>
+        <v>6728600</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132406844</v>
+        <v>132406817</v>
       </c>
       <c r="B46" t="n">
-        <v>81312</v>
+        <v>79085</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4970,21 +4970,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394322</v>
+        <v>394230</v>
       </c>
       <c r="R46" t="n">
-        <v>6728714</v>
+        <v>6728542</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5056,32 +5056,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132406842</v>
+        <v>132406845</v>
       </c>
       <c r="B47" t="n">
-        <v>81312</v>
+        <v>80392</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394087</v>
+        <v>394182</v>
       </c>
       <c r="R47" t="n">
-        <v>6728600</v>
+        <v>6728645</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5347,32 +5347,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132406824</v>
+        <v>132406850</v>
       </c>
       <c r="B50" t="n">
-        <v>79085</v>
+        <v>78338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6000248</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>394268</v>
+        <v>394578</v>
       </c>
       <c r="R50" t="n">
-        <v>6728667</v>
+        <v>6728822</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132406791</v>
+        <v>132406824</v>
       </c>
       <c r="B51" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5455,21 +5455,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>394101</v>
+        <v>394268</v>
       </c>
       <c r="R51" t="n">
-        <v>6728590</v>
+        <v>6728667</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132406816</v>
+        <v>132406791</v>
       </c>
       <c r="B52" t="n">
-        <v>79085</v>
+        <v>79917</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>394266</v>
+        <v>394101</v>
       </c>
       <c r="R52" t="n">
-        <v>6728588</v>
+        <v>6728590</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132406815</v>
+        <v>132406816</v>
       </c>
       <c r="B53" t="n">
         <v>79085</v>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>394482</v>
+        <v>394266</v>
       </c>
       <c r="R53" t="n">
-        <v>6728440</v>
+        <v>6728588</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5735,7 +5735,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132406831</v>
+        <v>132406815</v>
       </c>
       <c r="B54" t="n">
         <v>79085</v>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>394313</v>
+        <v>394482</v>
       </c>
       <c r="R54" t="n">
-        <v>6728712</v>
+        <v>6728440</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5832,10 +5832,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132406785</v>
+        <v>132406831</v>
       </c>
       <c r="B55" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5843,21 +5843,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>394219</v>
+        <v>394313</v>
       </c>
       <c r="R55" t="n">
-        <v>6728660</v>
+        <v>6728712</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5929,32 +5929,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132406850</v>
+        <v>132406785</v>
       </c>
       <c r="B56" t="n">
-        <v>78338</v>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6000248</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>394578</v>
+        <v>394219</v>
       </c>
       <c r="R56" t="n">
-        <v>6728822</v>
+        <v>6728660</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6123,32 +6123,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132406788</v>
+        <v>132406846</v>
       </c>
       <c r="B58" t="n">
-        <v>79946</v>
+        <v>80392</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>229497</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>394213</v>
+        <v>394178</v>
       </c>
       <c r="R58" t="n">
-        <v>6728660</v>
+        <v>6728650</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,10 +6220,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132406865</v>
+        <v>132406788</v>
       </c>
       <c r="B59" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6231,21 +6231,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394504</v>
+        <v>394213</v>
       </c>
       <c r="R59" t="n">
-        <v>6728428</v>
+        <v>6728660</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,53 +6317,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406801</v>
+        <v>132406865</v>
       </c>
       <c r="B60" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394300</v>
+        <v>394504</v>
       </c>
       <c r="R60" t="n">
-        <v>6728604</v>
+        <v>6728428</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6422,10 +6414,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132406846</v>
+        <v>132406801</v>
       </c>
       <c r="B61" t="n">
-        <v>80392</v>
+        <v>57141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6433,34 +6425,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>394178</v>
+        <v>394300</v>
       </c>
       <c r="R61" t="n">
-        <v>6728650</v>
+        <v>6728604</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6616,45 +6616,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132406854</v>
+        <v>132406802</v>
       </c>
       <c r="B63" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>394452</v>
+        <v>394104</v>
       </c>
       <c r="R63" t="n">
-        <v>6728433</v>
+        <v>6728596</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6713,53 +6721,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132406802</v>
+        <v>132406832</v>
       </c>
       <c r="B64" t="n">
-        <v>57141</v>
+        <v>79085</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>394104</v>
+        <v>394299</v>
       </c>
       <c r="R64" t="n">
-        <v>6728596</v>
+        <v>6728725</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6818,10 +6818,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132406832</v>
+        <v>132406854</v>
       </c>
       <c r="B65" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6829,21 +6829,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>394299</v>
+        <v>394452</v>
       </c>
       <c r="R65" t="n">
-        <v>6728725</v>
+        <v>6728433</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6915,10 +6915,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132406887</v>
+        <v>132406823</v>
       </c>
       <c r="B66" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6926,21 +6926,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>394304</v>
+        <v>394266</v>
       </c>
       <c r="R66" t="n">
-        <v>6728722</v>
+        <v>6728609</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132406891</v>
+        <v>132406887</v>
       </c>
       <c r="B68" t="n">
         <v>79327</v>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>394509</v>
+        <v>394304</v>
       </c>
       <c r="R68" t="n">
-        <v>6728838</v>
+        <v>6728722</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132406860</v>
+        <v>132406891</v>
       </c>
       <c r="B69" t="n">
         <v>79327</v>
@@ -7241,10 +7241,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>394205</v>
+        <v>394509</v>
       </c>
       <c r="R69" t="n">
-        <v>6728648</v>
+        <v>6728838</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7303,10 +7303,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132406823</v>
+        <v>132406860</v>
       </c>
       <c r="B70" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>394266</v>
+        <v>394205</v>
       </c>
       <c r="R70" t="n">
-        <v>6728609</v>
+        <v>6728648</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132406895</v>
+        <v>132406873</v>
       </c>
       <c r="B72" t="n">
-        <v>78993</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7508,21 +7508,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>394301</v>
+        <v>394217</v>
       </c>
       <c r="R72" t="n">
-        <v>6728610</v>
+        <v>6728660</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7594,10 +7594,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132406873</v>
+        <v>132406895</v>
       </c>
       <c r="B73" t="n">
-        <v>79327</v>
+        <v>78993</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7605,21 +7605,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>394217</v>
+        <v>394301</v>
       </c>
       <c r="R73" t="n">
-        <v>6728660</v>
+        <v>6728610</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132406896</v>
+        <v>132406829</v>
       </c>
       <c r="B11" t="n">
-        <v>78993</v>
+        <v>79085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394194</v>
+        <v>394324</v>
       </c>
       <c r="R11" t="n">
-        <v>6728673</v>
+        <v>6728712</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132406796</v>
+        <v>132406896</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,42 +1664,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394255</v>
+        <v>394194</v>
       </c>
       <c r="R12" t="n">
-        <v>6728707</v>
+        <v>6728673</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1758,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132406829</v>
+        <v>132406869</v>
       </c>
       <c r="B13" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1761,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394324</v>
+        <v>394106</v>
       </c>
       <c r="R13" t="n">
-        <v>6728712</v>
+        <v>6728622</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1855,7 +1847,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132406869</v>
+        <v>132406859</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -1890,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394106</v>
+        <v>394095</v>
       </c>
       <c r="R14" t="n">
-        <v>6728622</v>
+        <v>6728614</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1952,7 +1944,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132406859</v>
+        <v>132406871</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -1987,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394095</v>
+        <v>394156</v>
       </c>
       <c r="R15" t="n">
-        <v>6728614</v>
+        <v>6728616</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2049,10 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132406871</v>
+        <v>132406796</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,34 +2052,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394156</v>
+        <v>394255</v>
       </c>
       <c r="R16" t="n">
-        <v>6728616</v>
+        <v>6728707</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132406847</v>
+        <v>132406811</v>
       </c>
       <c r="B36" t="n">
-        <v>80392</v>
+        <v>97983</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4000,21 +4000,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394223</v>
+        <v>394327</v>
       </c>
       <c r="R36" t="n">
-        <v>6728619</v>
+        <v>6728676</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132406811</v>
+        <v>132406847</v>
       </c>
       <c r="B37" t="n">
-        <v>97983</v>
+        <v>80392</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394327</v>
+        <v>394223</v>
       </c>
       <c r="R37" t="n">
-        <v>6728676</v>
+        <v>6728619</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132406889</v>
+        <v>132406875</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394500</v>
+        <v>394228</v>
       </c>
       <c r="R39" t="n">
-        <v>6728810</v>
+        <v>6728628</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4377,7 +4377,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132406875</v>
+        <v>132406889</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394228</v>
+        <v>394500</v>
       </c>
       <c r="R40" t="n">
-        <v>6728628</v>
+        <v>6728810</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132406893</v>
+        <v>132406844</v>
       </c>
       <c r="B41" t="n">
-        <v>79327</v>
+        <v>81312</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4485,21 +4485,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394568</v>
+        <v>394322</v>
       </c>
       <c r="R41" t="n">
-        <v>6728820</v>
+        <v>6728714</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4571,32 +4571,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132406803</v>
+        <v>132406842</v>
       </c>
       <c r="B42" t="n">
-        <v>79413</v>
+        <v>81312</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6450</v>
+        <v>1049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394101</v>
+        <v>394087</v>
       </c>
       <c r="R42" t="n">
-        <v>6728595</v>
+        <v>6728600</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4668,32 +4668,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132406806</v>
+        <v>132406817</v>
       </c>
       <c r="B43" t="n">
-        <v>79413</v>
+        <v>79085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394329</v>
+        <v>394230</v>
       </c>
       <c r="R43" t="n">
-        <v>6728656</v>
+        <v>6728542</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4765,32 +4765,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132406844</v>
+        <v>132406845</v>
       </c>
       <c r="B44" t="n">
-        <v>81312</v>
+        <v>80392</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1049</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394322</v>
+        <v>394182</v>
       </c>
       <c r="R44" t="n">
-        <v>6728714</v>
+        <v>6728645</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132406842</v>
+        <v>132406893</v>
       </c>
       <c r="B45" t="n">
-        <v>81312</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394087</v>
+        <v>394568</v>
       </c>
       <c r="R45" t="n">
-        <v>6728600</v>
+        <v>6728820</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4959,32 +4959,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132406817</v>
+        <v>132406803</v>
       </c>
       <c r="B46" t="n">
-        <v>79085</v>
+        <v>79413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6450</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394230</v>
+        <v>394101</v>
       </c>
       <c r="R46" t="n">
-        <v>6728542</v>
+        <v>6728595</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5056,10 +5056,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132406845</v>
+        <v>132406806</v>
       </c>
       <c r="B47" t="n">
-        <v>80392</v>
+        <v>79413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5067,21 +5067,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>6450</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394182</v>
+        <v>394329</v>
       </c>
       <c r="R47" t="n">
-        <v>6728645</v>
+        <v>6728656</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5153,32 +5153,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132406878</v>
+        <v>132406850</v>
       </c>
       <c r="B48" t="n">
-        <v>79327</v>
+        <v>78338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6000248</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394267</v>
+        <v>394578</v>
       </c>
       <c r="R48" t="n">
-        <v>6728664</v>
+        <v>6728822</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5250,10 +5250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132406890</v>
+        <v>132406824</v>
       </c>
       <c r="B49" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5261,21 +5261,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>394513</v>
+        <v>394268</v>
       </c>
       <c r="R49" t="n">
-        <v>6728800</v>
+        <v>6728667</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5347,32 +5347,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132406850</v>
+        <v>132406791</v>
       </c>
       <c r="B50" t="n">
-        <v>78338</v>
+        <v>79917</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6000248</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>394578</v>
+        <v>394101</v>
       </c>
       <c r="R50" t="n">
-        <v>6728822</v>
+        <v>6728590</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5444,7 +5444,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132406824</v>
+        <v>132406816</v>
       </c>
       <c r="B51" t="n">
         <v>79085</v>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>394268</v>
+        <v>394266</v>
       </c>
       <c r="R51" t="n">
-        <v>6728667</v>
+        <v>6728588</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132406791</v>
+        <v>132406815</v>
       </c>
       <c r="B52" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>394101</v>
+        <v>394482</v>
       </c>
       <c r="R52" t="n">
-        <v>6728590</v>
+        <v>6728440</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132406816</v>
+        <v>132406831</v>
       </c>
       <c r="B53" t="n">
         <v>79085</v>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>394266</v>
+        <v>394313</v>
       </c>
       <c r="R53" t="n">
-        <v>6728588</v>
+        <v>6728712</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132406815</v>
+        <v>132406785</v>
       </c>
       <c r="B54" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>394482</v>
+        <v>394219</v>
       </c>
       <c r="R54" t="n">
-        <v>6728440</v>
+        <v>6728660</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5832,10 +5832,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132406831</v>
+        <v>132406878</v>
       </c>
       <c r="B55" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5843,21 +5843,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>394313</v>
+        <v>394267</v>
       </c>
       <c r="R55" t="n">
-        <v>6728712</v>
+        <v>6728664</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5929,10 +5929,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132406785</v>
+        <v>132406890</v>
       </c>
       <c r="B56" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5940,21 +5940,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>394219</v>
+        <v>394513</v>
       </c>
       <c r="R56" t="n">
-        <v>6728660</v>
+        <v>6728800</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6026,45 +6026,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132406900</v>
+        <v>132406801</v>
       </c>
       <c r="B57" t="n">
-        <v>83299</v>
+        <v>57141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>308</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>394335</v>
+        <v>394300</v>
       </c>
       <c r="R57" t="n">
-        <v>6728632</v>
+        <v>6728604</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,32 +6131,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132406846</v>
+        <v>132406788</v>
       </c>
       <c r="B58" t="n">
-        <v>80392</v>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6166,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>394178</v>
+        <v>394213</v>
       </c>
       <c r="R58" t="n">
-        <v>6728650</v>
+        <v>6728660</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,10 +6228,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132406788</v>
+        <v>132406865</v>
       </c>
       <c r="B59" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6231,21 +6239,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6263,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394213</v>
+        <v>394504</v>
       </c>
       <c r="R59" t="n">
-        <v>6728660</v>
+        <v>6728428</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6325,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406865</v>
+        <v>132406900</v>
       </c>
       <c r="B60" t="n">
-        <v>79327</v>
+        <v>83299</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6336,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6360,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394504</v>
+        <v>394335</v>
       </c>
       <c r="R60" t="n">
-        <v>6728428</v>
+        <v>6728632</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6414,10 +6422,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132406801</v>
+        <v>132406846</v>
       </c>
       <c r="B61" t="n">
-        <v>57141</v>
+        <v>80392</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,42 +6433,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>394300</v>
+        <v>394178</v>
       </c>
       <c r="R61" t="n">
-        <v>6728604</v>
+        <v>6728650</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6915,32 +6915,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132406823</v>
+        <v>132406782</v>
       </c>
       <c r="B66" t="n">
-        <v>79085</v>
+        <v>91872</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>394266</v>
+        <v>394325</v>
       </c>
       <c r="R66" t="n">
-        <v>6728609</v>
+        <v>6728655</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7012,32 +7012,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132406782</v>
+        <v>132406887</v>
       </c>
       <c r="B67" t="n">
-        <v>91872</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>394325</v>
+        <v>394304</v>
       </c>
       <c r="R67" t="n">
-        <v>6728655</v>
+        <v>6728722</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132406887</v>
+        <v>132406891</v>
       </c>
       <c r="B68" t="n">
         <v>79327</v>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>394304</v>
+        <v>394509</v>
       </c>
       <c r="R68" t="n">
-        <v>6728722</v>
+        <v>6728838</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132406891</v>
+        <v>132406860</v>
       </c>
       <c r="B69" t="n">
         <v>79327</v>
@@ -7241,10 +7241,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>394509</v>
+        <v>394205</v>
       </c>
       <c r="R69" t="n">
-        <v>6728838</v>
+        <v>6728648</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7303,10 +7303,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132406860</v>
+        <v>132406823</v>
       </c>
       <c r="B70" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>394205</v>
+        <v>394266</v>
       </c>
       <c r="R70" t="n">
-        <v>6728648</v>
+        <v>6728609</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132406822</v>
+        <v>132406789</v>
       </c>
       <c r="B4" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394220</v>
+        <v>394312</v>
       </c>
       <c r="R4" t="n">
-        <v>6728660</v>
+        <v>6728711</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132406789</v>
+        <v>132406876</v>
       </c>
       <c r="B5" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394312</v>
+        <v>394234</v>
       </c>
       <c r="R5" t="n">
-        <v>6728711</v>
+        <v>6728610</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132406876</v>
+        <v>132406858</v>
       </c>
       <c r="B6" t="n">
         <v>79327</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394234</v>
+        <v>394105</v>
       </c>
       <c r="R6" t="n">
-        <v>6728610</v>
+        <v>6728596</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132406858</v>
+        <v>132406794</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394105</v>
+        <v>394686</v>
       </c>
       <c r="R7" t="n">
-        <v>6728596</v>
+        <v>6728607</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132406794</v>
+        <v>132406822</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>79085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,42 +1276,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394686</v>
+        <v>394220</v>
       </c>
       <c r="R8" t="n">
-        <v>6728607</v>
+        <v>6728660</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132406829</v>
+        <v>132406796</v>
       </c>
       <c r="B11" t="n">
-        <v>79085</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,34 +1567,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394324</v>
+        <v>394255</v>
       </c>
       <c r="R11" t="n">
-        <v>6728712</v>
+        <v>6728707</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -2041,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132406796</v>
+        <v>132406829</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>79085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2052,42 +2060,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394255</v>
+        <v>394324</v>
       </c>
       <c r="R16" t="n">
-        <v>6728707</v>
+        <v>6728712</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132406784</v>
+        <v>132406825</v>
       </c>
       <c r="B26" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3030,21 +3030,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394200</v>
+        <v>394291</v>
       </c>
       <c r="R26" t="n">
-        <v>6728673</v>
+        <v>6728707</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3116,32 +3116,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132406807</v>
+        <v>132406784</v>
       </c>
       <c r="B27" t="n">
-        <v>79413</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394333</v>
+        <v>394200</v>
       </c>
       <c r="R27" t="n">
-        <v>6728635</v>
+        <v>6728673</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3213,32 +3213,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132406825</v>
+        <v>132406807</v>
       </c>
       <c r="B28" t="n">
-        <v>79085</v>
+        <v>79413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6450</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394291</v>
+        <v>394333</v>
       </c>
       <c r="R28" t="n">
-        <v>6728707</v>
+        <v>6728635</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132406857</v>
+        <v>132406867</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394275</v>
+        <v>394208</v>
       </c>
       <c r="R29" t="n">
-        <v>6728588</v>
+        <v>6728528</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3407,7 +3407,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132406879</v>
+        <v>132406857</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394255</v>
+        <v>394275</v>
       </c>
       <c r="R30" t="n">
-        <v>6728727</v>
+        <v>6728588</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132406913</v>
+        <v>132406790</v>
       </c>
       <c r="B32" t="n">
-        <v>78334</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394300</v>
+        <v>394508</v>
       </c>
       <c r="R32" t="n">
-        <v>6728717</v>
+        <v>6728780</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132406790</v>
+        <v>132406879</v>
       </c>
       <c r="B33" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394508</v>
+        <v>394255</v>
       </c>
       <c r="R33" t="n">
-        <v>6728780</v>
+        <v>6728727</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3795,10 +3795,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132406867</v>
+        <v>132406913</v>
       </c>
       <c r="B34" t="n">
-        <v>79327</v>
+        <v>78334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3806,21 +3806,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394208</v>
+        <v>394300</v>
       </c>
       <c r="R34" t="n">
-        <v>6728528</v>
+        <v>6728717</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132406875</v>
+        <v>132406889</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394228</v>
+        <v>394500</v>
       </c>
       <c r="R39" t="n">
-        <v>6728628</v>
+        <v>6728810</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4377,7 +4377,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132406889</v>
+        <v>132406875</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394500</v>
+        <v>394228</v>
       </c>
       <c r="R40" t="n">
-        <v>6728810</v>
+        <v>6728628</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132406817</v>
+        <v>132406893</v>
       </c>
       <c r="B43" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4679,21 +4679,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394230</v>
+        <v>394568</v>
       </c>
       <c r="R43" t="n">
-        <v>6728542</v>
+        <v>6728820</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132406845</v>
+        <v>132406803</v>
       </c>
       <c r="B44" t="n">
-        <v>80392</v>
+        <v>79413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4776,21 +4776,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>6450</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394182</v>
+        <v>394101</v>
       </c>
       <c r="R44" t="n">
-        <v>6728645</v>
+        <v>6728595</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4862,32 +4862,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132406893</v>
+        <v>132406806</v>
       </c>
       <c r="B45" t="n">
-        <v>79327</v>
+        <v>79413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394568</v>
+        <v>394329</v>
       </c>
       <c r="R45" t="n">
-        <v>6728820</v>
+        <v>6728656</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4959,32 +4959,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132406803</v>
+        <v>132406817</v>
       </c>
       <c r="B46" t="n">
-        <v>79413</v>
+        <v>79085</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394101</v>
+        <v>394230</v>
       </c>
       <c r="R46" t="n">
-        <v>6728595</v>
+        <v>6728542</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5056,10 +5056,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132406806</v>
+        <v>132406845</v>
       </c>
       <c r="B47" t="n">
-        <v>79413</v>
+        <v>80392</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5067,21 +5067,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6450</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394329</v>
+        <v>394182</v>
       </c>
       <c r="R47" t="n">
-        <v>6728656</v>
+        <v>6728645</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5153,32 +5153,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132406850</v>
+        <v>132406785</v>
       </c>
       <c r="B48" t="n">
-        <v>78338</v>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6000248</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394578</v>
+        <v>394219</v>
       </c>
       <c r="R48" t="n">
-        <v>6728822</v>
+        <v>6728660</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5250,10 +5250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132406824</v>
+        <v>132406878</v>
       </c>
       <c r="B49" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5261,21 +5261,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>394268</v>
+        <v>394267</v>
       </c>
       <c r="R49" t="n">
-        <v>6728667</v>
+        <v>6728664</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5347,10 +5347,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132406791</v>
+        <v>132406890</v>
       </c>
       <c r="B50" t="n">
-        <v>79917</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>394101</v>
+        <v>394513</v>
       </c>
       <c r="R50" t="n">
-        <v>6728590</v>
+        <v>6728800</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5444,32 +5444,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132406816</v>
+        <v>132406850</v>
       </c>
       <c r="B51" t="n">
-        <v>79085</v>
+        <v>78338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6000248</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>394266</v>
+        <v>394578</v>
       </c>
       <c r="R51" t="n">
-        <v>6728588</v>
+        <v>6728822</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5541,7 +5541,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132406815</v>
+        <v>132406831</v>
       </c>
       <c r="B52" t="n">
         <v>79085</v>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>394482</v>
+        <v>394313</v>
       </c>
       <c r="R52" t="n">
-        <v>6728440</v>
+        <v>6728712</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132406831</v>
+        <v>132406824</v>
       </c>
       <c r="B53" t="n">
         <v>79085</v>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>394313</v>
+        <v>394268</v>
       </c>
       <c r="R53" t="n">
-        <v>6728712</v>
+        <v>6728667</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132406785</v>
+        <v>132406791</v>
       </c>
       <c r="B54" t="n">
-        <v>79946</v>
+        <v>79917</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>394219</v>
+        <v>394101</v>
       </c>
       <c r="R54" t="n">
-        <v>6728660</v>
+        <v>6728590</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5832,10 +5832,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132406878</v>
+        <v>132406815</v>
       </c>
       <c r="B55" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5843,21 +5843,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>394267</v>
+        <v>394482</v>
       </c>
       <c r="R55" t="n">
-        <v>6728664</v>
+        <v>6728440</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5929,10 +5929,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132406890</v>
+        <v>132406816</v>
       </c>
       <c r="B56" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5940,21 +5940,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>394513</v>
+        <v>394266</v>
       </c>
       <c r="R56" t="n">
-        <v>6728800</v>
+        <v>6728588</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6131,10 +6131,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132406788</v>
+        <v>132406900</v>
       </c>
       <c r="B58" t="n">
-        <v>79946</v>
+        <v>83299</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6142,21 +6142,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>394213</v>
+        <v>394335</v>
       </c>
       <c r="R58" t="n">
-        <v>6728660</v>
+        <v>6728632</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6228,10 +6228,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132406865</v>
+        <v>132406788</v>
       </c>
       <c r="B59" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6239,21 +6239,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394504</v>
+        <v>394213</v>
       </c>
       <c r="R59" t="n">
-        <v>6728428</v>
+        <v>6728660</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6325,10 +6325,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406900</v>
+        <v>132406865</v>
       </c>
       <c r="B60" t="n">
-        <v>83299</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,21 +6336,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394335</v>
+        <v>394504</v>
       </c>
       <c r="R60" t="n">
-        <v>6728632</v>
+        <v>6728428</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6616,53 +6616,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132406802</v>
+        <v>132406854</v>
       </c>
       <c r="B63" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>394104</v>
+        <v>394452</v>
       </c>
       <c r="R63" t="n">
-        <v>6728596</v>
+        <v>6728433</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6721,45 +6713,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132406832</v>
+        <v>132406802</v>
       </c>
       <c r="B64" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>394299</v>
+        <v>394104</v>
       </c>
       <c r="R64" t="n">
-        <v>6728725</v>
+        <v>6728596</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6818,10 +6818,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132406854</v>
+        <v>132406832</v>
       </c>
       <c r="B65" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6829,21 +6829,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>394452</v>
+        <v>394299</v>
       </c>
       <c r="R65" t="n">
-        <v>6728433</v>
+        <v>6728725</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6915,32 +6915,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132406782</v>
+        <v>132406887</v>
       </c>
       <c r="B66" t="n">
-        <v>91872</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>394325</v>
+        <v>394304</v>
       </c>
       <c r="R66" t="n">
-        <v>6728655</v>
+        <v>6728722</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7012,32 +7012,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132406887</v>
+        <v>132406782</v>
       </c>
       <c r="B67" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>394304</v>
+        <v>394325</v>
       </c>
       <c r="R67" t="n">
-        <v>6728722</v>
+        <v>6728655</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132406873</v>
+        <v>132406895</v>
       </c>
       <c r="B72" t="n">
-        <v>79327</v>
+        <v>78993</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7508,21 +7508,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>394217</v>
+        <v>394301</v>
       </c>
       <c r="R72" t="n">
-        <v>6728660</v>
+        <v>6728610</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7594,10 +7594,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132406895</v>
+        <v>132406873</v>
       </c>
       <c r="B73" t="n">
-        <v>78993</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7605,21 +7605,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>394301</v>
+        <v>394217</v>
       </c>
       <c r="R73" t="n">
-        <v>6728610</v>
+        <v>6728660</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132406907</v>
+        <v>132406810</v>
       </c>
       <c r="B2" t="n">
-        <v>83299</v>
+        <v>80336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394350</v>
+        <v>394222</v>
       </c>
       <c r="R2" t="n">
-        <v>6728689</v>
+        <v>6728619</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132406810</v>
+        <v>132406907</v>
       </c>
       <c r="B3" t="n">
-        <v>80336</v>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394222</v>
+        <v>394350</v>
       </c>
       <c r="R3" t="n">
-        <v>6728619</v>
+        <v>6728689</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132406789</v>
+        <v>132406822</v>
       </c>
       <c r="B4" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394312</v>
+        <v>394220</v>
       </c>
       <c r="R4" t="n">
-        <v>6728711</v>
+        <v>6728660</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132406876</v>
+        <v>132406789</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394234</v>
+        <v>394312</v>
       </c>
       <c r="R5" t="n">
-        <v>6728610</v>
+        <v>6728711</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132406858</v>
+        <v>132406794</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1074,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394105</v>
+        <v>394686</v>
       </c>
       <c r="R6" t="n">
-        <v>6728596</v>
+        <v>6728607</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132406794</v>
+        <v>132406876</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,42 +1179,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394686</v>
+        <v>394234</v>
       </c>
       <c r="R7" t="n">
-        <v>6728607</v>
+        <v>6728610</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132406822</v>
+        <v>132406858</v>
       </c>
       <c r="B8" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394220</v>
+        <v>394105</v>
       </c>
       <c r="R8" t="n">
-        <v>6728660</v>
+        <v>6728596</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132406796</v>
+        <v>132406896</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,42 +1567,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394255</v>
+        <v>394194</v>
       </c>
       <c r="R11" t="n">
-        <v>6728707</v>
+        <v>6728673</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1661,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132406896</v>
+        <v>132406869</v>
       </c>
       <c r="B12" t="n">
-        <v>78993</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394194</v>
+        <v>394106</v>
       </c>
       <c r="R12" t="n">
-        <v>6728673</v>
+        <v>6728622</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1758,7 +1750,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132406869</v>
+        <v>132406859</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1793,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394106</v>
+        <v>394095</v>
       </c>
       <c r="R13" t="n">
-        <v>6728622</v>
+        <v>6728614</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1855,7 +1847,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132406859</v>
+        <v>132406871</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -1890,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394095</v>
+        <v>394156</v>
       </c>
       <c r="R14" t="n">
-        <v>6728614</v>
+        <v>6728616</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1952,10 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132406871</v>
+        <v>132406796</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,34 +1955,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394156</v>
+        <v>394255</v>
       </c>
       <c r="R15" t="n">
-        <v>6728616</v>
+        <v>6728707</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2146,10 +2146,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132406899</v>
+        <v>132406881</v>
       </c>
       <c r="B17" t="n">
-        <v>83299</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2157,21 +2157,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394326</v>
+        <v>394330</v>
       </c>
       <c r="R17" t="n">
-        <v>6728675</v>
+        <v>6728612</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132406881</v>
+        <v>132406866</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394330</v>
+        <v>394232</v>
       </c>
       <c r="R18" t="n">
-        <v>6728612</v>
+        <v>6728586</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132406866</v>
+        <v>132406864</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394232</v>
+        <v>394530</v>
       </c>
       <c r="R19" t="n">
-        <v>6728586</v>
+        <v>6728402</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132406864</v>
+        <v>132406899</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>83299</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2448,21 +2448,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394530</v>
+        <v>394326</v>
       </c>
       <c r="R20" t="n">
-        <v>6728402</v>
+        <v>6728675</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132406825</v>
+        <v>132406784</v>
       </c>
       <c r="B26" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3030,21 +3030,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394291</v>
+        <v>394200</v>
       </c>
       <c r="R26" t="n">
-        <v>6728707</v>
+        <v>6728673</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3116,32 +3116,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132406784</v>
+        <v>132406807</v>
       </c>
       <c r="B27" t="n">
-        <v>79946</v>
+        <v>79413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394200</v>
+        <v>394333</v>
       </c>
       <c r="R27" t="n">
-        <v>6728673</v>
+        <v>6728635</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3213,32 +3213,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132406807</v>
+        <v>132406825</v>
       </c>
       <c r="B28" t="n">
-        <v>79413</v>
+        <v>79085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394333</v>
+        <v>394291</v>
       </c>
       <c r="R28" t="n">
-        <v>6728635</v>
+        <v>6728707</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132406857</v>
+        <v>132406913</v>
       </c>
       <c r="B30" t="n">
-        <v>79327</v>
+        <v>78334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394275</v>
+        <v>394300</v>
       </c>
       <c r="R30" t="n">
-        <v>6728588</v>
+        <v>6728717</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132406880</v>
+        <v>132406821</v>
       </c>
       <c r="B31" t="n">
-        <v>79327</v>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3515,21 +3515,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394331</v>
+        <v>394200</v>
       </c>
       <c r="R31" t="n">
-        <v>6728694</v>
+        <v>6728673</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132406790</v>
+        <v>132406857</v>
       </c>
       <c r="B32" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394508</v>
+        <v>394275</v>
       </c>
       <c r="R32" t="n">
-        <v>6728780</v>
+        <v>6728588</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3795,10 +3795,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132406913</v>
+        <v>132406880</v>
       </c>
       <c r="B34" t="n">
-        <v>78334</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3806,21 +3806,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394300</v>
+        <v>394331</v>
       </c>
       <c r="R34" t="n">
-        <v>6728717</v>
+        <v>6728694</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132406821</v>
+        <v>132406790</v>
       </c>
       <c r="B35" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3903,21 +3903,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394200</v>
+        <v>394508</v>
       </c>
       <c r="R35" t="n">
-        <v>6728673</v>
+        <v>6728780</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132406811</v>
+        <v>132406847</v>
       </c>
       <c r="B36" t="n">
-        <v>97983</v>
+        <v>80392</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4000,21 +4000,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394327</v>
+        <v>394223</v>
       </c>
       <c r="R36" t="n">
-        <v>6728676</v>
+        <v>6728619</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132406847</v>
+        <v>132406811</v>
       </c>
       <c r="B37" t="n">
-        <v>80392</v>
+        <v>97983</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394223</v>
+        <v>394327</v>
       </c>
       <c r="R37" t="n">
-        <v>6728619</v>
+        <v>6728676</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -6026,53 +6026,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132406801</v>
+        <v>132406788</v>
       </c>
       <c r="B57" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>394300</v>
+        <v>394213</v>
       </c>
       <c r="R57" t="n">
-        <v>6728604</v>
+        <v>6728660</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6131,10 +6123,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132406900</v>
+        <v>132406865</v>
       </c>
       <c r="B58" t="n">
-        <v>83299</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6142,21 +6134,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6166,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>394335</v>
+        <v>394504</v>
       </c>
       <c r="R58" t="n">
-        <v>6728632</v>
+        <v>6728428</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6228,10 +6220,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132406788</v>
+        <v>132406900</v>
       </c>
       <c r="B59" t="n">
-        <v>79946</v>
+        <v>83299</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6239,21 +6231,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6263,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394213</v>
+        <v>394335</v>
       </c>
       <c r="R59" t="n">
-        <v>6728660</v>
+        <v>6728632</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6325,32 +6317,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406865</v>
+        <v>132406846</v>
       </c>
       <c r="B60" t="n">
-        <v>79327</v>
+        <v>80392</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6360,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394504</v>
+        <v>394178</v>
       </c>
       <c r="R60" t="n">
-        <v>6728428</v>
+        <v>6728650</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6422,10 +6414,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132406846</v>
+        <v>132406801</v>
       </c>
       <c r="B61" t="n">
-        <v>80392</v>
+        <v>57141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6433,34 +6425,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>394178</v>
+        <v>394300</v>
       </c>
       <c r="R61" t="n">
-        <v>6728650</v>
+        <v>6728604</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132406810</v>
+        <v>132406907</v>
       </c>
       <c r="B2" t="n">
-        <v>80336</v>
+        <v>83300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394222</v>
+        <v>394350</v>
       </c>
       <c r="R2" t="n">
-        <v>6728619</v>
+        <v>6728689</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132406907</v>
+        <v>132406810</v>
       </c>
       <c r="B3" t="n">
-        <v>83299</v>
+        <v>80337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394350</v>
+        <v>394222</v>
       </c>
       <c r="R3" t="n">
-        <v>6728689</v>
+        <v>6728619</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132406822</v>
+        <v>132406858</v>
       </c>
       <c r="B4" t="n">
-        <v>79085</v>
+        <v>79328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394220</v>
+        <v>394105</v>
       </c>
       <c r="R4" t="n">
-        <v>6728660</v>
+        <v>6728596</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,7 +969,7 @@
         <v>132406789</v>
       </c>
       <c r="B5" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132406794</v>
+        <v>132406876</v>
       </c>
       <c r="B6" t="n">
-        <v>57953</v>
+        <v>79328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,42 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394686</v>
+        <v>394234</v>
       </c>
       <c r="R6" t="n">
-        <v>6728607</v>
+        <v>6728610</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1168,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132406876</v>
+        <v>132406794</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>57954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1179,34 +1171,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394234</v>
+        <v>394686</v>
       </c>
       <c r="R7" t="n">
-        <v>6728610</v>
+        <v>6728607</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132406858</v>
+        <v>132406822</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>79086</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394105</v>
+        <v>394220</v>
       </c>
       <c r="R8" t="n">
-        <v>6728596</v>
+        <v>6728660</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1365,7 +1365,7 @@
         <v>132406870</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>132406812</v>
       </c>
       <c r="B10" t="n">
-        <v>79351</v>
+        <v>79352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132406896</v>
+        <v>132406859</v>
       </c>
       <c r="B11" t="n">
-        <v>78993</v>
+        <v>79328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394194</v>
+        <v>394095</v>
       </c>
       <c r="R11" t="n">
-        <v>6728673</v>
+        <v>6728614</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132406869</v>
+        <v>132406896</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>78994</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394106</v>
+        <v>394194</v>
       </c>
       <c r="R12" t="n">
-        <v>6728622</v>
+        <v>6728673</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132406859</v>
+        <v>132406869</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394095</v>
+        <v>394106</v>
       </c>
       <c r="R13" t="n">
-        <v>6728614</v>
+        <v>6728622</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1850,7 +1850,7 @@
         <v>132406871</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>132406796</v>
       </c>
       <c r="B15" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>132406829</v>
       </c>
       <c r="B16" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,10 +2146,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132406881</v>
+        <v>132406899</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>83300</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2157,21 +2157,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394330</v>
+        <v>394326</v>
       </c>
       <c r="R17" t="n">
-        <v>6728612</v>
+        <v>6728675</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132406866</v>
+        <v>132406864</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394232</v>
+        <v>394530</v>
       </c>
       <c r="R18" t="n">
-        <v>6728586</v>
+        <v>6728402</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132406864</v>
+        <v>132406866</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394530</v>
+        <v>394232</v>
       </c>
       <c r="R19" t="n">
-        <v>6728402</v>
+        <v>6728586</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132406899</v>
+        <v>132406881</v>
       </c>
       <c r="B20" t="n">
-        <v>83299</v>
+        <v>79328</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2448,21 +2448,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394326</v>
+        <v>394330</v>
       </c>
       <c r="R20" t="n">
-        <v>6728675</v>
+        <v>6728612</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2537,7 +2537,7 @@
         <v>132406863</v>
       </c>
       <c r="B21" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,32 +2631,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132406861</v>
+        <v>132406804</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>79414</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394220</v>
+        <v>394251</v>
       </c>
       <c r="R22" t="n">
-        <v>6728637</v>
+        <v>6728702</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2728,32 +2728,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132406804</v>
+        <v>132406861</v>
       </c>
       <c r="B23" t="n">
-        <v>79413</v>
+        <v>79328</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394251</v>
+        <v>394220</v>
       </c>
       <c r="R23" t="n">
-        <v>6728702</v>
+        <v>6728637</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2825,10 +2825,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132406877</v>
+        <v>132406820</v>
       </c>
       <c r="B24" t="n">
-        <v>79327</v>
+        <v>79086</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2836,21 +2836,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394260</v>
+        <v>394100</v>
       </c>
       <c r="R24" t="n">
-        <v>6728663</v>
+        <v>6728603</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132406820</v>
+        <v>132406877</v>
       </c>
       <c r="B25" t="n">
-        <v>79085</v>
+        <v>79328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2933,21 +2933,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394100</v>
+        <v>394260</v>
       </c>
       <c r="R25" t="n">
-        <v>6728603</v>
+        <v>6728663</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3022,7 +3022,7 @@
         <v>132406784</v>
       </c>
       <c r="B26" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>132406807</v>
       </c>
       <c r="B27" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>132406825</v>
       </c>
       <c r="B28" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>132406867</v>
       </c>
       <c r="B29" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132406913</v>
+        <v>132406879</v>
       </c>
       <c r="B30" t="n">
-        <v>78334</v>
+        <v>79328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394300</v>
+        <v>394255</v>
       </c>
       <c r="R30" t="n">
-        <v>6728717</v>
+        <v>6728727</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132406821</v>
+        <v>132406857</v>
       </c>
       <c r="B31" t="n">
-        <v>79085</v>
+        <v>79328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3515,21 +3515,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394200</v>
+        <v>394275</v>
       </c>
       <c r="R31" t="n">
-        <v>6728673</v>
+        <v>6728588</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132406857</v>
+        <v>132406880</v>
       </c>
       <c r="B32" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394275</v>
+        <v>394331</v>
       </c>
       <c r="R32" t="n">
-        <v>6728588</v>
+        <v>6728694</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132406879</v>
+        <v>132406913</v>
       </c>
       <c r="B33" t="n">
-        <v>79327</v>
+        <v>78335</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394255</v>
+        <v>394300</v>
       </c>
       <c r="R33" t="n">
-        <v>6728727</v>
+        <v>6728717</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3795,10 +3795,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132406880</v>
+        <v>132406790</v>
       </c>
       <c r="B34" t="n">
-        <v>79327</v>
+        <v>79947</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3806,21 +3806,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394331</v>
+        <v>394508</v>
       </c>
       <c r="R34" t="n">
-        <v>6728694</v>
+        <v>6728780</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132406790</v>
+        <v>132406821</v>
       </c>
       <c r="B35" t="n">
-        <v>79946</v>
+        <v>79086</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3903,21 +3903,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394508</v>
+        <v>394200</v>
       </c>
       <c r="R35" t="n">
-        <v>6728780</v>
+        <v>6728673</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3992,7 +3992,7 @@
         <v>132406847</v>
       </c>
       <c r="B36" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>132406811</v>
       </c>
       <c r="B37" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>132406818</v>
       </c>
       <c r="B38" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132406889</v>
+        <v>132406875</v>
       </c>
       <c r="B39" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394500</v>
+        <v>394228</v>
       </c>
       <c r="R39" t="n">
-        <v>6728810</v>
+        <v>6728628</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4377,10 +4377,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132406875</v>
+        <v>132406889</v>
       </c>
       <c r="B40" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394228</v>
+        <v>394500</v>
       </c>
       <c r="R40" t="n">
-        <v>6728628</v>
+        <v>6728810</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4477,7 +4477,7 @@
         <v>132406844</v>
       </c>
       <c r="B41" t="n">
-        <v>81312</v>
+        <v>81313</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>132406842</v>
       </c>
       <c r="B42" t="n">
-        <v>81312</v>
+        <v>81313</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4671,7 +4671,7 @@
         <v>132406893</v>
       </c>
       <c r="B43" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>132406803</v>
       </c>
       <c r="B44" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>132406806</v>
       </c>
       <c r="B45" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>132406817</v>
       </c>
       <c r="B46" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>132406845</v>
       </c>
       <c r="B47" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5153,32 +5153,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132406785</v>
+        <v>132406850</v>
       </c>
       <c r="B48" t="n">
-        <v>79946</v>
+        <v>78339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6000248</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394219</v>
+        <v>394578</v>
       </c>
       <c r="R48" t="n">
-        <v>6728660</v>
+        <v>6728822</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5250,10 +5250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132406878</v>
+        <v>132406824</v>
       </c>
       <c r="B49" t="n">
-        <v>79327</v>
+        <v>79086</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5261,21 +5261,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>394267</v>
+        <v>394268</v>
       </c>
       <c r="R49" t="n">
-        <v>6728664</v>
+        <v>6728667</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5347,10 +5347,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132406890</v>
+        <v>132406791</v>
       </c>
       <c r="B50" t="n">
-        <v>79327</v>
+        <v>79918</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>394513</v>
+        <v>394101</v>
       </c>
       <c r="R50" t="n">
-        <v>6728800</v>
+        <v>6728590</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5444,32 +5444,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132406850</v>
+        <v>132406816</v>
       </c>
       <c r="B51" t="n">
-        <v>78338</v>
+        <v>79086</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6000248</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>394578</v>
+        <v>394266</v>
       </c>
       <c r="R51" t="n">
-        <v>6728822</v>
+        <v>6728588</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132406831</v>
+        <v>132406815</v>
       </c>
       <c r="B52" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>394313</v>
+        <v>394482</v>
       </c>
       <c r="R52" t="n">
-        <v>6728712</v>
+        <v>6728440</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5638,10 +5638,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132406824</v>
+        <v>132406831</v>
       </c>
       <c r="B53" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>394268</v>
+        <v>394313</v>
       </c>
       <c r="R53" t="n">
-        <v>6728667</v>
+        <v>6728712</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132406791</v>
+        <v>132406890</v>
       </c>
       <c r="B54" t="n">
-        <v>79917</v>
+        <v>79328</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>394101</v>
+        <v>394513</v>
       </c>
       <c r="R54" t="n">
-        <v>6728590</v>
+        <v>6728800</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5832,10 +5832,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132406815</v>
+        <v>132406878</v>
       </c>
       <c r="B55" t="n">
-        <v>79085</v>
+        <v>79328</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5843,21 +5843,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>394482</v>
+        <v>394267</v>
       </c>
       <c r="R55" t="n">
-        <v>6728440</v>
+        <v>6728664</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5929,10 +5929,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132406816</v>
+        <v>132406785</v>
       </c>
       <c r="B56" t="n">
-        <v>79085</v>
+        <v>79947</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5940,21 +5940,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>394266</v>
+        <v>394219</v>
       </c>
       <c r="R56" t="n">
-        <v>6728588</v>
+        <v>6728660</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6026,10 +6026,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132406788</v>
+        <v>132406900</v>
       </c>
       <c r="B57" t="n">
-        <v>79946</v>
+        <v>83300</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6037,21 +6037,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>394213</v>
+        <v>394335</v>
       </c>
       <c r="R57" t="n">
-        <v>6728660</v>
+        <v>6728632</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6126,7 +6126,7 @@
         <v>132406865</v>
       </c>
       <c r="B58" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6220,10 +6220,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132406900</v>
+        <v>132406788</v>
       </c>
       <c r="B59" t="n">
-        <v>83299</v>
+        <v>79947</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6231,21 +6231,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394335</v>
+        <v>394213</v>
       </c>
       <c r="R59" t="n">
-        <v>6728632</v>
+        <v>6728660</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406846</v>
+        <v>132406801</v>
       </c>
       <c r="B60" t="n">
-        <v>80392</v>
+        <v>57142</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,34 +6328,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394178</v>
+        <v>394300</v>
       </c>
       <c r="R60" t="n">
-        <v>6728650</v>
+        <v>6728604</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6414,10 +6422,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132406801</v>
+        <v>132406846</v>
       </c>
       <c r="B61" t="n">
-        <v>57141</v>
+        <v>80393</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,42 +6433,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>394300</v>
+        <v>394178</v>
       </c>
       <c r="R61" t="n">
-        <v>6728604</v>
+        <v>6728650</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6522,7 +6522,7 @@
         <v>132406786</v>
       </c>
       <c r="B62" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6616,10 +6616,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132406854</v>
+        <v>132406832</v>
       </c>
       <c r="B63" t="n">
-        <v>79327</v>
+        <v>79086</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>394452</v>
+        <v>394299</v>
       </c>
       <c r="R63" t="n">
-        <v>6728433</v>
+        <v>6728725</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6713,53 +6713,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132406802</v>
+        <v>132406854</v>
       </c>
       <c r="B64" t="n">
-        <v>57141</v>
+        <v>79328</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>394104</v>
+        <v>394452</v>
       </c>
       <c r="R64" t="n">
-        <v>6728596</v>
+        <v>6728433</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6818,45 +6810,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132406832</v>
+        <v>132406802</v>
       </c>
       <c r="B65" t="n">
-        <v>79085</v>
+        <v>57142</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>394299</v>
+        <v>394104</v>
       </c>
       <c r="R65" t="n">
-        <v>6728725</v>
+        <v>6728596</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6918,7 +6918,7 @@
         <v>132406887</v>
       </c>
       <c r="B66" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7012,32 +7012,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132406782</v>
+        <v>132406891</v>
       </c>
       <c r="B67" t="n">
-        <v>91872</v>
+        <v>79328</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>394325</v>
+        <v>394509</v>
       </c>
       <c r="R67" t="n">
-        <v>6728655</v>
+        <v>6728838</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7109,10 +7109,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132406891</v>
+        <v>132406823</v>
       </c>
       <c r="B68" t="n">
-        <v>79327</v>
+        <v>79086</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7120,21 +7120,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>394509</v>
+        <v>394266</v>
       </c>
       <c r="R68" t="n">
-        <v>6728838</v>
+        <v>6728609</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7209,7 +7209,7 @@
         <v>132406860</v>
       </c>
       <c r="B69" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7303,32 +7303,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132406823</v>
+        <v>132406782</v>
       </c>
       <c r="B70" t="n">
-        <v>79085</v>
+        <v>91873</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>394266</v>
+        <v>394325</v>
       </c>
       <c r="R70" t="n">
-        <v>6728609</v>
+        <v>6728655</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7403,7 +7403,7 @@
         <v>132406872</v>
       </c>
       <c r="B71" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>132406895</v>
       </c>
       <c r="B72" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>132406873</v>
       </c>
       <c r="B73" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>132406909</v>
       </c>
       <c r="B74" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132406907</v>
+        <v>132406810</v>
       </c>
       <c r="B2" t="n">
-        <v>83300</v>
+        <v>80337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394350</v>
+        <v>394222</v>
       </c>
       <c r="R2" t="n">
-        <v>6728689</v>
+        <v>6728619</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132406810</v>
+        <v>132406907</v>
       </c>
       <c r="B3" t="n">
-        <v>80337</v>
+        <v>83302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394222</v>
+        <v>394350</v>
       </c>
       <c r="R3" t="n">
-        <v>6728619</v>
+        <v>6728689</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132406858</v>
+        <v>132406876</v>
       </c>
       <c r="B4" t="n">
         <v>79328</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394105</v>
+        <v>394234</v>
       </c>
       <c r="R4" t="n">
-        <v>6728596</v>
+        <v>6728610</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132406789</v>
+        <v>132406858</v>
       </c>
       <c r="B5" t="n">
-        <v>79947</v>
+        <v>79328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394312</v>
+        <v>394105</v>
       </c>
       <c r="R5" t="n">
-        <v>6728711</v>
+        <v>6728596</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132406876</v>
+        <v>132406822</v>
       </c>
       <c r="B6" t="n">
-        <v>79328</v>
+        <v>79086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394234</v>
+        <v>394220</v>
       </c>
       <c r="R6" t="n">
-        <v>6728610</v>
+        <v>6728660</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132406794</v>
+        <v>132406789</v>
       </c>
       <c r="B7" t="n">
-        <v>57954</v>
+        <v>79947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,42 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394686</v>
+        <v>394312</v>
       </c>
       <c r="R7" t="n">
-        <v>6728607</v>
+        <v>6728711</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1265,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132406822</v>
+        <v>132406794</v>
       </c>
       <c r="B8" t="n">
-        <v>79086</v>
+        <v>57954</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,34 +1268,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394220</v>
+        <v>394686</v>
       </c>
       <c r="R8" t="n">
-        <v>6728660</v>
+        <v>6728607</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132406859</v>
+        <v>132406896</v>
       </c>
       <c r="B11" t="n">
-        <v>79328</v>
+        <v>78994</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394095</v>
+        <v>394194</v>
       </c>
       <c r="R11" t="n">
-        <v>6728614</v>
+        <v>6728673</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132406896</v>
+        <v>132406869</v>
       </c>
       <c r="B12" t="n">
-        <v>78994</v>
+        <v>79328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394194</v>
+        <v>394106</v>
       </c>
       <c r="R12" t="n">
-        <v>6728673</v>
+        <v>6728622</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132406869</v>
+        <v>132406859</v>
       </c>
       <c r="B13" t="n">
         <v>79328</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394106</v>
+        <v>394095</v>
       </c>
       <c r="R13" t="n">
-        <v>6728622</v>
+        <v>6728614</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2149,7 +2149,7 @@
         <v>132406899</v>
       </c>
       <c r="B17" t="n">
-        <v>83300</v>
+        <v>83302</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132406864</v>
+        <v>132406881</v>
       </c>
       <c r="B18" t="n">
         <v>79328</v>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394530</v>
+        <v>394330</v>
       </c>
       <c r="R18" t="n">
-        <v>6728402</v>
+        <v>6728612</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132406881</v>
+        <v>132406864</v>
       </c>
       <c r="B20" t="n">
         <v>79328</v>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394330</v>
+        <v>394530</v>
       </c>
       <c r="R20" t="n">
-        <v>6728612</v>
+        <v>6728402</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2631,32 +2631,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132406804</v>
+        <v>132406861</v>
       </c>
       <c r="B22" t="n">
-        <v>79414</v>
+        <v>79328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394251</v>
+        <v>394220</v>
       </c>
       <c r="R22" t="n">
-        <v>6728702</v>
+        <v>6728637</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2728,32 +2728,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132406861</v>
+        <v>132406804</v>
       </c>
       <c r="B23" t="n">
-        <v>79328</v>
+        <v>79414</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394220</v>
+        <v>394251</v>
       </c>
       <c r="R23" t="n">
-        <v>6728637</v>
+        <v>6728702</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2825,10 +2825,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132406820</v>
+        <v>132406877</v>
       </c>
       <c r="B24" t="n">
-        <v>79086</v>
+        <v>79328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2836,21 +2836,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394100</v>
+        <v>394260</v>
       </c>
       <c r="R24" t="n">
-        <v>6728603</v>
+        <v>6728663</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132406877</v>
+        <v>132406820</v>
       </c>
       <c r="B25" t="n">
-        <v>79328</v>
+        <v>79086</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2933,21 +2933,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394260</v>
+        <v>394100</v>
       </c>
       <c r="R25" t="n">
-        <v>6728663</v>
+        <v>6728603</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132406784</v>
+        <v>132406825</v>
       </c>
       <c r="B26" t="n">
-        <v>79947</v>
+        <v>79086</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3030,21 +3030,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394200</v>
+        <v>394291</v>
       </c>
       <c r="R26" t="n">
-        <v>6728673</v>
+        <v>6728707</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3116,32 +3116,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132406807</v>
+        <v>132406784</v>
       </c>
       <c r="B27" t="n">
-        <v>79414</v>
+        <v>79947</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394333</v>
+        <v>394200</v>
       </c>
       <c r="R27" t="n">
-        <v>6728635</v>
+        <v>6728673</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3213,32 +3213,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132406825</v>
+        <v>132406807</v>
       </c>
       <c r="B28" t="n">
-        <v>79086</v>
+        <v>79414</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6450</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394291</v>
+        <v>394333</v>
       </c>
       <c r="R28" t="n">
-        <v>6728707</v>
+        <v>6728635</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132406857</v>
+        <v>132406880</v>
       </c>
       <c r="B31" t="n">
         <v>79328</v>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394275</v>
+        <v>394331</v>
       </c>
       <c r="R31" t="n">
-        <v>6728588</v>
+        <v>6728694</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3601,7 +3601,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132406880</v>
+        <v>132406857</v>
       </c>
       <c r="B32" t="n">
         <v>79328</v>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394331</v>
+        <v>394275</v>
       </c>
       <c r="R32" t="n">
-        <v>6728694</v>
+        <v>6728588</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132406913</v>
+        <v>132406790</v>
       </c>
       <c r="B33" t="n">
-        <v>78335</v>
+        <v>79947</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394300</v>
+        <v>394508</v>
       </c>
       <c r="R33" t="n">
-        <v>6728717</v>
+        <v>6728780</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3795,10 +3795,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132406790</v>
+        <v>132406913</v>
       </c>
       <c r="B34" t="n">
-        <v>79947</v>
+        <v>78335</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3806,21 +3806,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394508</v>
+        <v>394300</v>
       </c>
       <c r="R34" t="n">
-        <v>6728780</v>
+        <v>6728717</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132406847</v>
+        <v>132406811</v>
       </c>
       <c r="B36" t="n">
-        <v>80393</v>
+        <v>97986</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4000,21 +4000,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394223</v>
+        <v>394327</v>
       </c>
       <c r="R36" t="n">
-        <v>6728619</v>
+        <v>6728676</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132406811</v>
+        <v>132406847</v>
       </c>
       <c r="B37" t="n">
-        <v>97984</v>
+        <v>80393</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394327</v>
+        <v>394223</v>
       </c>
       <c r="R37" t="n">
-        <v>6728676</v>
+        <v>6728619</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132406875</v>
+        <v>132406889</v>
       </c>
       <c r="B39" t="n">
         <v>79328</v>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394228</v>
+        <v>394500</v>
       </c>
       <c r="R39" t="n">
-        <v>6728628</v>
+        <v>6728810</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4377,7 +4377,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132406889</v>
+        <v>132406875</v>
       </c>
       <c r="B40" t="n">
         <v>79328</v>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394500</v>
+        <v>394228</v>
       </c>
       <c r="R40" t="n">
-        <v>6728810</v>
+        <v>6728628</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132406844</v>
+        <v>132406893</v>
       </c>
       <c r="B41" t="n">
-        <v>81313</v>
+        <v>79328</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4485,21 +4485,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394322</v>
+        <v>394568</v>
       </c>
       <c r="R41" t="n">
-        <v>6728714</v>
+        <v>6728820</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4571,32 +4571,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132406842</v>
+        <v>132406803</v>
       </c>
       <c r="B42" t="n">
-        <v>81313</v>
+        <v>79414</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1049</v>
+        <v>6450</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394087</v>
+        <v>394101</v>
       </c>
       <c r="R42" t="n">
-        <v>6728600</v>
+        <v>6728595</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4668,32 +4668,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132406893</v>
+        <v>132406806</v>
       </c>
       <c r="B43" t="n">
-        <v>79328</v>
+        <v>79414</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394568</v>
+        <v>394329</v>
       </c>
       <c r="R43" t="n">
-        <v>6728820</v>
+        <v>6728656</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4765,32 +4765,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132406803</v>
+        <v>132406844</v>
       </c>
       <c r="B44" t="n">
-        <v>79414</v>
+        <v>81313</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6450</v>
+        <v>1049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394101</v>
+        <v>394322</v>
       </c>
       <c r="R44" t="n">
-        <v>6728595</v>
+        <v>6728714</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4862,32 +4862,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132406806</v>
+        <v>132406842</v>
       </c>
       <c r="B45" t="n">
-        <v>79414</v>
+        <v>81313</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6450</v>
+        <v>1049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394329</v>
+        <v>394087</v>
       </c>
       <c r="R45" t="n">
-        <v>6728656</v>
+        <v>6728600</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132406890</v>
+        <v>132406785</v>
       </c>
       <c r="B54" t="n">
-        <v>79328</v>
+        <v>79947</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>394513</v>
+        <v>394219</v>
       </c>
       <c r="R54" t="n">
-        <v>6728800</v>
+        <v>6728660</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5929,10 +5929,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132406785</v>
+        <v>132406890</v>
       </c>
       <c r="B56" t="n">
-        <v>79947</v>
+        <v>79328</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5940,21 +5940,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>394219</v>
+        <v>394513</v>
       </c>
       <c r="R56" t="n">
-        <v>6728660</v>
+        <v>6728800</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6026,10 +6026,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132406900</v>
+        <v>132406788</v>
       </c>
       <c r="B57" t="n">
-        <v>83300</v>
+        <v>79947</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6037,21 +6037,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>394335</v>
+        <v>394213</v>
       </c>
       <c r="R57" t="n">
-        <v>6728632</v>
+        <v>6728660</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6220,45 +6220,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132406788</v>
+        <v>132406801</v>
       </c>
       <c r="B59" t="n">
-        <v>79947</v>
+        <v>57142</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394213</v>
+        <v>394300</v>
       </c>
       <c r="R59" t="n">
-        <v>6728660</v>
+        <v>6728604</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6325,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406801</v>
+        <v>132406846</v>
       </c>
       <c r="B60" t="n">
-        <v>57142</v>
+        <v>80393</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,42 +6336,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394300</v>
+        <v>394178</v>
       </c>
       <c r="R60" t="n">
-        <v>6728604</v>
+        <v>6728650</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6422,32 +6422,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132406846</v>
+        <v>132406900</v>
       </c>
       <c r="B61" t="n">
-        <v>80393</v>
+        <v>83302</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>394178</v>
+        <v>394335</v>
       </c>
       <c r="R61" t="n">
-        <v>6728650</v>
+        <v>6728632</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6616,10 +6616,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132406832</v>
+        <v>132406854</v>
       </c>
       <c r="B63" t="n">
-        <v>79086</v>
+        <v>79328</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>394299</v>
+        <v>394452</v>
       </c>
       <c r="R63" t="n">
-        <v>6728725</v>
+        <v>6728433</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6713,45 +6713,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132406854</v>
+        <v>132406802</v>
       </c>
       <c r="B64" t="n">
-        <v>79328</v>
+        <v>57142</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>394452</v>
+        <v>394104</v>
       </c>
       <c r="R64" t="n">
-        <v>6728433</v>
+        <v>6728596</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6810,53 +6818,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132406802</v>
+        <v>132406832</v>
       </c>
       <c r="B65" t="n">
-        <v>57142</v>
+        <v>79086</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>394104</v>
+        <v>394299</v>
       </c>
       <c r="R65" t="n">
-        <v>6728596</v>
+        <v>6728725</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7012,32 +7012,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132406891</v>
+        <v>132406782</v>
       </c>
       <c r="B67" t="n">
-        <v>79328</v>
+        <v>91875</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>394509</v>
+        <v>394325</v>
       </c>
       <c r="R67" t="n">
-        <v>6728838</v>
+        <v>6728655</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7109,10 +7109,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132406823</v>
+        <v>132406891</v>
       </c>
       <c r="B68" t="n">
-        <v>79086</v>
+        <v>79328</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7120,21 +7120,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>394266</v>
+        <v>394509</v>
       </c>
       <c r="R68" t="n">
-        <v>6728609</v>
+        <v>6728838</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7303,32 +7303,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132406782</v>
+        <v>132406823</v>
       </c>
       <c r="B70" t="n">
-        <v>91873</v>
+        <v>79086</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>394325</v>
+        <v>394266</v>
       </c>
       <c r="R70" t="n">
-        <v>6728655</v>
+        <v>6728609</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132406810</v>
+        <v>132406907</v>
       </c>
       <c r="B2" t="n">
-        <v>80337</v>
+        <v>83303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394222</v>
+        <v>394350</v>
       </c>
       <c r="R2" t="n">
-        <v>6728619</v>
+        <v>6728689</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132406907</v>
+        <v>132406810</v>
       </c>
       <c r="B3" t="n">
-        <v>83302</v>
+        <v>80338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394350</v>
+        <v>394222</v>
       </c>
       <c r="R3" t="n">
-        <v>6728689</v>
+        <v>6728619</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132406876</v>
+        <v>132406789</v>
       </c>
       <c r="B4" t="n">
-        <v>79328</v>
+        <v>79948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394234</v>
+        <v>394312</v>
       </c>
       <c r="R4" t="n">
-        <v>6728610</v>
+        <v>6728711</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132406858</v>
+        <v>132406876</v>
       </c>
       <c r="B5" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394105</v>
+        <v>394234</v>
       </c>
       <c r="R5" t="n">
-        <v>6728596</v>
+        <v>6728610</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132406822</v>
+        <v>132406858</v>
       </c>
       <c r="B6" t="n">
-        <v>79086</v>
+        <v>79329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394220</v>
+        <v>394105</v>
       </c>
       <c r="R6" t="n">
-        <v>6728660</v>
+        <v>6728596</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132406789</v>
+        <v>132406794</v>
       </c>
       <c r="B7" t="n">
-        <v>79947</v>
+        <v>57954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394312</v>
+        <v>394686</v>
       </c>
       <c r="R7" t="n">
-        <v>6728711</v>
+        <v>6728607</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132406794</v>
+        <v>132406822</v>
       </c>
       <c r="B8" t="n">
-        <v>57954</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,42 +1276,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394686</v>
+        <v>394220</v>
       </c>
       <c r="R8" t="n">
-        <v>6728607</v>
+        <v>6728660</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1365,7 +1365,7 @@
         <v>132406870</v>
       </c>
       <c r="B9" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>132406812</v>
       </c>
       <c r="B10" t="n">
-        <v>79352</v>
+        <v>79353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>132406896</v>
       </c>
       <c r="B11" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>132406869</v>
       </c>
       <c r="B12" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>132406859</v>
       </c>
       <c r="B13" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>132406871</v>
       </c>
       <c r="B14" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>132406829</v>
       </c>
       <c r="B16" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>132406899</v>
       </c>
       <c r="B17" t="n">
-        <v>83302</v>
+        <v>83303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>132406881</v>
       </c>
       <c r="B18" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>132406866</v>
       </c>
       <c r="B19" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>132406864</v>
       </c>
       <c r="B20" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>132406863</v>
       </c>
       <c r="B21" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>132406861</v>
       </c>
       <c r="B22" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>132406804</v>
       </c>
       <c r="B23" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>132406877</v>
       </c>
       <c r="B24" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>132406820</v>
       </c>
       <c r="B25" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>132406825</v>
       </c>
       <c r="B26" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>132406784</v>
       </c>
       <c r="B27" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>132406807</v>
       </c>
       <c r="B28" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132406867</v>
+        <v>132406821</v>
       </c>
       <c r="B29" t="n">
-        <v>79328</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394208</v>
+        <v>394200</v>
       </c>
       <c r="R29" t="n">
-        <v>6728528</v>
+        <v>6728673</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132406879</v>
+        <v>132406867</v>
       </c>
       <c r="B30" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394255</v>
+        <v>394208</v>
       </c>
       <c r="R30" t="n">
-        <v>6728727</v>
+        <v>6728528</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132406880</v>
+        <v>132406857</v>
       </c>
       <c r="B31" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394331</v>
+        <v>394275</v>
       </c>
       <c r="R31" t="n">
-        <v>6728694</v>
+        <v>6728588</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132406857</v>
+        <v>132406879</v>
       </c>
       <c r="B32" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394275</v>
+        <v>394255</v>
       </c>
       <c r="R32" t="n">
-        <v>6728588</v>
+        <v>6728727</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132406790</v>
+        <v>132406880</v>
       </c>
       <c r="B33" t="n">
-        <v>79947</v>
+        <v>79329</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394508</v>
+        <v>394331</v>
       </c>
       <c r="R33" t="n">
-        <v>6728780</v>
+        <v>6728694</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3798,7 +3798,7 @@
         <v>132406913</v>
       </c>
       <c r="B34" t="n">
-        <v>78335</v>
+        <v>78336</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132406821</v>
+        <v>132406790</v>
       </c>
       <c r="B35" t="n">
-        <v>79086</v>
+        <v>79948</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3903,21 +3903,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394200</v>
+        <v>394508</v>
       </c>
       <c r="R35" t="n">
-        <v>6728673</v>
+        <v>6728780</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132406811</v>
+        <v>132406847</v>
       </c>
       <c r="B36" t="n">
-        <v>97986</v>
+        <v>80394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4000,21 +4000,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394327</v>
+        <v>394223</v>
       </c>
       <c r="R36" t="n">
-        <v>6728676</v>
+        <v>6728619</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132406847</v>
+        <v>132406811</v>
       </c>
       <c r="B37" t="n">
-        <v>80393</v>
+        <v>97987</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394223</v>
+        <v>394327</v>
       </c>
       <c r="R37" t="n">
-        <v>6728619</v>
+        <v>6728676</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4186,7 +4186,7 @@
         <v>132406818</v>
       </c>
       <c r="B38" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>132406889</v>
       </c>
       <c r="B39" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>132406875</v>
       </c>
       <c r="B40" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132406893</v>
+        <v>132406817</v>
       </c>
       <c r="B41" t="n">
-        <v>79328</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4485,21 +4485,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394568</v>
+        <v>394230</v>
       </c>
       <c r="R41" t="n">
-        <v>6728820</v>
+        <v>6728542</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4571,10 +4571,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132406803</v>
+        <v>132406845</v>
       </c>
       <c r="B42" t="n">
-        <v>79414</v>
+        <v>80394</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4582,21 +4582,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6450</v>
+        <v>229497</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394101</v>
+        <v>394182</v>
       </c>
       <c r="R42" t="n">
-        <v>6728595</v>
+        <v>6728645</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4668,32 +4668,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132406806</v>
+        <v>132406842</v>
       </c>
       <c r="B43" t="n">
-        <v>79414</v>
+        <v>81314</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6450</v>
+        <v>1049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394329</v>
+        <v>394087</v>
       </c>
       <c r="R43" t="n">
-        <v>6728656</v>
+        <v>6728600</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4768,7 +4768,7 @@
         <v>132406844</v>
       </c>
       <c r="B44" t="n">
-        <v>81313</v>
+        <v>81314</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132406842</v>
+        <v>132406893</v>
       </c>
       <c r="B45" t="n">
-        <v>81313</v>
+        <v>79329</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394087</v>
+        <v>394568</v>
       </c>
       <c r="R45" t="n">
-        <v>6728600</v>
+        <v>6728820</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4959,32 +4959,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132406817</v>
+        <v>132406803</v>
       </c>
       <c r="B46" t="n">
-        <v>79086</v>
+        <v>79415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6450</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394230</v>
+        <v>394101</v>
       </c>
       <c r="R46" t="n">
-        <v>6728542</v>
+        <v>6728595</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5056,10 +5056,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132406845</v>
+        <v>132406806</v>
       </c>
       <c r="B47" t="n">
-        <v>80393</v>
+        <v>79415</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5067,21 +5067,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>6450</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394182</v>
+        <v>394329</v>
       </c>
       <c r="R47" t="n">
-        <v>6728645</v>
+        <v>6728656</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5153,32 +5153,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132406850</v>
+        <v>132406824</v>
       </c>
       <c r="B48" t="n">
-        <v>78339</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6000248</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394578</v>
+        <v>394268</v>
       </c>
       <c r="R48" t="n">
-        <v>6728822</v>
+        <v>6728667</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5250,10 +5250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132406824</v>
+        <v>132406791</v>
       </c>
       <c r="B49" t="n">
-        <v>79086</v>
+        <v>79919</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5261,21 +5261,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>394268</v>
+        <v>394101</v>
       </c>
       <c r="R49" t="n">
-        <v>6728667</v>
+        <v>6728590</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5347,10 +5347,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132406791</v>
+        <v>132406816</v>
       </c>
       <c r="B50" t="n">
-        <v>79918</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>394101</v>
+        <v>394266</v>
       </c>
       <c r="R50" t="n">
-        <v>6728590</v>
+        <v>6728588</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132406816</v>
+        <v>132406815</v>
       </c>
       <c r="B51" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>394266</v>
+        <v>394482</v>
       </c>
       <c r="R51" t="n">
-        <v>6728588</v>
+        <v>6728440</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132406815</v>
+        <v>132406831</v>
       </c>
       <c r="B52" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>394482</v>
+        <v>394313</v>
       </c>
       <c r="R52" t="n">
-        <v>6728440</v>
+        <v>6728712</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5638,32 +5638,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132406831</v>
+        <v>132406850</v>
       </c>
       <c r="B53" t="n">
-        <v>79086</v>
+        <v>78340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6000248</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Rikkinen</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>394313</v>
+        <v>394578</v>
       </c>
       <c r="R53" t="n">
-        <v>6728712</v>
+        <v>6728822</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5738,7 +5738,7 @@
         <v>132406785</v>
       </c>
       <c r="B54" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>132406878</v>
       </c>
       <c r="B55" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>132406890</v>
       </c>
       <c r="B56" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6026,45 +6026,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132406788</v>
+        <v>132406801</v>
       </c>
       <c r="B57" t="n">
-        <v>79947</v>
+        <v>57142</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>394213</v>
+        <v>394300</v>
       </c>
       <c r="R57" t="n">
-        <v>6728660</v>
+        <v>6728604</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,10 +6131,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132406865</v>
+        <v>132406900</v>
       </c>
       <c r="B58" t="n">
-        <v>79328</v>
+        <v>83303</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6134,21 +6142,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6166,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>394504</v>
+        <v>394335</v>
       </c>
       <c r="R58" t="n">
-        <v>6728428</v>
+        <v>6728632</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,53 +6228,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132406801</v>
+        <v>132406788</v>
       </c>
       <c r="B59" t="n">
-        <v>57142</v>
+        <v>79948</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394300</v>
+        <v>394213</v>
       </c>
       <c r="R59" t="n">
-        <v>6728604</v>
+        <v>6728660</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6325,32 +6325,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406846</v>
+        <v>132406865</v>
       </c>
       <c r="B60" t="n">
-        <v>80393</v>
+        <v>79329</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394178</v>
+        <v>394504</v>
       </c>
       <c r="R60" t="n">
-        <v>6728650</v>
+        <v>6728428</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6422,32 +6422,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132406900</v>
+        <v>132406846</v>
       </c>
       <c r="B61" t="n">
-        <v>83302</v>
+        <v>80394</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>308</v>
+        <v>229497</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>394335</v>
+        <v>394178</v>
       </c>
       <c r="R61" t="n">
-        <v>6728632</v>
+        <v>6728650</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6522,7 +6522,7 @@
         <v>132406786</v>
       </c>
       <c r="B62" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>132406854</v>
       </c>
       <c r="B63" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>132406832</v>
       </c>
       <c r="B65" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>132406887</v>
       </c>
       <c r="B66" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>132406782</v>
       </c>
       <c r="B67" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>132406891</v>
       </c>
       <c r="B68" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>132406860</v>
       </c>
       <c r="B69" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>132406823</v>
       </c>
       <c r="B70" t="n">
-        <v>79086</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>132406872</v>
       </c>
       <c r="B71" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7497,10 +7497,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132406895</v>
+        <v>132406873</v>
       </c>
       <c r="B72" t="n">
-        <v>78994</v>
+        <v>79329</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7508,21 +7508,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>394301</v>
+        <v>394217</v>
       </c>
       <c r="R72" t="n">
-        <v>6728610</v>
+        <v>6728660</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7594,10 +7594,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132406873</v>
+        <v>132406895</v>
       </c>
       <c r="B73" t="n">
-        <v>79328</v>
+        <v>78995</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7605,21 +7605,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>394217</v>
+        <v>394301</v>
       </c>
       <c r="R73" t="n">
-        <v>6728660</v>
+        <v>6728610</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7694,7 +7694,7 @@
         <v>132406909</v>
       </c>
       <c r="B74" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132406810</v>
+        <v>132406781</v>
       </c>
       <c r="B2" t="n">
-        <v>80342</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>394222</v>
+        <v>394318</v>
       </c>
       <c r="R2" t="n">
-        <v>6728619</v>
+        <v>6728740</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132406907</v>
+        <v>132406909</v>
       </c>
       <c r="B3" t="n">
-        <v>83307</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>394350</v>
+        <v>394279</v>
       </c>
       <c r="R3" t="n">
-        <v>6728689</v>
+        <v>6728740</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -851,6 +851,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132406794</v>
+        <v>119382199</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,45 +881,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öst långavhallasätern, Vrm</t>
+          <t>Öst Långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>394686</v>
+        <v>394334</v>
       </c>
       <c r="R4" t="n">
-        <v>6728607</v>
+        <v>6728534</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -942,12 +935,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -962,22 +955,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132406822</v>
+        <v>132406899</v>
       </c>
       <c r="B5" t="n">
-        <v>79091</v>
+        <v>83350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>394220</v>
+        <v>394326</v>
       </c>
       <c r="R5" t="n">
-        <v>6728660</v>
+        <v>6728675</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1071,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132406789</v>
+        <v>132406900</v>
       </c>
       <c r="B6" t="n">
-        <v>79952</v>
+        <v>83350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>394312</v>
+        <v>394335</v>
       </c>
       <c r="R6" t="n">
-        <v>6728711</v>
+        <v>6728632</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1168,10 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132406876</v>
+        <v>132406905</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>83350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1179,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>394234</v>
+        <v>394398</v>
       </c>
       <c r="R7" t="n">
-        <v>6728610</v>
+        <v>6728662</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1265,10 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132406858</v>
+        <v>132406907</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>83350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,21 +1269,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1300,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>394105</v>
+        <v>394350</v>
       </c>
       <c r="R8" t="n">
-        <v>6728596</v>
+        <v>6728689</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1362,10 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132406870</v>
+        <v>132406908</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>83350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1373,21 +1366,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1397,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>394127</v>
+        <v>394537</v>
       </c>
       <c r="R9" t="n">
-        <v>6728621</v>
+        <v>6728856</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1459,32 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132406812</v>
+        <v>132406895</v>
       </c>
       <c r="B10" t="n">
-        <v>79357</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1494,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>394226</v>
+        <v>394301</v>
       </c>
       <c r="R10" t="n">
-        <v>6728553</v>
+        <v>6728610</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1556,10 +1549,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132406829</v>
+        <v>132406896</v>
       </c>
       <c r="B11" t="n">
-        <v>79091</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,21 +1560,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>394324</v>
+        <v>394194</v>
       </c>
       <c r="R11" t="n">
-        <v>6728712</v>
+        <v>6728673</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1653,10 +1646,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132406796</v>
+        <v>132406842</v>
       </c>
       <c r="B12" t="n">
-        <v>57958</v>
+        <v>81355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,42 +1657,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>394255</v>
+        <v>394087</v>
       </c>
       <c r="R12" t="n">
-        <v>6728707</v>
+        <v>6728600</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1758,10 +1743,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132406869</v>
+        <v>132406844</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>81355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1754,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394106</v>
+        <v>394322</v>
       </c>
       <c r="R13" t="n">
-        <v>6728622</v>
+        <v>6728714</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1855,32 +1840,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132406859</v>
+        <v>132406782</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>91937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>394095</v>
+        <v>394325</v>
       </c>
       <c r="R14" t="n">
-        <v>6728614</v>
+        <v>6728655</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1952,32 +1937,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132406871</v>
+        <v>132406783</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>91937</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1972,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>394156</v>
+        <v>394393</v>
       </c>
       <c r="R15" t="n">
-        <v>6728616</v>
+        <v>6728679</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2049,45 +2034,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132406896</v>
+        <v>119382206</v>
       </c>
       <c r="B16" t="n">
-        <v>78999</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öst långavhallasätern, Vrm</t>
+          <t>Öst Långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>394194</v>
+        <v>394426</v>
       </c>
       <c r="R16" t="n">
-        <v>6728673</v>
+        <v>6728390</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2114,12 +2099,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2134,44 +2119,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132406899</v>
+        <v>132406854</v>
       </c>
       <c r="B17" t="n">
-        <v>83307</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394326</v>
+        <v>394452</v>
       </c>
       <c r="R17" t="n">
-        <v>6728675</v>
+        <v>6728433</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2243,14 +2228,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132406881</v>
+        <v>132406857</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2278,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394330</v>
+        <v>394275</v>
       </c>
       <c r="R18" t="n">
-        <v>6728612</v>
+        <v>6728588</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2340,14 +2325,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132406866</v>
+        <v>132406858</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2375,10 +2360,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394232</v>
+        <v>394105</v>
       </c>
       <c r="R19" t="n">
-        <v>6728586</v>
+        <v>6728596</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2437,14 +2422,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132406864</v>
+        <v>132406859</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2472,10 +2457,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394530</v>
+        <v>394095</v>
       </c>
       <c r="R20" t="n">
-        <v>6728402</v>
+        <v>6728614</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2534,14 +2519,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132406863</v>
+        <v>132406860</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2569,10 +2554,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394633</v>
+        <v>394205</v>
       </c>
       <c r="R21" t="n">
-        <v>6728442</v>
+        <v>6728648</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2634,11 +2619,11 @@
         <v>132406861</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2728,32 +2713,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132406804</v>
+        <v>132406862</v>
       </c>
       <c r="B23" t="n">
-        <v>79419</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2763,10 +2748,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394251</v>
+        <v>394674</v>
       </c>
       <c r="R23" t="n">
-        <v>6728702</v>
+        <v>6728647</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2825,14 +2810,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132406877</v>
+        <v>132406863</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2860,10 +2845,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394260</v>
+        <v>394633</v>
       </c>
       <c r="R24" t="n">
-        <v>6728663</v>
+        <v>6728442</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2922,32 +2907,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132406820</v>
+        <v>132406864</v>
       </c>
       <c r="B25" t="n">
-        <v>79091</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2957,10 +2942,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394100</v>
+        <v>394530</v>
       </c>
       <c r="R25" t="n">
-        <v>6728603</v>
+        <v>6728402</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3019,32 +3004,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132406784</v>
+        <v>132406865</v>
       </c>
       <c r="B26" t="n">
-        <v>79952</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3054,10 +3039,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394200</v>
+        <v>394504</v>
       </c>
       <c r="R26" t="n">
-        <v>6728673</v>
+        <v>6728428</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3116,32 +3101,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132406807</v>
+        <v>132406866</v>
       </c>
       <c r="B27" t="n">
-        <v>79419</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3151,10 +3136,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394333</v>
+        <v>394232</v>
       </c>
       <c r="R27" t="n">
-        <v>6728635</v>
+        <v>6728586</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3213,32 +3198,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132406825</v>
+        <v>132406867</v>
       </c>
       <c r="B28" t="n">
-        <v>79091</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3248,10 +3233,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394291</v>
+        <v>394208</v>
       </c>
       <c r="R28" t="n">
-        <v>6728707</v>
+        <v>6728528</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3310,14 +3295,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132406867</v>
+        <v>132406868</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3345,10 +3330,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394208</v>
+        <v>394102</v>
       </c>
       <c r="R29" t="n">
-        <v>6728528</v>
+        <v>6728577</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3407,14 +3392,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132406857</v>
+        <v>132406869</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3442,10 +3427,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394275</v>
+        <v>394106</v>
       </c>
       <c r="R30" t="n">
-        <v>6728588</v>
+        <v>6728622</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3504,14 +3489,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132406879</v>
+        <v>132406870</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3539,10 +3524,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394255</v>
+        <v>394127</v>
       </c>
       <c r="R31" t="n">
-        <v>6728727</v>
+        <v>6728621</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3601,14 +3586,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132406880</v>
+        <v>132406871</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3636,10 +3621,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394331</v>
+        <v>394156</v>
       </c>
       <c r="R32" t="n">
-        <v>6728694</v>
+        <v>6728616</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3698,32 +3683,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132406913</v>
+        <v>132406872</v>
       </c>
       <c r="B33" t="n">
-        <v>78340</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3718,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394300</v>
+        <v>394181</v>
       </c>
       <c r="R33" t="n">
-        <v>6728717</v>
+        <v>6728656</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3795,32 +3780,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132406790</v>
+        <v>132406873</v>
       </c>
       <c r="B34" t="n">
-        <v>79952</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3830,10 +3815,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394508</v>
+        <v>394217</v>
       </c>
       <c r="R34" t="n">
-        <v>6728780</v>
+        <v>6728660</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3892,32 +3877,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132406821</v>
+        <v>132406875</v>
       </c>
       <c r="B35" t="n">
-        <v>79091</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3927,10 +3912,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394200</v>
+        <v>394228</v>
       </c>
       <c r="R35" t="n">
-        <v>6728673</v>
+        <v>6728628</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3989,32 +3974,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132406847</v>
+        <v>132406876</v>
       </c>
       <c r="B36" t="n">
-        <v>80398</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4024,10 +4009,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394223</v>
+        <v>394234</v>
       </c>
       <c r="R36" t="n">
-        <v>6728619</v>
+        <v>6728610</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4086,32 +4071,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132406811</v>
+        <v>132406877</v>
       </c>
       <c r="B37" t="n">
-        <v>97995</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4121,10 +4106,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394327</v>
+        <v>394260</v>
       </c>
       <c r="R37" t="n">
-        <v>6728676</v>
+        <v>6728663</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4183,32 +4168,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132406818</v>
+        <v>132406878</v>
       </c>
       <c r="B38" t="n">
-        <v>79091</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4218,10 +4203,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394232</v>
+        <v>394267</v>
       </c>
       <c r="R38" t="n">
-        <v>6728542</v>
+        <v>6728664</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4280,14 +4265,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132406889</v>
+        <v>132406879</v>
       </c>
       <c r="B39" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4315,10 +4300,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394500</v>
+        <v>394255</v>
       </c>
       <c r="R39" t="n">
-        <v>6728810</v>
+        <v>6728727</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4377,14 +4362,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132406875</v>
+        <v>132406880</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4412,10 +4397,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394228</v>
+        <v>394331</v>
       </c>
       <c r="R40" t="n">
-        <v>6728628</v>
+        <v>6728694</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4474,14 +4459,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132406893</v>
+        <v>132406881</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4509,10 +4494,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394568</v>
+        <v>394330</v>
       </c>
       <c r="R41" t="n">
-        <v>6728820</v>
+        <v>6728612</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4571,32 +4556,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132406803</v>
+        <v>132406882</v>
       </c>
       <c r="B42" t="n">
-        <v>79419</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4606,10 +4591,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394101</v>
+        <v>394311</v>
       </c>
       <c r="R42" t="n">
-        <v>6728595</v>
+        <v>6728550</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4668,32 +4653,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132406806</v>
+        <v>132406883</v>
       </c>
       <c r="B43" t="n">
-        <v>79419</v>
+        <v>79373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4703,10 +4688,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394329</v>
+        <v>394348</v>
       </c>
       <c r="R43" t="n">
-        <v>6728656</v>
+        <v>6728555</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4765,32 +4750,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132406844</v>
+        <v>132406884</v>
       </c>
       <c r="B44" t="n">
-        <v>81318</v>
+        <v>79373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4800,10 +4785,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394322</v>
+        <v>394355</v>
       </c>
       <c r="R44" t="n">
-        <v>6728714</v>
+        <v>6728562</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4862,32 +4847,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132406842</v>
+        <v>132406885</v>
       </c>
       <c r="B45" t="n">
-        <v>81318</v>
+        <v>79373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4897,10 +4882,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394087</v>
+        <v>394365</v>
       </c>
       <c r="R45" t="n">
-        <v>6728600</v>
+        <v>6728551</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4959,32 +4944,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132406817</v>
+        <v>132406887</v>
       </c>
       <c r="B46" t="n">
-        <v>79091</v>
+        <v>79373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4994,10 +4979,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394230</v>
+        <v>394304</v>
       </c>
       <c r="R46" t="n">
-        <v>6728542</v>
+        <v>6728722</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5056,32 +5041,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132406845</v>
+        <v>132406888</v>
       </c>
       <c r="B47" t="n">
-        <v>80398</v>
+        <v>79373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5091,10 +5076,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394182</v>
+        <v>394326</v>
       </c>
       <c r="R47" t="n">
-        <v>6728645</v>
+        <v>6728740</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5153,32 +5138,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132406850</v>
+        <v>132406889</v>
       </c>
       <c r="B48" t="n">
-        <v>78344</v>
+        <v>79373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6000248</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5188,10 +5173,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394578</v>
+        <v>394500</v>
       </c>
       <c r="R48" t="n">
-        <v>6728822</v>
+        <v>6728810</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5250,32 +5235,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132406785</v>
+        <v>132406890</v>
       </c>
       <c r="B49" t="n">
-        <v>79952</v>
+        <v>79373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5285,10 +5270,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>394219</v>
+        <v>394513</v>
       </c>
       <c r="R49" t="n">
-        <v>6728660</v>
+        <v>6728800</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5347,14 +5332,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132406878</v>
+        <v>132406891</v>
       </c>
       <c r="B50" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5382,10 +5367,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>394267</v>
+        <v>394509</v>
       </c>
       <c r="R50" t="n">
-        <v>6728664</v>
+        <v>6728838</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5444,14 +5429,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132406890</v>
+        <v>132406892</v>
       </c>
       <c r="B51" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5479,10 +5464,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>394513</v>
+        <v>394552</v>
       </c>
       <c r="R51" t="n">
-        <v>6728800</v>
+        <v>6728861</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5541,32 +5526,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132406824</v>
+        <v>132406893</v>
       </c>
       <c r="B52" t="n">
-        <v>79091</v>
+        <v>79373</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5576,10 +5561,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>394268</v>
+        <v>394568</v>
       </c>
       <c r="R52" t="n">
-        <v>6728667</v>
+        <v>6728820</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5638,32 +5623,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132406791</v>
+        <v>132406812</v>
       </c>
       <c r="B53" t="n">
-        <v>79923</v>
+        <v>79397</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5673,10 +5658,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>394101</v>
+        <v>394226</v>
       </c>
       <c r="R53" t="n">
-        <v>6728590</v>
+        <v>6728553</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5735,32 +5720,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132406816</v>
+        <v>132406813</v>
       </c>
       <c r="B54" t="n">
-        <v>79091</v>
+        <v>79397</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5770,10 +5755,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>394266</v>
+        <v>394324</v>
       </c>
       <c r="R54" t="n">
-        <v>6728588</v>
+        <v>6728717</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5832,10 +5817,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132406815</v>
+        <v>119382194</v>
       </c>
       <c r="B55" t="n">
-        <v>79091</v>
+        <v>78730</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5843,37 +5828,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Öst långavhallasätern, Vrm</t>
+          <t>Öst Långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>394482</v>
+        <v>394180</v>
       </c>
       <c r="R55" t="n">
-        <v>6728440</v>
+        <v>6728494</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5897,12 +5882,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5917,60 +5902,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132406831</v>
+        <v>119382198</v>
       </c>
       <c r="B56" t="n">
-        <v>79091</v>
+        <v>83290</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6439</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Öst långavhallasätern, Vrm</t>
+          <t>Öst Långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>394313</v>
+        <v>394334</v>
       </c>
       <c r="R56" t="n">
-        <v>6728712</v>
+        <v>6728532</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5994,12 +5979,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6014,22 +5999,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132406801</v>
+        <v>132406851</v>
       </c>
       <c r="B57" t="n">
-        <v>57145</v>
+        <v>83341</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6037,42 +6022,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6439</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>394300</v>
+        <v>394369</v>
       </c>
       <c r="R57" t="n">
-        <v>6728604</v>
+        <v>6728684</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6131,32 +6108,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132406846</v>
+        <v>132406780</v>
       </c>
       <c r="B58" t="n">
-        <v>80398</v>
+        <v>83358</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6166,10 +6143,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>394178</v>
+        <v>394564</v>
       </c>
       <c r="R58" t="n">
-        <v>6728650</v>
+        <v>6728842</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6228,10 +6205,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132406788</v>
+        <v>119382193</v>
       </c>
       <c r="B59" t="n">
-        <v>79952</v>
+        <v>79084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6239,37 +6216,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Öst långavhallasätern, Vrm</t>
+          <t>Öst Långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394213</v>
+        <v>394189</v>
       </c>
       <c r="R59" t="n">
-        <v>6728660</v>
+        <v>6728499</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6293,12 +6270,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6313,22 +6290,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406865</v>
+        <v>132406849</v>
       </c>
       <c r="B60" t="n">
-        <v>79333</v>
+        <v>79130</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,21 +6313,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6360,10 +6337,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394504</v>
+        <v>394189</v>
       </c>
       <c r="R60" t="n">
-        <v>6728428</v>
+        <v>6728492</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6422,10 +6399,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132406900</v>
+        <v>132406803</v>
       </c>
       <c r="B61" t="n">
-        <v>83307</v>
+        <v>79459</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6433,21 +6410,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>308</v>
+        <v>6450</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6457,10 +6434,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>394335</v>
+        <v>394101</v>
       </c>
       <c r="R61" t="n">
-        <v>6728632</v>
+        <v>6728595</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6519,10 +6496,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132406786</v>
+        <v>132406804</v>
       </c>
       <c r="B62" t="n">
-        <v>79952</v>
+        <v>79459</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6530,21 +6507,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6554,10 +6531,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>394302</v>
+        <v>394251</v>
       </c>
       <c r="R62" t="n">
-        <v>6728723</v>
+        <v>6728702</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6616,10 +6593,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132406854</v>
+        <v>132406806</v>
       </c>
       <c r="B63" t="n">
-        <v>79333</v>
+        <v>79459</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6627,21 +6604,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6651,10 +6628,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>394452</v>
+        <v>394329</v>
       </c>
       <c r="R63" t="n">
-        <v>6728433</v>
+        <v>6728656</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6713,53 +6690,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132406802</v>
+        <v>132406807</v>
       </c>
       <c r="B64" t="n">
-        <v>57145</v>
+        <v>79459</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>6450</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>394104</v>
+        <v>394333</v>
       </c>
       <c r="R64" t="n">
-        <v>6728596</v>
+        <v>6728635</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6818,10 +6787,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132406832</v>
+        <v>132406784</v>
       </c>
       <c r="B65" t="n">
-        <v>79091</v>
+        <v>79992</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6829,21 +6798,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6853,10 +6822,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>394299</v>
+        <v>394200</v>
       </c>
       <c r="R65" t="n">
-        <v>6728725</v>
+        <v>6728673</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6915,10 +6884,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132406887</v>
+        <v>132406785</v>
       </c>
       <c r="B66" t="n">
-        <v>79333</v>
+        <v>79992</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6926,21 +6895,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6950,10 +6919,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>394304</v>
+        <v>394219</v>
       </c>
       <c r="R66" t="n">
-        <v>6728722</v>
+        <v>6728660</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7012,10 +6981,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132406891</v>
+        <v>132406786</v>
       </c>
       <c r="B67" t="n">
-        <v>79333</v>
+        <v>79992</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7023,21 +6992,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7047,10 +7016,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>394509</v>
+        <v>394302</v>
       </c>
       <c r="R67" t="n">
-        <v>6728838</v>
+        <v>6728723</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7109,10 +7078,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132406860</v>
+        <v>132406788</v>
       </c>
       <c r="B68" t="n">
-        <v>79333</v>
+        <v>79992</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7120,21 +7089,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7144,10 +7113,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>394205</v>
+        <v>394213</v>
       </c>
       <c r="R68" t="n">
-        <v>6728648</v>
+        <v>6728660</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7206,10 +7175,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132406823</v>
+        <v>132406789</v>
       </c>
       <c r="B69" t="n">
-        <v>79091</v>
+        <v>79992</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7217,21 +7186,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7241,10 +7210,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>394266</v>
+        <v>394312</v>
       </c>
       <c r="R69" t="n">
-        <v>6728609</v>
+        <v>6728711</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7303,32 +7272,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132406782</v>
+        <v>132406790</v>
       </c>
       <c r="B70" t="n">
-        <v>91881</v>
+        <v>79992</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7338,10 +7307,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>394325</v>
+        <v>394508</v>
       </c>
       <c r="R70" t="n">
-        <v>6728655</v>
+        <v>6728780</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7400,32 +7369,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132406872</v>
+        <v>132406810</v>
       </c>
       <c r="B71" t="n">
-        <v>79333</v>
+        <v>80382</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7435,10 +7404,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>394181</v>
+        <v>394222</v>
       </c>
       <c r="R71" t="n">
-        <v>6728656</v>
+        <v>6728619</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7497,32 +7466,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132406873</v>
+        <v>132406897</v>
       </c>
       <c r="B72" t="n">
-        <v>79333</v>
+        <v>80382</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7532,10 +7501,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>394217</v>
+        <v>394323</v>
       </c>
       <c r="R72" t="n">
-        <v>6728660</v>
+        <v>6728536</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7576,6 +7545,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7594,10 +7564,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132406895</v>
+        <v>132406837</v>
       </c>
       <c r="B73" t="n">
-        <v>78999</v>
+        <v>80488</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7605,21 +7575,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7629,10 +7599,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>394301</v>
+        <v>394323</v>
       </c>
       <c r="R73" t="n">
-        <v>6728610</v>
+        <v>6728533</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7691,10 +7661,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132406909</v>
+        <v>132406838</v>
       </c>
       <c r="B74" t="n">
-        <v>79365</v>
+        <v>80488</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7702,21 +7672,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7726,10 +7696,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>394279</v>
+        <v>394323</v>
       </c>
       <c r="R74" t="n">
-        <v>6728740</v>
+        <v>6728536</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7770,7 +7740,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7786,6 +7755,3668 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>132406839</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>394689</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6728620</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>132406840</v>
+      </c>
+      <c r="B76" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>394333</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6728543</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>132406913</v>
+      </c>
+      <c r="B77" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>394300</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6728717</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>132406792</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>394390</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6728685</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>132406794</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>394686</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6728607</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>132406795</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>394414</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6728473</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>132406796</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>394255</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6728707</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>132406797</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>394353</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6728558</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>132406799</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>394395</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6728610</v>
+      </c>
+      <c r="S83" t="n">
+        <v>25</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>132406800</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>394395</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6728615</v>
+      </c>
+      <c r="S84" t="n">
+        <v>25</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>132406801</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>394300</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6728604</v>
+      </c>
+      <c r="S85" t="n">
+        <v>25</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>132406802</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>394104</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6728596</v>
+      </c>
+      <c r="S86" t="n">
+        <v>25</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>132406811</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>394327</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6728676</v>
+      </c>
+      <c r="S87" t="n">
+        <v>25</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>132406815</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>394482</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6728440</v>
+      </c>
+      <c r="S88" t="n">
+        <v>25</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>132406816</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>394266</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6728588</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>132406817</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>394230</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6728542</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>132406818</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>394232</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6728542</v>
+      </c>
+      <c r="S91" t="n">
+        <v>25</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>132406819</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>394191</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6728490</v>
+      </c>
+      <c r="S92" t="n">
+        <v>25</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>132406820</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>394100</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6728603</v>
+      </c>
+      <c r="S93" t="n">
+        <v>25</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>132406821</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>394200</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6728673</v>
+      </c>
+      <c r="S94" t="n">
+        <v>25</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>132406822</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>394220</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6728660</v>
+      </c>
+      <c r="S95" t="n">
+        <v>25</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>132406823</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>394266</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6728609</v>
+      </c>
+      <c r="S96" t="n">
+        <v>25</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>132406824</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>394268</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6728667</v>
+      </c>
+      <c r="S97" t="n">
+        <v>25</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>132406825</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>394291</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6728707</v>
+      </c>
+      <c r="S98" t="n">
+        <v>25</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>132406828</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>394371</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6728698</v>
+      </c>
+      <c r="S99" t="n">
+        <v>25</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>132406829</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>394324</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6728712</v>
+      </c>
+      <c r="S100" t="n">
+        <v>25</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>132406830</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>394321</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6728718</v>
+      </c>
+      <c r="S101" t="n">
+        <v>25</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>132406831</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>394313</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6728712</v>
+      </c>
+      <c r="S102" t="n">
+        <v>25</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>132406832</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>394299</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6728725</v>
+      </c>
+      <c r="S103" t="n">
+        <v>25</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>132406834</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>394410</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6728838</v>
+      </c>
+      <c r="S104" t="n">
+        <v>25</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>132406845</v>
+      </c>
+      <c r="B105" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>394182</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6728645</v>
+      </c>
+      <c r="S105" t="n">
+        <v>25</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>132406846</v>
+      </c>
+      <c r="B106" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>394178</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6728650</v>
+      </c>
+      <c r="S106" t="n">
+        <v>25</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>132406847</v>
+      </c>
+      <c r="B107" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>394223</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6728619</v>
+      </c>
+      <c r="S107" t="n">
+        <v>25</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>132406848</v>
+      </c>
+      <c r="B108" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>394323</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6728536</v>
+      </c>
+      <c r="S108" t="n">
+        <v>25</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>132406791</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>394101</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6728590</v>
+      </c>
+      <c r="S109" t="n">
+        <v>25</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>132406835</v>
+      </c>
+      <c r="B110" t="n">
+        <v>78381</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>394389</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6728679</v>
+      </c>
+      <c r="S110" t="n">
+        <v>25</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>132406850</v>
+      </c>
+      <c r="B111" t="n">
+        <v>78381</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>394578</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6728822</v>
+      </c>
+      <c r="S111" t="n">
+        <v>25</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY111"/>
+  <dimension ref="A1:AY113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2131,7 +2131,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132406854</v>
+        <v>132406852</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>394452</v>
+        <v>394346</v>
       </c>
       <c r="R17" t="n">
-        <v>6728433</v>
+        <v>6728549</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2204,12 +2204,18 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Garnlavstrassel</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2228,7 +2234,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132406857</v>
+        <v>132406853</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2263,10 +2269,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>394275</v>
+        <v>394259</v>
       </c>
       <c r="R18" t="n">
-        <v>6728588</v>
+        <v>6728658</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2301,12 +2307,18 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Garnlavstrassel</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2325,7 +2337,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132406858</v>
+        <v>132406854</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2360,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>394105</v>
+        <v>394452</v>
       </c>
       <c r="R19" t="n">
-        <v>6728596</v>
+        <v>6728433</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2422,7 +2434,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132406859</v>
+        <v>132406857</v>
       </c>
       <c r="B20" t="n">
         <v>79373</v>
@@ -2457,10 +2469,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>394095</v>
+        <v>394275</v>
       </c>
       <c r="R20" t="n">
-        <v>6728614</v>
+        <v>6728588</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2519,7 +2531,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132406860</v>
+        <v>132406858</v>
       </c>
       <c r="B21" t="n">
         <v>79373</v>
@@ -2554,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>394205</v>
+        <v>394105</v>
       </c>
       <c r="R21" t="n">
-        <v>6728648</v>
+        <v>6728596</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2616,7 +2628,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132406861</v>
+        <v>132406859</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2651,10 +2663,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>394220</v>
+        <v>394095</v>
       </c>
       <c r="R22" t="n">
-        <v>6728637</v>
+        <v>6728614</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2713,7 +2725,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132406862</v>
+        <v>132406860</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2748,10 +2760,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>394674</v>
+        <v>394205</v>
       </c>
       <c r="R23" t="n">
-        <v>6728647</v>
+        <v>6728648</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2810,7 +2822,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132406863</v>
+        <v>132406861</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -2845,10 +2857,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>394633</v>
+        <v>394220</v>
       </c>
       <c r="R24" t="n">
-        <v>6728442</v>
+        <v>6728637</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2907,7 +2919,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132406864</v>
+        <v>132406862</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -2942,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>394530</v>
+        <v>394674</v>
       </c>
       <c r="R25" t="n">
-        <v>6728402</v>
+        <v>6728647</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3004,7 +3016,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132406865</v>
+        <v>132406863</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3039,10 +3051,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>394504</v>
+        <v>394633</v>
       </c>
       <c r="R26" t="n">
-        <v>6728428</v>
+        <v>6728442</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3101,7 +3113,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132406866</v>
+        <v>132406864</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3136,10 +3148,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>394232</v>
+        <v>394530</v>
       </c>
       <c r="R27" t="n">
-        <v>6728586</v>
+        <v>6728402</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3198,7 +3210,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132406867</v>
+        <v>132406865</v>
       </c>
       <c r="B28" t="n">
         <v>79373</v>
@@ -3233,10 +3245,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>394208</v>
+        <v>394504</v>
       </c>
       <c r="R28" t="n">
-        <v>6728528</v>
+        <v>6728428</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3295,7 +3307,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132406868</v>
+        <v>132406866</v>
       </c>
       <c r="B29" t="n">
         <v>79373</v>
@@ -3330,10 +3342,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>394102</v>
+        <v>394232</v>
       </c>
       <c r="R29" t="n">
-        <v>6728577</v>
+        <v>6728586</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3392,7 +3404,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132406869</v>
+        <v>132406867</v>
       </c>
       <c r="B30" t="n">
         <v>79373</v>
@@ -3427,10 +3439,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>394106</v>
+        <v>394208</v>
       </c>
       <c r="R30" t="n">
-        <v>6728622</v>
+        <v>6728528</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3489,7 +3501,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132406870</v>
+        <v>132406868</v>
       </c>
       <c r="B31" t="n">
         <v>79373</v>
@@ -3524,10 +3536,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>394127</v>
+        <v>394102</v>
       </c>
       <c r="R31" t="n">
-        <v>6728621</v>
+        <v>6728577</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3586,7 +3598,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132406871</v>
+        <v>132406869</v>
       </c>
       <c r="B32" t="n">
         <v>79373</v>
@@ -3621,10 +3633,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>394156</v>
+        <v>394106</v>
       </c>
       <c r="R32" t="n">
-        <v>6728616</v>
+        <v>6728622</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3683,7 +3695,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132406872</v>
+        <v>132406870</v>
       </c>
       <c r="B33" t="n">
         <v>79373</v>
@@ -3718,10 +3730,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>394181</v>
+        <v>394127</v>
       </c>
       <c r="R33" t="n">
-        <v>6728656</v>
+        <v>6728621</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3780,7 +3792,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132406873</v>
+        <v>132406871</v>
       </c>
       <c r="B34" t="n">
         <v>79373</v>
@@ -3815,10 +3827,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>394217</v>
+        <v>394156</v>
       </c>
       <c r="R34" t="n">
-        <v>6728660</v>
+        <v>6728616</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3877,7 +3889,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132406875</v>
+        <v>132406872</v>
       </c>
       <c r="B35" t="n">
         <v>79373</v>
@@ -3912,10 +3924,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>394228</v>
+        <v>394181</v>
       </c>
       <c r="R35" t="n">
-        <v>6728628</v>
+        <v>6728656</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3974,7 +3986,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132406876</v>
+        <v>132406873</v>
       </c>
       <c r="B36" t="n">
         <v>79373</v>
@@ -4009,10 +4021,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>394234</v>
+        <v>394217</v>
       </c>
       <c r="R36" t="n">
-        <v>6728610</v>
+        <v>6728660</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4071,7 +4083,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132406877</v>
+        <v>132406875</v>
       </c>
       <c r="B37" t="n">
         <v>79373</v>
@@ -4106,10 +4118,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>394260</v>
+        <v>394228</v>
       </c>
       <c r="R37" t="n">
-        <v>6728663</v>
+        <v>6728628</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4168,7 +4180,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132406878</v>
+        <v>132406876</v>
       </c>
       <c r="B38" t="n">
         <v>79373</v>
@@ -4203,10 +4215,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>394267</v>
+        <v>394234</v>
       </c>
       <c r="R38" t="n">
-        <v>6728664</v>
+        <v>6728610</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4265,7 +4277,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132406879</v>
+        <v>132406877</v>
       </c>
       <c r="B39" t="n">
         <v>79373</v>
@@ -4300,10 +4312,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>394255</v>
+        <v>394260</v>
       </c>
       <c r="R39" t="n">
-        <v>6728727</v>
+        <v>6728663</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4362,7 +4374,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132406880</v>
+        <v>132406878</v>
       </c>
       <c r="B40" t="n">
         <v>79373</v>
@@ -4397,10 +4409,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>394331</v>
+        <v>394267</v>
       </c>
       <c r="R40" t="n">
-        <v>6728694</v>
+        <v>6728664</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4459,7 +4471,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132406881</v>
+        <v>132406879</v>
       </c>
       <c r="B41" t="n">
         <v>79373</v>
@@ -4494,10 +4506,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>394330</v>
+        <v>394255</v>
       </c>
       <c r="R41" t="n">
-        <v>6728612</v>
+        <v>6728727</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4556,7 +4568,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132406882</v>
+        <v>132406880</v>
       </c>
       <c r="B42" t="n">
         <v>79373</v>
@@ -4591,10 +4603,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>394311</v>
+        <v>394331</v>
       </c>
       <c r="R42" t="n">
-        <v>6728550</v>
+        <v>6728694</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4653,7 +4665,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132406883</v>
+        <v>132406881</v>
       </c>
       <c r="B43" t="n">
         <v>79373</v>
@@ -4688,10 +4700,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>394348</v>
+        <v>394330</v>
       </c>
       <c r="R43" t="n">
-        <v>6728555</v>
+        <v>6728612</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4750,7 +4762,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132406884</v>
+        <v>132406882</v>
       </c>
       <c r="B44" t="n">
         <v>79373</v>
@@ -4785,10 +4797,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>394355</v>
+        <v>394311</v>
       </c>
       <c r="R44" t="n">
-        <v>6728562</v>
+        <v>6728550</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4847,7 +4859,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132406885</v>
+        <v>132406883</v>
       </c>
       <c r="B45" t="n">
         <v>79373</v>
@@ -4882,10 +4894,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>394365</v>
+        <v>394348</v>
       </c>
       <c r="R45" t="n">
-        <v>6728551</v>
+        <v>6728555</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4944,7 +4956,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132406887</v>
+        <v>132406884</v>
       </c>
       <c r="B46" t="n">
         <v>79373</v>
@@ -4979,10 +4991,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>394304</v>
+        <v>394355</v>
       </c>
       <c r="R46" t="n">
-        <v>6728722</v>
+        <v>6728562</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5041,7 +5053,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132406888</v>
+        <v>132406885</v>
       </c>
       <c r="B47" t="n">
         <v>79373</v>
@@ -5076,10 +5088,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>394326</v>
+        <v>394365</v>
       </c>
       <c r="R47" t="n">
-        <v>6728740</v>
+        <v>6728551</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5138,7 +5150,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132406889</v>
+        <v>132406887</v>
       </c>
       <c r="B48" t="n">
         <v>79373</v>
@@ -5173,10 +5185,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>394500</v>
+        <v>394304</v>
       </c>
       <c r="R48" t="n">
-        <v>6728810</v>
+        <v>6728722</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5235,7 +5247,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132406890</v>
+        <v>132406888</v>
       </c>
       <c r="B49" t="n">
         <v>79373</v>
@@ -5270,10 +5282,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>394513</v>
+        <v>394326</v>
       </c>
       <c r="R49" t="n">
-        <v>6728800</v>
+        <v>6728740</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5332,7 +5344,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132406891</v>
+        <v>132406889</v>
       </c>
       <c r="B50" t="n">
         <v>79373</v>
@@ -5367,10 +5379,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>394509</v>
+        <v>394500</v>
       </c>
       <c r="R50" t="n">
-        <v>6728838</v>
+        <v>6728810</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5429,7 +5441,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132406892</v>
+        <v>132406890</v>
       </c>
       <c r="B51" t="n">
         <v>79373</v>
@@ -5464,10 +5476,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>394552</v>
+        <v>394513</v>
       </c>
       <c r="R51" t="n">
-        <v>6728861</v>
+        <v>6728800</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5526,7 +5538,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132406893</v>
+        <v>132406891</v>
       </c>
       <c r="B52" t="n">
         <v>79373</v>
@@ -5561,10 +5573,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>394568</v>
+        <v>394509</v>
       </c>
       <c r="R52" t="n">
-        <v>6728820</v>
+        <v>6728838</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5623,32 +5635,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132406812</v>
+        <v>132406892</v>
       </c>
       <c r="B53" t="n">
-        <v>79397</v>
+        <v>79373</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5658,10 +5670,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>394226</v>
+        <v>394552</v>
       </c>
       <c r="R53" t="n">
-        <v>6728553</v>
+        <v>6728861</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5720,32 +5732,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132406813</v>
+        <v>132406893</v>
       </c>
       <c r="B54" t="n">
-        <v>79397</v>
+        <v>79373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5755,10 +5767,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>394324</v>
+        <v>394568</v>
       </c>
       <c r="R54" t="n">
-        <v>6728717</v>
+        <v>6728820</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5817,48 +5829,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119382194</v>
+        <v>132406812</v>
       </c>
       <c r="B55" t="n">
-        <v>78730</v>
+        <v>79397</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Öst Långavhallasätern, Vrm</t>
+          <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>394180</v>
+        <v>394226</v>
       </c>
       <c r="R55" t="n">
-        <v>6728494</v>
+        <v>6728553</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5882,12 +5894,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5902,22 +5914,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119382198</v>
+        <v>132406813</v>
       </c>
       <c r="B56" t="n">
-        <v>83290</v>
+        <v>79397</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5925,37 +5937,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6439</v>
+        <v>6434</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Öst Långavhallasätern, Vrm</t>
+          <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>394334</v>
+        <v>394324</v>
       </c>
       <c r="R56" t="n">
-        <v>6728532</v>
+        <v>6728717</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5979,12 +5991,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -5999,60 +6011,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132406851</v>
+        <v>119382194</v>
       </c>
       <c r="B57" t="n">
-        <v>83341</v>
+        <v>78730</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6439</v>
+        <v>6437</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Öst långavhallasätern, Vrm</t>
+          <t>Öst Långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>394369</v>
+        <v>394180</v>
       </c>
       <c r="R57" t="n">
-        <v>6728684</v>
+        <v>6728494</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6076,12 +6088,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6096,60 +6108,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132406780</v>
+        <v>119382198</v>
       </c>
       <c r="B58" t="n">
-        <v>83358</v>
+        <v>83290</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Öst långavhallasätern, Vrm</t>
+          <t>Öst Långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>394564</v>
+        <v>394334</v>
       </c>
       <c r="R58" t="n">
-        <v>6728842</v>
+        <v>6728532</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6173,12 +6185,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6193,60 +6205,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119382193</v>
+        <v>132406851</v>
       </c>
       <c r="B59" t="n">
-        <v>79084</v>
+        <v>83341</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6439</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Öst Långavhallasätern, Vrm</t>
+          <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>394189</v>
+        <v>394369</v>
       </c>
       <c r="R59" t="n">
-        <v>6728499</v>
+        <v>6728684</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6270,12 +6282,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6290,22 +6302,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132406849</v>
+        <v>132406780</v>
       </c>
       <c r="B60" t="n">
-        <v>79130</v>
+        <v>83358</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6313,21 +6325,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6337,10 +6349,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>394189</v>
+        <v>394564</v>
       </c>
       <c r="R60" t="n">
-        <v>6728492</v>
+        <v>6728842</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6399,10 +6411,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132406803</v>
+        <v>119382193</v>
       </c>
       <c r="B61" t="n">
-        <v>79459</v>
+        <v>79084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6410,37 +6422,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6450</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Öst långavhallasätern, Vrm</t>
+          <t>Öst Långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>394101</v>
+        <v>394189</v>
       </c>
       <c r="R61" t="n">
-        <v>6728595</v>
+        <v>6728499</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6464,12 +6476,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6484,22 +6496,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132406804</v>
+        <v>132406849</v>
       </c>
       <c r="B62" t="n">
-        <v>79459</v>
+        <v>79130</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6507,21 +6519,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6450</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6531,10 +6543,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>394251</v>
+        <v>394189</v>
       </c>
       <c r="R62" t="n">
-        <v>6728702</v>
+        <v>6728492</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6593,7 +6605,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132406806</v>
+        <v>132406803</v>
       </c>
       <c r="B63" t="n">
         <v>79459</v>
@@ -6628,10 +6640,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>394329</v>
+        <v>394101</v>
       </c>
       <c r="R63" t="n">
-        <v>6728656</v>
+        <v>6728595</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6690,7 +6702,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132406807</v>
+        <v>132406804</v>
       </c>
       <c r="B64" t="n">
         <v>79459</v>
@@ -6725,10 +6737,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>394333</v>
+        <v>394251</v>
       </c>
       <c r="R64" t="n">
-        <v>6728635</v>
+        <v>6728702</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6787,10 +6799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132406784</v>
+        <v>132406806</v>
       </c>
       <c r="B65" t="n">
-        <v>79992</v>
+        <v>79459</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6798,21 +6810,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6822,10 +6834,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>394200</v>
+        <v>394329</v>
       </c>
       <c r="R65" t="n">
-        <v>6728673</v>
+        <v>6728656</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6884,10 +6896,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132406785</v>
+        <v>132406807</v>
       </c>
       <c r="B66" t="n">
-        <v>79992</v>
+        <v>79459</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6895,21 +6907,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6919,10 +6931,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>394219</v>
+        <v>394333</v>
       </c>
       <c r="R66" t="n">
-        <v>6728660</v>
+        <v>6728635</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6981,7 +6993,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132406786</v>
+        <v>132406784</v>
       </c>
       <c r="B67" t="n">
         <v>79992</v>
@@ -7016,10 +7028,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>394302</v>
+        <v>394200</v>
       </c>
       <c r="R67" t="n">
-        <v>6728723</v>
+        <v>6728673</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7078,7 +7090,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132406788</v>
+        <v>132406785</v>
       </c>
       <c r="B68" t="n">
         <v>79992</v>
@@ -7113,7 +7125,7 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>394213</v>
+        <v>394219</v>
       </c>
       <c r="R68" t="n">
         <v>6728660</v>
@@ -7175,7 +7187,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132406789</v>
+        <v>132406786</v>
       </c>
       <c r="B69" t="n">
         <v>79992</v>
@@ -7210,10 +7222,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>394312</v>
+        <v>394302</v>
       </c>
       <c r="R69" t="n">
-        <v>6728711</v>
+        <v>6728723</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7272,7 +7284,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132406790</v>
+        <v>132406788</v>
       </c>
       <c r="B70" t="n">
         <v>79992</v>
@@ -7307,10 +7319,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>394508</v>
+        <v>394213</v>
       </c>
       <c r="R70" t="n">
-        <v>6728780</v>
+        <v>6728660</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7369,32 +7381,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132406810</v>
+        <v>132406789</v>
       </c>
       <c r="B71" t="n">
-        <v>80382</v>
+        <v>79992</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7404,10 +7416,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>394222</v>
+        <v>394312</v>
       </c>
       <c r="R71" t="n">
-        <v>6728619</v>
+        <v>6728711</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7466,32 +7478,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132406897</v>
+        <v>132406790</v>
       </c>
       <c r="B72" t="n">
-        <v>80382</v>
+        <v>79992</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7501,10 +7513,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>394323</v>
+        <v>394508</v>
       </c>
       <c r="R72" t="n">
-        <v>6728536</v>
+        <v>6728780</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7545,7 +7557,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7564,32 +7575,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132406837</v>
+        <v>132406810</v>
       </c>
       <c r="B73" t="n">
-        <v>80488</v>
+        <v>80382</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7599,10 +7610,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>394323</v>
+        <v>394222</v>
       </c>
       <c r="R73" t="n">
-        <v>6728533</v>
+        <v>6728619</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7661,32 +7672,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132406838</v>
+        <v>132406897</v>
       </c>
       <c r="B74" t="n">
-        <v>80488</v>
+        <v>80382</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7740,6 +7751,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7758,7 +7770,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132406839</v>
+        <v>132406837</v>
       </c>
       <c r="B75" t="n">
         <v>80488</v>
@@ -7793,10 +7805,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>394689</v>
+        <v>394323</v>
       </c>
       <c r="R75" t="n">
-        <v>6728620</v>
+        <v>6728533</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7855,7 +7867,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132406840</v>
+        <v>132406838</v>
       </c>
       <c r="B76" t="n">
         <v>80488</v>
@@ -7890,10 +7902,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>394333</v>
+        <v>394323</v>
       </c>
       <c r="R76" t="n">
-        <v>6728543</v>
+        <v>6728536</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -7952,10 +7964,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132406913</v>
+        <v>132406839</v>
       </c>
       <c r="B77" t="n">
-        <v>78377</v>
+        <v>80488</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7963,21 +7975,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -7987,10 +7999,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>394300</v>
+        <v>394689</v>
       </c>
       <c r="R77" t="n">
-        <v>6728717</v>
+        <v>6728620</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8049,10 +8061,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132406792</v>
+        <v>132406840</v>
       </c>
       <c r="B78" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8060,42 +8072,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>394390</v>
+        <v>394333</v>
       </c>
       <c r="R78" t="n">
-        <v>6728685</v>
+        <v>6728543</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8154,10 +8158,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132406794</v>
+        <v>132406913</v>
       </c>
       <c r="B79" t="n">
-        <v>57975</v>
+        <v>78377</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8165,42 +8169,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>394686</v>
+        <v>394300</v>
       </c>
       <c r="R79" t="n">
-        <v>6728607</v>
+        <v>6728717</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8259,7 +8255,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132406795</v>
+        <v>132406792</v>
       </c>
       <c r="B80" t="n">
         <v>57975</v>
@@ -8302,10 +8298,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>394414</v>
+        <v>394390</v>
       </c>
       <c r="R80" t="n">
-        <v>6728473</v>
+        <v>6728685</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8364,7 +8360,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132406796</v>
+        <v>132406794</v>
       </c>
       <c r="B81" t="n">
         <v>57975</v>
@@ -8407,10 +8403,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>394255</v>
+        <v>394686</v>
       </c>
       <c r="R81" t="n">
-        <v>6728707</v>
+        <v>6728607</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8469,7 +8465,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132406797</v>
+        <v>132406795</v>
       </c>
       <c r="B82" t="n">
         <v>57975</v>
@@ -8512,10 +8508,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>394353</v>
+        <v>394414</v>
       </c>
       <c r="R82" t="n">
-        <v>6728558</v>
+        <v>6728473</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8574,7 +8570,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132406799</v>
+        <v>132406796</v>
       </c>
       <c r="B83" t="n">
         <v>57975</v>
@@ -8617,10 +8613,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>394395</v>
+        <v>394255</v>
       </c>
       <c r="R83" t="n">
-        <v>6728610</v>
+        <v>6728707</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8679,7 +8675,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132406800</v>
+        <v>132406797</v>
       </c>
       <c r="B84" t="n">
         <v>57975</v>
@@ -8722,10 +8718,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>394395</v>
+        <v>394353</v>
       </c>
       <c r="R84" t="n">
-        <v>6728615</v>
+        <v>6728558</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -8784,32 +8780,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132406801</v>
+        <v>132406799</v>
       </c>
       <c r="B85" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8817,7 +8813,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -8827,10 +8823,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>394300</v>
+        <v>394395</v>
       </c>
       <c r="R85" t="n">
-        <v>6728604</v>
+        <v>6728610</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -8889,32 +8885,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132406802</v>
+        <v>132406800</v>
       </c>
       <c r="B86" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8922,7 +8918,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -8932,10 +8928,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>394104</v>
+        <v>394395</v>
       </c>
       <c r="R86" t="n">
-        <v>6728596</v>
+        <v>6728615</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -8994,10 +8990,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132406811</v>
+        <v>132406801</v>
       </c>
       <c r="B87" t="n">
-        <v>98060</v>
+        <v>57162</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9005,34 +9001,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>394327</v>
+        <v>394300</v>
       </c>
       <c r="R87" t="n">
-        <v>6728676</v>
+        <v>6728604</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9091,45 +9095,53 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132406815</v>
+        <v>132406802</v>
       </c>
       <c r="B88" t="n">
-        <v>79131</v>
+        <v>57162</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Öst långavhallasätern, Vrm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>394482</v>
+        <v>394104</v>
       </c>
       <c r="R88" t="n">
-        <v>6728440</v>
+        <v>6728596</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9188,32 +9200,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132406816</v>
+        <v>132406811</v>
       </c>
       <c r="B89" t="n">
-        <v>79131</v>
+        <v>98060</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9223,10 +9235,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>394266</v>
+        <v>394327</v>
       </c>
       <c r="R89" t="n">
-        <v>6728588</v>
+        <v>6728676</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9285,7 +9297,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132406817</v>
+        <v>132406815</v>
       </c>
       <c r="B90" t="n">
         <v>79131</v>
@@ -9320,10 +9332,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>394230</v>
+        <v>394482</v>
       </c>
       <c r="R90" t="n">
-        <v>6728542</v>
+        <v>6728440</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9382,7 +9394,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132406818</v>
+        <v>132406816</v>
       </c>
       <c r="B91" t="n">
         <v>79131</v>
@@ -9417,10 +9429,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>394232</v>
+        <v>394266</v>
       </c>
       <c r="R91" t="n">
-        <v>6728542</v>
+        <v>6728588</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9479,7 +9491,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132406819</v>
+        <v>132406817</v>
       </c>
       <c r="B92" t="n">
         <v>79131</v>
@@ -9514,10 +9526,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>394191</v>
+        <v>394230</v>
       </c>
       <c r="R92" t="n">
-        <v>6728490</v>
+        <v>6728542</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -9576,7 +9588,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132406820</v>
+        <v>132406818</v>
       </c>
       <c r="B93" t="n">
         <v>79131</v>
@@ -9611,10 +9623,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>394100</v>
+        <v>394232</v>
       </c>
       <c r="R93" t="n">
-        <v>6728603</v>
+        <v>6728542</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -9673,7 +9685,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132406821</v>
+        <v>132406819</v>
       </c>
       <c r="B94" t="n">
         <v>79131</v>
@@ -9708,10 +9720,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>394200</v>
+        <v>394191</v>
       </c>
       <c r="R94" t="n">
-        <v>6728673</v>
+        <v>6728490</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -9770,7 +9782,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132406822</v>
+        <v>132406820</v>
       </c>
       <c r="B95" t="n">
         <v>79131</v>
@@ -9805,10 +9817,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>394220</v>
+        <v>394100</v>
       </c>
       <c r="R95" t="n">
-        <v>6728660</v>
+        <v>6728603</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -9867,7 +9879,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132406823</v>
+        <v>132406821</v>
       </c>
       <c r="B96" t="n">
         <v>79131</v>
@@ -9902,10 +9914,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>394266</v>
+        <v>394200</v>
       </c>
       <c r="R96" t="n">
-        <v>6728609</v>
+        <v>6728673</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -9964,7 +9976,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132406824</v>
+        <v>132406822</v>
       </c>
       <c r="B97" t="n">
         <v>79131</v>
@@ -9999,10 +10011,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>394268</v>
+        <v>394220</v>
       </c>
       <c r="R97" t="n">
-        <v>6728667</v>
+        <v>6728660</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10061,7 +10073,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132406825</v>
+        <v>132406823</v>
       </c>
       <c r="B98" t="n">
         <v>79131</v>
@@ -10096,10 +10108,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>394291</v>
+        <v>394266</v>
       </c>
       <c r="R98" t="n">
-        <v>6728707</v>
+        <v>6728609</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10158,7 +10170,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132406828</v>
+        <v>132406824</v>
       </c>
       <c r="B99" t="n">
         <v>79131</v>
@@ -10193,10 +10205,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>394371</v>
+        <v>394268</v>
       </c>
       <c r="R99" t="n">
-        <v>6728698</v>
+        <v>6728667</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10255,7 +10267,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132406829</v>
+        <v>132406825</v>
       </c>
       <c r="B100" t="n">
         <v>79131</v>
@@ -10290,10 +10302,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>394324</v>
+        <v>394291</v>
       </c>
       <c r="R100" t="n">
-        <v>6728712</v>
+        <v>6728707</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10352,7 +10364,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132406830</v>
+        <v>132406828</v>
       </c>
       <c r="B101" t="n">
         <v>79131</v>
@@ -10387,10 +10399,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>394321</v>
+        <v>394371</v>
       </c>
       <c r="R101" t="n">
-        <v>6728718</v>
+        <v>6728698</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10449,7 +10461,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132406831</v>
+        <v>132406829</v>
       </c>
       <c r="B102" t="n">
         <v>79131</v>
@@ -10484,7 +10496,7 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>394313</v>
+        <v>394324</v>
       </c>
       <c r="R102" t="n">
         <v>6728712</v>
@@ -10546,7 +10558,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132406832</v>
+        <v>132406830</v>
       </c>
       <c r="B103" t="n">
         <v>79131</v>
@@ -10581,10 +10593,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>394299</v>
+        <v>394321</v>
       </c>
       <c r="R103" t="n">
-        <v>6728725</v>
+        <v>6728718</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -10643,7 +10655,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132406834</v>
+        <v>132406831</v>
       </c>
       <c r="B104" t="n">
         <v>79131</v>
@@ -10678,10 +10690,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>394410</v>
+        <v>394313</v>
       </c>
       <c r="R104" t="n">
-        <v>6728838</v>
+        <v>6728712</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -10740,32 +10752,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132406845</v>
+        <v>132406832</v>
       </c>
       <c r="B105" t="n">
-        <v>80438</v>
+        <v>79131</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10775,10 +10787,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>394182</v>
+        <v>394299</v>
       </c>
       <c r="R105" t="n">
-        <v>6728645</v>
+        <v>6728725</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -10837,32 +10849,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132406846</v>
+        <v>132406834</v>
       </c>
       <c r="B106" t="n">
-        <v>80438</v>
+        <v>79131</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10872,10 +10884,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>394178</v>
+        <v>394410</v>
       </c>
       <c r="R106" t="n">
-        <v>6728650</v>
+        <v>6728838</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -10934,7 +10946,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132406847</v>
+        <v>132406845</v>
       </c>
       <c r="B107" t="n">
         <v>80438</v>
@@ -10969,10 +10981,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>394223</v>
+        <v>394182</v>
       </c>
       <c r="R107" t="n">
-        <v>6728619</v>
+        <v>6728645</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11031,7 +11043,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132406848</v>
+        <v>132406846</v>
       </c>
       <c r="B108" t="n">
         <v>80438</v>
@@ -11066,10 +11078,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>394323</v>
+        <v>394178</v>
       </c>
       <c r="R108" t="n">
-        <v>6728536</v>
+        <v>6728650</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11128,32 +11140,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132406791</v>
+        <v>132406847</v>
       </c>
       <c r="B109" t="n">
-        <v>79963</v>
+        <v>80438</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>229497</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11163,10 +11175,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>394101</v>
+        <v>394223</v>
       </c>
       <c r="R109" t="n">
-        <v>6728590</v>
+        <v>6728619</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11225,32 +11237,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132406835</v>
+        <v>132406848</v>
       </c>
       <c r="B110" t="n">
-        <v>78381</v>
+        <v>80438</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6000248</v>
+        <v>229497</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11260,10 +11272,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>394389</v>
+        <v>394323</v>
       </c>
       <c r="R110" t="n">
-        <v>6728679</v>
+        <v>6728536</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11304,7 +11316,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11323,32 +11334,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132406850</v>
+        <v>132406791</v>
       </c>
       <c r="B111" t="n">
-        <v>78381</v>
+        <v>79963</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6000248</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11358,10 +11369,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>394578</v>
+        <v>394101</v>
       </c>
       <c r="R111" t="n">
-        <v>6728822</v>
+        <v>6728590</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11417,6 +11428,201 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>132406835</v>
+      </c>
+      <c r="B112" t="n">
+        <v>78381</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>394389</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6728679</v>
+      </c>
+      <c r="S112" t="n">
+        <v>25</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>132406850</v>
+      </c>
+      <c r="B113" t="n">
+        <v>78381</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Öst långavhallasätern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>394578</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6728822</v>
+      </c>
+      <c r="S113" t="n">
+        <v>25</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12434-2026 artfynd.xlsx
+++ b/artfynd/A 12434-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY113"/>
+  <dimension ref="A1:AZ113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406781</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406909</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382199</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406899</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406900</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406905</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406907</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406908</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406895</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406896</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406842</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406844</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406782</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406783</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382206</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2231,6 +2311,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406852</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2334,6 +2419,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406853</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2431,6 +2521,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406854</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2528,6 +2623,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406857</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2625,6 +2725,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406858</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2722,6 +2827,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406859</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2819,6 +2929,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406860</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2916,6 +3031,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406861</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3013,6 +3133,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406862</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3110,6 +3235,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406863</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3207,6 +3337,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406864</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3304,6 +3439,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406865</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3401,6 +3541,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406866</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3498,6 +3643,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406867</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3595,6 +3745,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406868</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3692,6 +3847,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406869</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3789,6 +3949,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406870</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3886,6 +4051,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406871</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3983,6 +4153,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406872</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4080,6 +4255,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406873</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4177,6 +4357,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406875</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4274,6 +4459,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406876</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4371,6 +4561,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406877</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4468,6 +4663,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406878</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4565,6 +4765,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406879</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4662,6 +4867,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406880</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4759,6 +4969,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406881</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4856,6 +5071,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406882</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4953,6 +5173,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406883</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5050,6 +5275,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406884</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5147,6 +5377,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406885</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5244,6 +5479,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406887</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5341,6 +5581,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406888</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5438,6 +5683,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406889</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5535,6 +5785,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406890</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5632,6 +5887,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406891</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5729,6 +5989,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406892</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5826,6 +6091,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406893</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5923,6 +6193,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406812</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6020,6 +6295,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406813</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6117,6 +6397,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382194</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6214,6 +6499,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382198</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6311,6 +6601,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406851</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6408,6 +6703,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406780</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6505,6 +6805,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119382193</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6602,6 +6907,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406849</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6699,6 +7009,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406803</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6796,6 +7111,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406804</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6893,6 +7213,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406806</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6990,6 +7315,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406807</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7087,6 +7417,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406784</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7184,6 +7519,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406785</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7281,6 +7621,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406786</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7378,6 +7723,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406788</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7475,6 +7825,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406789</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7572,6 +7927,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406790</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7669,6 +8029,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406810</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7767,6 +8132,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406897</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7864,6 +8234,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406837</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7961,6 +8336,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406838</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8058,6 +8438,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406839</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8155,6 +8540,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406840</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8252,6 +8642,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406913</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8357,6 +8752,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406792</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8462,6 +8862,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406794</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8567,6 +8972,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406795</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8672,6 +9082,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406796</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8777,6 +9192,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406797</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8882,6 +9302,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406799</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8987,6 +9412,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406800</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9092,6 +9522,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406801</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9197,6 +9632,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406802</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9294,6 +9734,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406811</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9391,6 +9836,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406815</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9488,6 +9938,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406816</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9585,6 +10040,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406817</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9682,6 +10142,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406818</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9779,6 +10244,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406819</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9876,6 +10346,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406820</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9973,6 +10448,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406821</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10070,6 +10550,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406822</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10167,6 +10652,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406823</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10264,6 +10754,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406824</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10361,6 +10856,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406825</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10458,6 +10958,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406828</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10555,6 +11060,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406829</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10652,6 +11162,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406830</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10749,6 +11264,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406831</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10846,6 +11366,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406832</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10943,6 +11468,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406834</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11040,6 +11570,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406845</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11137,6 +11672,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406846</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11234,6 +11774,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406847</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11331,6 +11876,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406848</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11428,6 +11978,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406791</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11526,6 +12081,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406835</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11623,8 +12183,127 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132406850</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>